--- a/Seguimiento de Vacantes.xlsx
+++ b/Seguimiento de Vacantes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan Pablo Sanchez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89C3CDD6-1B20-4CBD-B2D3-179B4F56FE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFF3D570-E1C6-4DFC-BFE3-3DB362DCC267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{3B13A29B-20F1-4D27-890C-391D6AD58285}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" firstSheet="4" xr2:uid="{3B13A29B-20F1-4D27-890C-391D6AD58285}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE" sheetId="1" r:id="rId1"/>
@@ -20,11 +20,11 @@
     <sheet name="Búsqueda rápida. " sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BASE!$A$1:$AN$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BASE!$A$1:$AN$309</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="326" r:id="rId6"/>
+    <pivotCache cacheId="1249" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6189" uniqueCount="1649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6299" uniqueCount="1656">
   <si>
     <t>N° Vacante</t>
   </si>
@@ -2837,13 +2837,16 @@
     <t>00160</t>
   </si>
   <si>
+    <t>Entrevista Hiring Manager</t>
+  </si>
+  <si>
     <t>Blanco Beatriz</t>
   </si>
   <si>
     <t>TT - 14 a 22 HS</t>
   </si>
   <si>
-    <t>ANA TORRES</t>
+    <t xml:space="preserve"> 7/4 Se baja del proceso previo a la firma</t>
   </si>
   <si>
     <t>00161</t>
@@ -2993,10 +2996,13 @@
     <t xml:space="preserve">Preselección/Screening </t>
   </si>
   <si>
+    <t xml:space="preserve">Renuncia </t>
+  </si>
+  <si>
     <t>00173</t>
   </si>
   <si>
-    <t>SANCHEZ OLIVERA, ROMINA (1088)</t>
+    <t>SANCHEZ OLIVERA, ROMINA</t>
   </si>
   <si>
     <t>00174</t>
@@ -3191,9 +3197,6 @@
     <t>Gerente/a de Compras</t>
   </si>
   <si>
-    <t>Entrevista Hiring Manager</t>
-  </si>
-  <si>
     <t>Se abre nuevamente la búsqueda. El proceso anterior inicio en 10/2025. Con esta nueva apertura se busca un perfil con foco en compras pero con potencial para tomar áreas de administración y operación</t>
   </si>
   <si>
@@ -3218,9 +3221,6 @@
     <t>Ayelen Sanchez</t>
   </si>
   <si>
-    <t xml:space="preserve">Renuncia </t>
-  </si>
-  <si>
     <t>CRISTINA BRAVO</t>
   </si>
   <si>
@@ -3605,19 +3605,19 @@
     <t>Turno Noche - Viernes 20hs a 08 am</t>
   </si>
   <si>
+    <t>00228</t>
+  </si>
+  <si>
+    <t>WALL, DEBORAH</t>
+  </si>
+  <si>
+    <t>Miercoles 8 a 20 hs</t>
+  </si>
+  <si>
     <t>Evelyn Gladys Ergueta</t>
   </si>
   <si>
-    <t>00228</t>
-  </si>
-  <si>
-    <t>WALL, DEBORAH</t>
-  </si>
-  <si>
-    <t>Miercoles 8 a 20 hs</t>
-  </si>
-  <si>
-    <t>Agustin Aller</t>
+    <t xml:space="preserve"> $1.190.771,47 bruto /	 $970.478,75 neto</t>
   </si>
   <si>
     <t>00229</t>
@@ -3743,7 +3743,13 @@
     <t>Lima Pedro</t>
   </si>
   <si>
+    <t>Lunes a Viernes 8 a 14 hs</t>
+  </si>
+  <si>
     <t>Diego Gabela</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> $2.636.960,68 bruto /	 $2.162.073,00 neto</t>
   </si>
   <si>
     <t>00241</t>
@@ -3943,7 +3949,7 @@
     <t>Pendiente de Aprobación</t>
   </si>
   <si>
-    <t>Galadis Ortiz</t>
+    <t>NEGRI, ELENA GLADYS</t>
   </si>
   <si>
     <t>9 a 18 hs lunes a Viernes</t>
@@ -3976,16 +3982,31 @@
     <t>00266</t>
   </si>
   <si>
+    <t>GUTCOVSKY, JULIETA</t>
+  </si>
+  <si>
     <t>00267</t>
   </si>
   <si>
+    <t>YAÑES BOGNI, MATIAS VALENTIN</t>
+  </si>
+  <si>
     <t>00268</t>
   </si>
   <si>
+    <t>MENESES MARIN, TANIUSKA ROGERLYS</t>
+  </si>
+  <si>
     <t>00269</t>
   </si>
   <si>
+    <t>CORREA, CAMILA MARIEL</t>
+  </si>
+  <si>
     <t>00270</t>
+  </si>
+  <si>
+    <t>PONCE, MATHEO NICOLAS</t>
   </si>
   <si>
     <t>00271</t>
@@ -5345,7 +5366,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Excel Services" refreshedDate="46119.375298726853" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="303" xr:uid="{ABBB2370-C06A-4D77-8664-32F0663D2C71}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Excel Services" refreshedDate="46119.622350231482" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="303" xr:uid="{ABBB2370-C06A-4D77-8664-32F0663D2C71}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:AN304" sheet="BASE"/>
   </cacheSource>
@@ -5354,7 +5375,7 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Fecha de solicitud" numFmtId="0">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2025-01-16T00:00:00" maxDate="2026-04-02T00:00:00"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2025-01-16T00:00:00" maxDate="2026-04-07T00:00:00"/>
     </cacheField>
     <cacheField name="Días de apertura" numFmtId="1">
       <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="6" maxValue="203"/>
@@ -5437,8 +5458,8 @@
         <s v="En proceso de Ingreso"/>
         <s v="StandBy"/>
         <s v="Cancelada"/>
+        <s v="Pendiente de Aprobación"/>
         <m/>
-        <s v="Pendiente de Aprobación" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Status del proceso " numFmtId="0">
@@ -5457,10 +5478,10 @@
         <s v="Entrevista Hiring Manager"/>
         <s v="Ingreso"/>
         <s v="Relevamiento de Perfil"/>
+        <s v="Pendiente de Aprobación"/>
         <s v="Entrevista Gestor" u="1"/>
         <s v="Psicotécnico " u="1"/>
         <s v="Psicotécnico" u="1"/>
-        <s v="Pendiente de Aprobación" u="1"/>
         <s v="Publicación/Analizando CVs" u="1"/>
         <s v="Cerrada" u="1"/>
       </sharedItems>
@@ -5478,7 +5499,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Número de Legajo del reemplazo" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="818" maxValue="170649"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="11" maxValue="170649"/>
     </cacheField>
     <cacheField name="Nombre de reemplazo " numFmtId="0">
       <sharedItems containsBlank="1"/>
@@ -5502,7 +5523,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Fecha de cierre" numFmtId="0">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2025-11-06T00:00:00" maxDate="2026-03-31T00:00:00"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2025-11-06T00:00:00" maxDate="2026-04-08T00:00:00"/>
     </cacheField>
     <cacheField name="Fecha de Ingreso" numFmtId="0">
       <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-01-02T00:00:00" maxDate="2026-04-09T00:00:00"/>
@@ -12747,9 +12768,9 @@
     <s v="Baja"/>
     <s v="Media"/>
     <s v="Reemplazo"/>
-    <m/>
+    <n v="169836"/>
     <s v="Adrian Torosantucci"/>
-    <m/>
+    <s v="Renuncia "/>
     <s v="Inderminado "/>
     <m/>
     <m/>
@@ -12789,9 +12810,9 @@
     <s v="Baja"/>
     <s v="Media"/>
     <s v="Reemplazo"/>
-    <m/>
-    <s v="SANCHEZ OLIVERA, ROMINA (1088)"/>
-    <m/>
+    <n v="1088"/>
+    <s v="SANCHEZ OLIVERA, ROMINA"/>
+    <s v="Desvinculación empresa"/>
     <s v="Inderminado "/>
     <m/>
     <m/>
@@ -12957,9 +12978,9 @@
     <s v="Baja"/>
     <s v="Media"/>
     <s v="Reemplazo"/>
-    <m/>
+    <n v="157853"/>
     <s v="MENDIETA, MARTIN JULIAN"/>
-    <m/>
+    <s v="Renuncia "/>
     <s v="Inderminado "/>
     <m/>
     <m/>
@@ -12999,9 +13020,9 @@
     <s v="Baja"/>
     <s v="Media"/>
     <s v="Reemplazo"/>
-    <m/>
+    <n v="1002"/>
     <s v="Ferreyra, Maria Pia"/>
-    <m/>
+    <s v="Renuncia "/>
     <s v="Inderminado "/>
     <m/>
     <m/>
@@ -13041,9 +13062,9 @@
     <s v="Baja"/>
     <s v="Media"/>
     <s v="Reemplazo"/>
-    <m/>
+    <n v="154670"/>
     <s v="GONZALEZ, CONSTANZA ROMINA"/>
-    <m/>
+    <s v="Renuncia "/>
     <s v="Inderminado "/>
     <m/>
     <m/>
@@ -13839,9 +13860,9 @@
     <s v="Baja"/>
     <s v="Media"/>
     <s v="Reemplazo"/>
-    <m/>
+    <n v="168093"/>
     <s v="PEREDA, VANESSA RITA"/>
-    <m/>
+    <s v="Renuncia "/>
     <s v="Inderminado "/>
     <m/>
     <m/>
@@ -13883,7 +13904,7 @@
     <s v="Reemplazo"/>
     <n v="818"/>
     <s v="Contreras, Paula"/>
-    <m/>
+    <s v="Renuncia "/>
     <s v="Inderminado "/>
     <m/>
     <m/>
@@ -13925,7 +13946,7 @@
     <s v="Reemplazo"/>
     <n v="1036"/>
     <s v="Miranda, Daira"/>
-    <m/>
+    <s v="Renuncia "/>
     <s v="Inderminado "/>
     <m/>
     <m/>
@@ -13967,7 +13988,7 @@
     <s v="Reemplazo"/>
     <n v="170601"/>
     <s v="ROJAS VIDABLE, ROMINA LORENA"/>
-    <m/>
+    <s v="Renuncia "/>
     <s v="Inderminado "/>
     <m/>
     <m/>
@@ -14009,7 +14030,7 @@
     <s v="Reemplazo"/>
     <n v="170649"/>
     <s v="DREE, JOEL IGNACIO"/>
-    <m/>
+    <s v="Desvinculación empresa"/>
     <s v="Inderminado "/>
     <m/>
     <m/>
@@ -14051,7 +14072,7 @@
     <s v="Reemplazo"/>
     <n v="1099"/>
     <s v="GONZALEZ, RODRIGO CRISTIAN EMMANUEL"/>
-    <m/>
+    <s v="Renuncia "/>
     <s v="Inderminado "/>
     <m/>
     <m/>
@@ -14257,7 +14278,7 @@
     <x v="4"/>
     <m/>
     <s v="Alta "/>
-    <s v="Baja "/>
+    <s v="Media"/>
     <s v="Reemplazo"/>
     <m/>
     <s v="Liz Marlene Rodriguez"/>
@@ -16590,38 +16611,38 @@
   </r>
   <r>
     <s v="00264"/>
-    <m/>
-    <s v=""/>
+    <d v="2026-04-06T00:00:00"/>
+    <s v="Cerrada"/>
+    <x v="1"/>
+    <s v="Pendiente"/>
+    <s v="No"/>
+    <m/>
+    <m/>
     <x v="5"/>
     <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="9"/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="12"/>
-    <m/>
-    <m/>
+    <s v="Atención al Paciente"/>
+    <s v="Operaciones"/>
+    <x v="3"/>
+    <s v="FACTURISTA"/>
+    <s v="Valeria Rios"/>
     <m/>
     <x v="5"/>
-    <x v="9"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <x v="14"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Reemplazo"/>
+    <n v="11"/>
+    <s v="NEGRI, ELENA GLADYS"/>
+    <s v="Renuncia "/>
+    <s v="Inderminado "/>
+    <m/>
+    <m/>
+    <s v="9 a 18 hs lunes a Viernes"/>
+    <s v="Sede Amenabar"/>
+    <m/>
+    <m/>
+    <s v="Externa"/>
     <m/>
     <m/>
     <m/>
@@ -16632,40 +16653,40 @@
   </r>
   <r>
     <s v="00265"/>
-    <m/>
-    <s v=""/>
+    <d v="2026-03-31T00:00:00"/>
+    <n v="7"/>
+    <x v="4"/>
+    <s v="Aprobada"/>
+    <s v="No"/>
+    <m/>
+    <m/>
+    <x v="4"/>
+    <s v="Cobensil SA"/>
+    <s v="Pagos"/>
+    <s v="ADMINISTRACION Y FINANZAS"/>
+    <x v="3"/>
+    <s v="ADMINISTRATIVO/A"/>
+    <s v="Carla Fado"/>
+    <m/>
+    <x v="2"/>
     <x v="5"/>
     <m/>
     <m/>
     <m/>
-    <m/>
-    <x v="9"/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="12"/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="5"/>
-    <x v="9"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="Reemplazo"/>
+    <m/>
+    <s v="Analia Olmeda"/>
+    <s v="Renuncia "/>
+    <s v="Inderminado "/>
+    <m/>
+    <m/>
+    <s v="9 a 18 hs lunes a Viernes"/>
+    <s v="La Musa"/>
+    <d v="2026-04-07T00:00:00"/>
+    <d v="2026-04-08T00:00:00"/>
+    <s v="Interna"/>
+    <s v="Búsqueda Interna"/>
+    <s v="Tirado Laurente, Florencia "/>
     <m/>
     <m/>
     <m/>
@@ -16674,31 +16695,31 @@
   </r>
   <r>
     <s v="00266"/>
-    <m/>
-    <s v=""/>
-    <x v="5"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="9"/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="12"/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="5"/>
-    <x v="9"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <d v="2026-03-27T00:00:00"/>
+    <n v="11"/>
+    <x v="0"/>
+    <s v="Aprobada"/>
+    <s v="No"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <s v="Ventas Retail"/>
+    <s v="Comercial"/>
+    <x v="0"/>
+    <s v="VENDEDOR/A"/>
+    <s v="Serafin"/>
+    <m/>
+    <x v="1"/>
+    <x v="10"/>
+    <m/>
+    <s v="Baja"/>
+    <s v="Media"/>
+    <s v="Reemplazo"/>
+    <n v="170632"/>
+    <s v="GUTCOVSKY, JULIETA"/>
+    <s v="Renuncia "/>
+    <s v="Inderminado "/>
     <m/>
     <m/>
     <m/>
@@ -16716,31 +16737,31 @@
   </r>
   <r>
     <s v="00267"/>
-    <m/>
-    <s v=""/>
-    <x v="5"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="9"/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="12"/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="5"/>
-    <x v="9"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <d v="2026-03-31T00:00:00"/>
+    <n v="7"/>
+    <x v="0"/>
+    <s v="Aprobada"/>
+    <s v="No"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <s v="Ventas Retail"/>
+    <s v="Comercial"/>
+    <x v="0"/>
+    <s v="VENDEDOR/A"/>
+    <s v="Serafin"/>
+    <m/>
+    <x v="1"/>
+    <x v="10"/>
+    <m/>
+    <s v="Baja"/>
+    <s v="Media"/>
+    <s v="Reemplazo"/>
+    <n v="1094"/>
+    <s v="YAÑES BOGNI, MATIAS VALENTIN"/>
+    <s v="Renuncia "/>
+    <s v="Inderminado "/>
     <m/>
     <m/>
     <m/>
@@ -16758,31 +16779,31 @@
   </r>
   <r>
     <s v="00268"/>
-    <m/>
-    <s v=""/>
-    <x v="5"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="9"/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="12"/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="5"/>
-    <x v="9"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <d v="2026-03-16T00:00:00"/>
+    <n v="22"/>
+    <x v="0"/>
+    <s v="Aprobada"/>
+    <s v="No"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <s v="Ventas Retail"/>
+    <s v="Comercial"/>
+    <x v="0"/>
+    <s v="VENDEDOR/A"/>
+    <s v="Serafin"/>
+    <m/>
+    <x v="1"/>
+    <x v="10"/>
+    <m/>
+    <s v="Baja"/>
+    <s v="Media"/>
+    <s v="Reemplazo"/>
+    <n v="1093"/>
+    <s v="MENESES MARIN, TANIUSKA ROGERLYS"/>
+    <s v="Desvinculación empresa"/>
+    <s v="Inderminado "/>
     <m/>
     <m/>
     <m/>
@@ -16800,31 +16821,31 @@
   </r>
   <r>
     <s v="00269"/>
-    <m/>
-    <s v=""/>
-    <x v="5"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="9"/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="12"/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="5"/>
-    <x v="9"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <d v="2026-03-16T00:00:00"/>
+    <n v="22"/>
+    <x v="0"/>
+    <s v="Aprobada"/>
+    <s v="No"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <s v="Ventas Retail"/>
+    <s v="Comercial"/>
+    <x v="0"/>
+    <s v="VENDEDOR/A"/>
+    <s v="Serafin"/>
+    <m/>
+    <x v="1"/>
+    <x v="10"/>
+    <m/>
+    <s v="Baja"/>
+    <s v="Media"/>
+    <s v="Reemplazo"/>
+    <n v="168680"/>
+    <s v="CORREA, CAMILA MARIEL"/>
+    <s v="Desvinculación empresa"/>
+    <s v="Inderminado "/>
     <m/>
     <m/>
     <m/>
@@ -16842,31 +16863,31 @@
   </r>
   <r>
     <s v="00270"/>
-    <m/>
-    <s v=""/>
-    <x v="5"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="9"/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="12"/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="5"/>
-    <x v="9"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <d v="2026-03-16T00:00:00"/>
+    <n v="22"/>
+    <x v="0"/>
+    <s v="Aprobada"/>
+    <s v="No"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <s v="Ventas Retail"/>
+    <s v="Comercial"/>
+    <x v="0"/>
+    <s v="VENDEDOR/A"/>
+    <s v="Serafin"/>
+    <m/>
+    <x v="1"/>
+    <x v="10"/>
+    <m/>
+    <s v="Baja"/>
+    <s v="Media"/>
+    <s v="Reemplazo"/>
+    <n v="168697"/>
+    <s v="PONCE, MATHEO NICOLAS"/>
+    <s v="Desvinculación empresa"/>
+    <s v="Inderminado "/>
     <m/>
     <m/>
     <m/>
@@ -16899,7 +16920,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -16941,7 +16962,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -16983,7 +17004,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17025,7 +17046,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17067,7 +17088,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17109,7 +17130,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17151,7 +17172,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17193,7 +17214,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17235,7 +17256,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17277,7 +17298,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17319,7 +17340,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17361,7 +17382,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17403,7 +17424,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17445,7 +17466,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17487,7 +17508,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17529,7 +17550,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17571,7 +17592,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17613,7 +17634,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17655,7 +17676,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17697,7 +17718,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17739,7 +17760,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17781,7 +17802,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17823,7 +17844,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17865,7 +17886,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17907,7 +17928,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17949,7 +17970,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -17991,7 +18012,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -18033,7 +18054,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -18075,7 +18096,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -18117,7 +18138,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -18159,7 +18180,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -18201,7 +18222,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -18243,7 +18264,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="5"/>
+    <x v="6"/>
     <x v="9"/>
     <m/>
     <m/>
@@ -18272,7 +18293,183 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7C50B5DE-D50F-4C80-82D7-43929FE13854}" name="TablaDinámica5" cacheId="326" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6DB312C6-2869-4C58-B7C2-10B48ECD48B8}" name="Tabla dinámica1" cacheId="1249" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A12:J19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="40">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="descending">
+      <items count="11">
+        <item x="2"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item h="1" x="9"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="8">
+        <item h="1" x="4"/>
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item h="1" x="3"/>
+        <item x="6"/>
+        <item h="1" x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="21">
+        <item x="7"/>
+        <item x="8"/>
+        <item m="1" x="15"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item m="1" x="17"/>
+        <item x="13"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item m="1" x="19"/>
+        <item m="1" x="18"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="11"/>
+        <item m="1" x="16"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="17"/>
+  </colFields>
+  <colItems count="9">
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="16" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Familia de Puesto" fld="12" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7C50B5DE-D50F-4C80-82D7-43929FE13854}" name="TablaDinámica5" cacheId="1249" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A5:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="40">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -18321,8 +18518,8 @@
         <item x="1"/>
         <item x="2"/>
         <item h="1" x="3"/>
-        <item x="5"/>
-        <item h="1" m="1" x="6"/>
+        <item x="6"/>
+        <item h="1" x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -18330,11 +18527,11 @@
       <items count="21">
         <item x="7"/>
         <item x="8"/>
-        <item m="1" x="14"/>
+        <item m="1" x="15"/>
         <item x="1"/>
         <item x="0"/>
         <item x="3"/>
-        <item m="1" x="16"/>
+        <item m="1" x="17"/>
         <item x="13"/>
         <item x="6"/>
         <item x="9"/>
@@ -18345,9 +18542,9 @@
         <item x="10"/>
         <item x="5"/>
         <item x="11"/>
-        <item m="1" x="15"/>
+        <item m="1" x="16"/>
         <item x="12"/>
-        <item m="1" x="17"/>
+        <item x="14"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -18408,8 +18605,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AAFDAB6A-7018-4F4F-9BCD-4A1F9F2FBFF2}" name="TablaDinámica4" cacheId="326" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AAFDAB6A-7018-4F4F-9BCD-4A1F9F2FBFF2}" name="TablaDinámica4" cacheId="1249" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A51:D61" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="40">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -18494,8 +18691,8 @@
         <item x="1"/>
         <item x="2"/>
         <item h="1" x="3"/>
+        <item h="1" x="6"/>
         <item h="1" x="5"/>
-        <item h="1" m="1" x="6"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -18503,11 +18700,11 @@
       <items count="21">
         <item x="7"/>
         <item x="8"/>
-        <item m="1" x="14"/>
+        <item m="1" x="15"/>
         <item x="1"/>
         <item x="0"/>
         <item x="3"/>
-        <item m="1" x="16"/>
+        <item m="1" x="17"/>
         <item x="13"/>
         <item x="6"/>
         <item x="9"/>
@@ -18518,9 +18715,9 @@
         <item x="10"/>
         <item x="5"/>
         <item x="11"/>
-        <item m="1" x="15"/>
+        <item m="1" x="16"/>
         <item x="12"/>
-        <item m="1" x="17"/>
+        <item x="14"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -18612,8 +18809,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0CA6B483-6C7D-4E04-A036-9E58477B651E}" name="TablaDinámica3" cacheId="326" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0CA6B483-6C7D-4E04-A036-9E58477B651E}" name="TablaDinámica3" cacheId="1249" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A39:D45" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="40">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -18668,8 +18865,8 @@
         <item x="1"/>
         <item x="2"/>
         <item h="1" x="3"/>
+        <item h="1" x="6"/>
         <item h="1" x="5"/>
-        <item h="1" m="1" x="6"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -18677,11 +18874,11 @@
       <items count="21">
         <item x="7"/>
         <item x="8"/>
-        <item m="1" x="14"/>
+        <item m="1" x="15"/>
         <item x="1"/>
         <item x="0"/>
         <item x="3"/>
-        <item m="1" x="16"/>
+        <item m="1" x="17"/>
         <item x="13"/>
         <item x="6"/>
         <item x="9"/>
@@ -18692,9 +18889,9 @@
         <item x="10"/>
         <item x="5"/>
         <item x="11"/>
-        <item m="1" x="15"/>
+        <item m="1" x="16"/>
         <item x="12"/>
-        <item m="1" x="17"/>
+        <item x="14"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -18773,8 +18970,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7743F151-BF27-48DE-9002-CBE448111DE7}" name="TablaDinámica1" cacheId="326" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7743F151-BF27-48DE-9002-CBE448111DE7}" name="TablaDinámica1" cacheId="1249" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A26:B32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="40">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -18823,8 +19020,8 @@
         <item x="1"/>
         <item x="2"/>
         <item h="1" x="3"/>
-        <item x="5"/>
-        <item h="1" m="1" x="6"/>
+        <item x="6"/>
+        <item h="1" x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -18832,11 +19029,11 @@
       <items count="21">
         <item h="1" x="7"/>
         <item h="1" x="8"/>
-        <item m="1" x="14"/>
+        <item m="1" x="15"/>
         <item x="1"/>
         <item h="1" x="0"/>
         <item x="3"/>
-        <item m="1" x="16"/>
+        <item m="1" x="17"/>
         <item x="13"/>
         <item h="1" x="6"/>
         <item h="1" x="9"/>
@@ -18847,9 +19044,9 @@
         <item x="10"/>
         <item x="5"/>
         <item x="11"/>
-        <item m="1" x="15"/>
+        <item m="1" x="16"/>
         <item h="1" x="12"/>
-        <item h="1" m="1" x="17"/>
+        <item h="1" x="14"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -18904,182 +19101,6 @@
   </colItems>
   <pageFields count="2">
     <pageField fld="17" hier="-1"/>
-    <pageField fld="16" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Familia de Puesto" fld="12" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6DB312C6-2869-4C58-B7C2-10B48ECD48B8}" name="Tabla dinámica1" cacheId="326" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A12:J19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="40">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="descending">
-      <items count="11">
-        <item x="2"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item h="1" x="9"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="8">
-        <item h="1" x="4"/>
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item h="1" x="3"/>
-        <item x="5"/>
-        <item h="1" m="1" x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="21">
-        <item x="7"/>
-        <item x="8"/>
-        <item m="1" x="14"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item m="1" x="16"/>
-        <item x="13"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item m="1" x="19"/>
-        <item m="1" x="18"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="11"/>
-        <item m="1" x="15"/>
-        <item x="12"/>
-        <item m="1" x="17"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="17"/>
-  </colFields>
-  <colItems count="9">
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
     <pageField fld="16" hier="-1"/>
   </pageFields>
   <dataFields count="1">
@@ -19394,7 +19415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{325F248B-5B5A-4EA2-90C8-48DA023AA97A}">
-  <dimension ref="A1:AN309"/>
+  <dimension ref="A1:AN310"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="6" customWidth="1"/>
@@ -19409,14 +19430,14 @@
     <col min="10" max="10" width="27.140625" style="6" customWidth="1"/>
     <col min="11" max="11" width="30.28515625" style="6" customWidth="1"/>
     <col min="12" max="12" width="30.140625" style="6" customWidth="1"/>
-    <col min="13" max="13" width="34.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="34.140625" style="6" customWidth="1"/>
     <col min="14" max="14" width="47.5703125" style="6" customWidth="1"/>
     <col min="15" max="15" width="21.140625" style="6" customWidth="1"/>
     <col min="16" max="16" width="21.7109375" style="6" customWidth="1"/>
     <col min="17" max="17" width="24.28515625" style="6" customWidth="1"/>
     <col min="18" max="18" width="33.5703125" style="6" customWidth="1"/>
-    <col min="19" max="19" width="24.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="11.42578125" style="6"/>
+    <col min="19" max="19" width="24.42578125" style="6" customWidth="1"/>
+    <col min="20" max="21" width="11.42578125" style="6" customWidth="1"/>
     <col min="22" max="23" width="32.42578125" style="6" customWidth="1"/>
     <col min="24" max="24" width="46" style="6" customWidth="1"/>
     <col min="25" max="25" width="26.5703125" style="6" bestFit="1" customWidth="1"/>
@@ -30510,9 +30531,9 @@
       <c r="B118" s="5">
         <v>46036</v>
       </c>
-      <c r="C118" s="17">
+      <c r="C118" s="17" t="str">
         <f ca="1">IF(B118="","",IF(OR(TRIM(Q118)="En curso",TRIM(Q118)="En proceso de ingreso"),TODAY()-B118,"Cerrada"))</f>
-        <v>83</v>
+        <v>Cerrada</v>
       </c>
       <c r="D118" s="8" t="s">
         <v>144</v>
@@ -30546,10 +30567,10 @@
       </c>
       <c r="P118" s="8"/>
       <c r="Q118" s="8" t="s">
-        <v>472</v>
+        <v>51</v>
       </c>
       <c r="R118" s="8" t="s">
-        <v>733</v>
+        <v>52</v>
       </c>
       <c r="S118" s="8"/>
       <c r="T118" s="8" t="s">
@@ -30611,9 +30632,9 @@
       <c r="B119" s="5">
         <v>46036</v>
       </c>
-      <c r="C119" s="17">
+      <c r="C119" s="17" t="str">
         <f ca="1">IF(B119="","",IF(OR(TRIM(Q119)="En curso",TRIM(Q119)="En proceso de ingreso"),TODAY()-B119,"Cerrada"))</f>
-        <v>83</v>
+        <v>Cerrada</v>
       </c>
       <c r="D119" s="8" t="s">
         <v>144</v>
@@ -30647,10 +30668,10 @@
       </c>
       <c r="P119" s="8"/>
       <c r="Q119" s="8" t="s">
-        <v>472</v>
+        <v>51</v>
       </c>
       <c r="R119" s="8" t="s">
-        <v>733</v>
+        <v>52</v>
       </c>
       <c r="S119" s="8"/>
       <c r="T119" s="8" t="s">
@@ -31624,9 +31645,9 @@
       <c r="B130" s="5">
         <v>46052</v>
       </c>
-      <c r="C130" s="17">
+      <c r="C130" s="17" t="str">
         <f ca="1">IF(B130="","",IF(OR(TRIM(Q130)="En curso",TRIM(Q130)="En proceso de ingreso"),TODAY()-B130,"Cerrada"))</f>
-        <v>67</v>
+        <v>Cerrada</v>
       </c>
       <c r="D130" s="8" t="s">
         <v>144</v>
@@ -31660,10 +31681,10 @@
       </c>
       <c r="P130" s="8"/>
       <c r="Q130" s="8" t="s">
-        <v>472</v>
+        <v>51</v>
       </c>
       <c r="R130" s="8" t="s">
-        <v>733</v>
+        <v>52</v>
       </c>
       <c r="S130" s="8"/>
       <c r="T130" s="8" t="s">
@@ -31917,9 +31938,9 @@
       <c r="B133" s="5">
         <v>46054</v>
       </c>
-      <c r="C133" s="17">
+      <c r="C133" s="17" t="str">
         <f ca="1">IF(B133="","",IF(OR(TRIM(Q133)="En curso",TRIM(Q133)="En proceso de ingreso"),TODAY()-B133,"Cerrada"))</f>
-        <v>65</v>
+        <v>Cerrada</v>
       </c>
       <c r="D133" s="8" t="s">
         <v>144</v>
@@ -31953,10 +31974,10 @@
       </c>
       <c r="P133" s="8"/>
       <c r="Q133" s="8" t="s">
-        <v>472</v>
+        <v>51</v>
       </c>
       <c r="R133" s="8" t="s">
-        <v>733</v>
+        <v>52</v>
       </c>
       <c r="S133" s="8"/>
       <c r="T133" s="8" t="s">
@@ -33414,9 +33435,9 @@
       <c r="B150" s="5">
         <v>46059</v>
       </c>
-      <c r="C150" s="17">
+      <c r="C150" s="17" t="str">
         <f ca="1">IF(B150="","",IF(OR(TRIM(Q150)="En curso",TRIM(Q150)="En proceso de ingreso"),TODAY()-B150,"Cerrada"))</f>
-        <v>60</v>
+        <v>Cerrada</v>
       </c>
       <c r="D150" s="8" t="s">
         <v>144</v>
@@ -33448,10 +33469,10 @@
       </c>
       <c r="P150" s="8"/>
       <c r="Q150" s="8" t="s">
-        <v>472</v>
+        <v>51</v>
       </c>
       <c r="R150" s="8" t="s">
-        <v>733</v>
+        <v>52</v>
       </c>
       <c r="S150" s="8"/>
       <c r="T150" s="8" t="s">
@@ -34077,9 +34098,9 @@
       <c r="B157" s="5">
         <v>46064</v>
       </c>
-      <c r="C157" s="17">
+      <c r="C157" s="17" t="str">
         <f ca="1">IF(B157="","",IF(OR(TRIM(Q157)="En curso",TRIM(Q157)="En proceso de ingreso"),TODAY()-B157,"Cerrada"))</f>
-        <v>55</v>
+        <v>Cerrada</v>
       </c>
       <c r="D157" s="8" t="s">
         <v>144</v>
@@ -34113,10 +34134,10 @@
       </c>
       <c r="P157" s="8"/>
       <c r="Q157" s="8" t="s">
-        <v>472</v>
+        <v>51</v>
       </c>
       <c r="R157" s="8" t="s">
-        <v>733</v>
+        <v>52</v>
       </c>
       <c r="S157" s="8"/>
       <c r="T157" s="8" t="s">
@@ -34271,9 +34292,9 @@
       <c r="B159" s="5">
         <v>46065</v>
       </c>
-      <c r="C159" s="17">
+      <c r="C159" s="17" t="str">
         <f ca="1">IF(B159="","",IF(OR(TRIM(Q159)="En curso",TRIM(Q159)="En proceso de ingreso"),TODAY()-B159,"Cerrada"))</f>
-        <v>54</v>
+        <v>Cerrada</v>
       </c>
       <c r="D159" s="8" t="s">
         <v>144</v>
@@ -34307,10 +34328,10 @@
       </c>
       <c r="P159" s="8"/>
       <c r="Q159" s="8" t="s">
-        <v>472</v>
+        <v>51</v>
       </c>
       <c r="R159" s="8" t="s">
-        <v>733</v>
+        <v>52</v>
       </c>
       <c r="S159" s="8"/>
       <c r="T159" s="8" t="s">
@@ -34499,10 +34520,10 @@
       </c>
       <c r="P161" s="8"/>
       <c r="Q161" s="8" t="s">
-        <v>472</v>
+        <v>136</v>
       </c>
       <c r="R161" s="8" t="s">
-        <v>733</v>
+        <v>929</v>
       </c>
       <c r="S161" s="8"/>
       <c r="T161" s="8" t="s">
@@ -34516,7 +34537,7 @@
       </c>
       <c r="W161" s="8"/>
       <c r="X161" s="8" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="Y161" s="8"/>
       <c r="Z161" s="8" t="s">
@@ -34525,22 +34546,16 @@
       <c r="AA161" s="8"/>
       <c r="AB161" s="8"/>
       <c r="AC161" s="8" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="AD161" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="AE161" s="5">
-        <v>46104</v>
-      </c>
-      <c r="AF161" s="5">
-        <v>46120</v>
-      </c>
+      <c r="AE161" s="5"/>
+      <c r="AF161" s="5"/>
       <c r="AG161" s="5"/>
       <c r="AH161" s="8"/>
-      <c r="AI161" s="8" t="s">
-        <v>931</v>
-      </c>
+      <c r="AI161" s="8"/>
       <c r="AJ161" s="8" t="s">
         <v>818</v>
       </c>
@@ -34554,12 +34569,12 @@
         <v>43</v>
       </c>
       <c r="AN161" s="8" t="s">
-        <v>698</v>
+        <v>932</v>
       </c>
     </row>
     <row r="162" spans="1:40" ht="28.5">
       <c r="A162" s="7" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B162" s="5">
         <v>46067</v>
@@ -34596,7 +34611,7 @@
         <v>653</v>
       </c>
       <c r="O162" s="8" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="P162" s="8"/>
       <c r="Q162" s="8" t="s">
@@ -34617,7 +34632,7 @@
       </c>
       <c r="W162" s="8"/>
       <c r="X162" s="8" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="Y162" s="8"/>
       <c r="Z162" s="8" t="s">
@@ -34626,7 +34641,7 @@
       <c r="AA162" s="8"/>
       <c r="AB162" s="8"/>
       <c r="AC162" s="8" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="AD162" s="8" t="s">
         <v>657</v>
@@ -34640,7 +34655,7 @@
       <c r="AG162" s="5"/>
       <c r="AH162" s="8"/>
       <c r="AI162" s="8" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="AJ162" s="8" t="s">
         <v>659</v>
@@ -34656,7 +34671,7 @@
     </row>
     <row r="163" spans="1:40">
       <c r="A163" s="7" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B163" s="5">
         <v>46068</v>
@@ -34737,7 +34752,7 @@
     </row>
     <row r="164" spans="1:40" ht="28.5">
       <c r="A164" s="7" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B164" s="5">
         <v>46068</v>
@@ -34793,7 +34808,7 @@
       </c>
       <c r="W164" s="8"/>
       <c r="X164" s="8" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="Y164" s="8"/>
       <c r="Z164" s="8" t="s">
@@ -34816,7 +34831,7 @@
       <c r="AG164" s="5"/>
       <c r="AH164" s="8"/>
       <c r="AI164" s="8" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="AJ164" s="8" t="s">
         <v>423</v>
@@ -34834,7 +34849,7 @@
     </row>
     <row r="165" spans="1:40" ht="28.5">
       <c r="A165" s="7" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B165" s="5">
         <v>46068</v>
@@ -34890,7 +34905,7 @@
       </c>
       <c r="W165" s="8"/>
       <c r="X165" s="8" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="Y165" s="8"/>
       <c r="Z165" s="8" t="s">
@@ -34913,7 +34928,7 @@
       <c r="AG165" s="5"/>
       <c r="AH165" s="8"/>
       <c r="AI165" s="8" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="AJ165" s="8" t="s">
         <v>423</v>
@@ -34931,7 +34946,7 @@
     </row>
     <row r="166" spans="1:40">
       <c r="A166" s="7" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B166" s="5">
         <v>46068</v>
@@ -34987,7 +35002,7 @@
       </c>
       <c r="W166" s="8"/>
       <c r="X166" s="8" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="Y166" s="8"/>
       <c r="Z166" s="8" t="s">
@@ -34996,7 +35011,7 @@
       <c r="AA166" s="8"/>
       <c r="AB166" s="8"/>
       <c r="AC166" s="8" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="AD166" s="8" t="s">
         <v>154</v>
@@ -35014,7 +35029,7 @@
     </row>
     <row r="167" spans="1:40" ht="28.5">
       <c r="A167" s="7" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B167" s="5">
         <v>46069</v>
@@ -35072,7 +35087,7 @@
       </c>
       <c r="W167" s="8"/>
       <c r="X167" s="8" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="Y167" s="8"/>
       <c r="Z167" s="8" t="s">
@@ -35095,7 +35110,7 @@
       <c r="AG167" s="5"/>
       <c r="AH167" s="8"/>
       <c r="AI167" s="8" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="AJ167" s="8" t="s">
         <v>518</v>
@@ -35113,7 +35128,7 @@
     </row>
     <row r="168" spans="1:40" ht="28.5">
       <c r="A168" s="7" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B168" s="5">
         <v>46069</v>
@@ -35171,10 +35186,10 @@
       </c>
       <c r="W168" s="8"/>
       <c r="X168" s="8" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="Y168" s="8" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="Z168" s="8" t="s">
         <v>173</v>
@@ -35182,7 +35197,7 @@
       <c r="AA168" s="8"/>
       <c r="AB168" s="8"/>
       <c r="AC168" s="8" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="AD168" s="8" t="s">
         <v>657</v>
@@ -35198,10 +35213,10 @@
       </c>
       <c r="AH168" s="8"/>
       <c r="AI168" s="8" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="AJ168" s="8" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="AK168" s="8" t="s">
         <v>60</v>
@@ -35214,7 +35229,7 @@
     </row>
     <row r="169" spans="1:40">
       <c r="A169" s="7" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B169" s="5">
         <v>46071</v>
@@ -35236,7 +35251,7 @@
         <v>44</v>
       </c>
       <c r="J169" s="8" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="K169" s="8" t="s">
         <v>121</v>
@@ -35268,7 +35283,7 @@
       </c>
       <c r="W169" s="8"/>
       <c r="X169" s="8" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="Y169" s="8"/>
       <c r="Z169" s="8" t="s">
@@ -35277,10 +35292,10 @@
       <c r="AA169" s="8"/>
       <c r="AB169" s="8"/>
       <c r="AC169" s="8" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="AD169" s="8" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="AE169" s="5">
         <v>46072</v>
@@ -35291,7 +35306,7 @@
       <c r="AG169" s="5"/>
       <c r="AH169" s="8"/>
       <c r="AI169" s="8" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="AJ169" s="8" t="s">
         <v>546</v>
@@ -35306,12 +35321,12 @@
         <v>76</v>
       </c>
       <c r="AN169" s="8" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="170" spans="1:40" ht="43.5">
       <c r="A170" s="7" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B170" s="5">
         <v>46071</v>
@@ -35343,10 +35358,10 @@
         <v>238</v>
       </c>
       <c r="N170" s="8" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="O170" s="8" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="P170" s="8"/>
       <c r="Q170" s="8" t="s">
@@ -35389,13 +35404,13 @@
         <v>72</v>
       </c>
       <c r="AH170" s="8" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="AI170" s="8" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="AJ170" s="8" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="AK170" s="8" t="s">
         <v>115</v>
@@ -35407,12 +35422,12 @@
         <v>76</v>
       </c>
       <c r="AN170" s="8" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="171" spans="1:40" ht="28.5">
       <c r="A171" s="7" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B171" s="5">
         <v>46071</v>
@@ -35438,13 +35453,13 @@
         <v>293</v>
       </c>
       <c r="L171" s="8" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="M171" s="8" t="s">
         <v>170</v>
       </c>
       <c r="N171" s="8" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="O171" s="8" t="s">
         <v>296</v>
@@ -35466,7 +35481,7 @@
       </c>
       <c r="W171" s="8"/>
       <c r="X171" s="8" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="Y171" s="8"/>
       <c r="Z171" s="8" t="s">
@@ -35475,7 +35490,7 @@
       <c r="AA171" s="8"/>
       <c r="AB171" s="8"/>
       <c r="AC171" s="8" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="AD171" s="8" t="s">
         <v>154</v>
@@ -35487,7 +35502,7 @@
       <c r="AG171" s="5"/>
       <c r="AH171" s="8"/>
       <c r="AI171" s="8" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="AJ171" s="8" t="s">
         <v>919</v>
@@ -35503,7 +35518,7 @@
     </row>
     <row r="172" spans="1:40">
       <c r="A172" s="7" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B172" s="5">
         <v>46071</v>
@@ -35535,10 +35550,10 @@
         <v>213</v>
       </c>
       <c r="N172" s="8" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="O172" s="8" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="P172" s="8"/>
       <c r="Q172" s="8" t="s">
@@ -35555,7 +35570,7 @@
       </c>
       <c r="W172" s="8"/>
       <c r="X172" s="8" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="Y172" s="8"/>
       <c r="Z172" s="8" t="s">
@@ -35578,7 +35593,7 @@
     </row>
     <row r="173" spans="1:40">
       <c r="A173" s="7" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B173" s="5">
         <v>46071</v>
@@ -35620,7 +35635,7 @@
         <v>136</v>
       </c>
       <c r="R173" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S173" s="8"/>
       <c r="T173" s="8" t="s">
@@ -35632,11 +35647,15 @@
       <c r="V173" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="W173" s="8"/>
+      <c r="W173" s="8">
+        <v>169836</v>
+      </c>
       <c r="X173" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="Y173" s="8"/>
+      <c r="Y173" s="8" t="s">
+        <v>982</v>
+      </c>
       <c r="Z173" s="8" t="s">
         <v>55</v>
       </c>
@@ -35657,7 +35676,7 @@
     </row>
     <row r="174" spans="1:40">
       <c r="A174" s="7" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B174" s="5">
         <v>46071</v>
@@ -35699,7 +35718,7 @@
         <v>136</v>
       </c>
       <c r="R174" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S174" s="8"/>
       <c r="T174" s="8" t="s">
@@ -35711,11 +35730,15 @@
       <c r="V174" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="W174" s="8"/>
+      <c r="W174" s="8">
+        <v>1088</v>
+      </c>
       <c r="X174" s="8" t="s">
-        <v>982</v>
-      </c>
-      <c r="Y174" s="8"/>
+        <v>984</v>
+      </c>
+      <c r="Y174" s="8" t="s">
+        <v>275</v>
+      </c>
       <c r="Z174" s="8" t="s">
         <v>55</v>
       </c>
@@ -35736,7 +35759,7 @@
     </row>
     <row r="175" spans="1:40">
       <c r="A175" s="7" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B175" s="5">
         <v>46071</v>
@@ -35778,7 +35801,7 @@
         <v>136</v>
       </c>
       <c r="R175" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S175" s="8"/>
       <c r="T175" s="8" t="s">
@@ -35813,7 +35836,7 @@
     </row>
     <row r="176" spans="1:40">
       <c r="A176" s="7" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="B176" s="5">
         <v>46071</v>
@@ -35855,7 +35878,7 @@
         <v>136</v>
       </c>
       <c r="R176" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S176" s="8"/>
       <c r="T176" s="8" t="s">
@@ -35890,7 +35913,7 @@
     </row>
     <row r="177" spans="1:40">
       <c r="A177" s="7" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="B177" s="5">
         <v>46071</v>
@@ -35932,7 +35955,7 @@
         <v>136</v>
       </c>
       <c r="R177" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S177" s="8"/>
       <c r="T177" s="8" t="s">
@@ -35967,7 +35990,7 @@
     </row>
     <row r="178" spans="1:40">
       <c r="A178" s="7" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="B178" s="5">
         <v>46073</v>
@@ -36009,7 +36032,7 @@
         <v>136</v>
       </c>
       <c r="R178" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S178" s="8"/>
       <c r="T178" s="8" t="s">
@@ -36021,11 +36044,15 @@
       <c r="V178" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="W178" s="8"/>
+      <c r="W178" s="8">
+        <v>157853</v>
+      </c>
       <c r="X178" s="8" t="s">
-        <v>987</v>
-      </c>
-      <c r="Y178" s="8"/>
+        <v>989</v>
+      </c>
+      <c r="Y178" s="8" t="s">
+        <v>982</v>
+      </c>
       <c r="Z178" s="8" t="s">
         <v>55</v>
       </c>
@@ -36046,7 +36073,7 @@
     </row>
     <row r="179" spans="1:40">
       <c r="A179" s="7" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B179" s="5">
         <v>46077</v>
@@ -36088,7 +36115,7 @@
         <v>136</v>
       </c>
       <c r="R179" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S179" s="8"/>
       <c r="T179" s="8" t="s">
@@ -36100,11 +36127,15 @@
       <c r="V179" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="W179" s="8"/>
+      <c r="W179" s="8">
+        <v>1002</v>
+      </c>
       <c r="X179" s="8" t="s">
-        <v>989</v>
-      </c>
-      <c r="Y179" s="8"/>
+        <v>991</v>
+      </c>
+      <c r="Y179" s="8" t="s">
+        <v>982</v>
+      </c>
       <c r="Z179" s="8" t="s">
         <v>55</v>
       </c>
@@ -36125,7 +36156,7 @@
     </row>
     <row r="180" spans="1:40">
       <c r="A180" s="7" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="B180" s="5">
         <v>46079</v>
@@ -36167,7 +36198,7 @@
         <v>136</v>
       </c>
       <c r="R180" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S180" s="8"/>
       <c r="T180" s="8" t="s">
@@ -36179,11 +36210,15 @@
       <c r="V180" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="W180" s="8"/>
+      <c r="W180" s="8">
+        <v>154670</v>
+      </c>
       <c r="X180" s="8" t="s">
-        <v>991</v>
-      </c>
-      <c r="Y180" s="8"/>
+        <v>993</v>
+      </c>
+      <c r="Y180" s="8" t="s">
+        <v>982</v>
+      </c>
       <c r="Z180" s="8" t="s">
         <v>55</v>
       </c>
@@ -36204,7 +36239,7 @@
     </row>
     <row r="181" spans="1:40">
       <c r="A181" s="7" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="B181" s="5">
         <v>46071</v>
@@ -36226,7 +36261,7 @@
         <v>145</v>
       </c>
       <c r="J181" s="8" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="K181" s="13" t="s">
         <v>47</v>
@@ -36238,10 +36273,10 @@
         <v>469</v>
       </c>
       <c r="N181" s="8" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="O181" s="8" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="P181" s="8"/>
       <c r="Q181" s="8" t="s">
@@ -36262,7 +36297,7 @@
       </c>
       <c r="W181" s="8"/>
       <c r="X181" s="8" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="Y181" s="8"/>
       <c r="Z181" s="8" t="s">
@@ -36287,10 +36322,10 @@
         <v>752</v>
       </c>
       <c r="AI181" s="8" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="AJ181" s="8" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="AK181" s="8" t="s">
         <v>115</v>
@@ -36303,7 +36338,7 @@
     </row>
     <row r="182" spans="1:40" ht="28.5">
       <c r="A182" s="7" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B182" s="5">
         <v>46071</v>
@@ -36335,7 +36370,7 @@
         <v>170</v>
       </c>
       <c r="N182" s="8" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="O182" s="8" t="s">
         <v>796</v>
@@ -36359,7 +36394,7 @@
       </c>
       <c r="W182" s="8"/>
       <c r="X182" s="8" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="Y182" s="8"/>
       <c r="Z182" s="8" t="s">
@@ -36368,7 +36403,7 @@
       <c r="AA182" s="8"/>
       <c r="AB182" s="8"/>
       <c r="AC182" s="8" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="AD182" s="8" t="s">
         <v>190</v>
@@ -36382,10 +36417,10 @@
       </c>
       <c r="AH182" s="8"/>
       <c r="AI182" s="8" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="AJ182" s="8" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="AK182" s="8" t="s">
         <v>801</v>
@@ -36397,12 +36432,12 @@
         <v>76</v>
       </c>
       <c r="AN182" s="8" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="183" spans="1:40" ht="28.5">
       <c r="A183" s="7" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="B183" s="5">
         <v>46052</v>
@@ -36436,7 +36471,7 @@
         <v>107</v>
       </c>
       <c r="N183" s="8" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="O183" s="8" t="s">
         <v>202</v>
@@ -36460,7 +36495,7 @@
       </c>
       <c r="W183" s="8"/>
       <c r="X183" s="8" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="Y183" s="8"/>
       <c r="Z183" s="8" t="s">
@@ -36469,7 +36504,7 @@
       <c r="AA183" s="8"/>
       <c r="AB183" s="8"/>
       <c r="AC183" s="8" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="AD183" s="8" t="s">
         <v>154</v>
@@ -36480,7 +36515,7 @@
       <c r="AH183" s="8"/>
       <c r="AI183" s="8"/>
       <c r="AJ183" s="8" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="AK183" s="8" t="s">
         <v>207</v>
@@ -36490,12 +36525,12 @@
       </c>
       <c r="AM183" s="8"/>
       <c r="AN183" s="8" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="184" spans="1:40" ht="28.5">
       <c r="A184" s="7" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="B184" s="5">
         <v>46072</v>
@@ -36529,7 +36564,7 @@
         <v>107</v>
       </c>
       <c r="N184" s="8" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="O184" s="8" t="s">
         <v>796</v>
@@ -36553,7 +36588,7 @@
       </c>
       <c r="W184" s="8"/>
       <c r="X184" s="8" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="Y184" s="8"/>
       <c r="Z184" s="8" t="s">
@@ -36562,7 +36597,7 @@
       <c r="AA184" s="8"/>
       <c r="AB184" s="8"/>
       <c r="AC184" s="8" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="AD184" s="8" t="s">
         <v>190</v>
@@ -36580,10 +36615,10 @@
         <v>752</v>
       </c>
       <c r="AI184" s="8" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="AJ184" s="8" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="AK184" s="8" t="s">
         <v>801</v>
@@ -36595,12 +36630,12 @@
         <v>76</v>
       </c>
       <c r="AN184" s="8" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="185" spans="1:40">
       <c r="A185" s="7" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B185" s="5">
         <v>46073</v>
@@ -36613,7 +36648,7 @@
         <v>467</v>
       </c>
       <c r="E185" s="8" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="F185" s="8" t="s">
         <v>43</v>
@@ -36627,19 +36662,19 @@
       </c>
       <c r="J185" s="8"/>
       <c r="K185" s="8" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="L185" s="8" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="M185" s="8" t="s">
         <v>238</v>
       </c>
       <c r="N185" s="8" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="O185" s="8" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="P185" s="8"/>
       <c r="Q185" s="8" t="s">
@@ -36677,7 +36712,7 @@
     </row>
     <row r="186" spans="1:40">
       <c r="A186" s="7" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="B186" s="5">
         <v>46073</v>
@@ -36704,19 +36739,19 @@
       </c>
       <c r="J186" s="8"/>
       <c r="K186" s="8" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="L186" s="8" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="M186" s="8" t="s">
         <v>107</v>
       </c>
       <c r="N186" s="8" t="s">
+        <v>1027</v>
+      </c>
+      <c r="O186" s="8" t="s">
         <v>1025</v>
-      </c>
-      <c r="O186" s="8" t="s">
-        <v>1023</v>
       </c>
       <c r="P186" s="8"/>
       <c r="Q186" s="8" t="s">
@@ -36733,7 +36768,7 @@
       </c>
       <c r="W186" s="8"/>
       <c r="X186" s="8" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="Y186" s="8"/>
       <c r="Z186" s="8" t="s">
@@ -36756,7 +36791,7 @@
     </row>
     <row r="187" spans="1:40" ht="28.5">
       <c r="A187" s="7" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="B187" s="5">
         <v>46076</v>
@@ -36793,7 +36828,7 @@
         <v>653</v>
       </c>
       <c r="O187" s="8" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="P187" s="8"/>
       <c r="Q187" s="8" t="s">
@@ -36814,7 +36849,7 @@
       </c>
       <c r="W187" s="8"/>
       <c r="X187" s="8" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="Y187" s="8"/>
       <c r="Z187" s="8" t="s">
@@ -36823,7 +36858,7 @@
       <c r="AA187" s="8"/>
       <c r="AB187" s="8"/>
       <c r="AC187" s="8" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="AD187" s="8" t="s">
         <v>657</v>
@@ -36837,7 +36872,7 @@
       <c r="AG187" s="5"/>
       <c r="AH187" s="8"/>
       <c r="AI187" s="8" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="AJ187" s="8" t="s">
         <v>659</v>
@@ -36855,7 +36890,7 @@
     </row>
     <row r="188" spans="1:40" ht="28.5">
       <c r="A188" s="7" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="B188" s="5">
         <v>46076</v>
@@ -36892,7 +36927,7 @@
         <v>653</v>
       </c>
       <c r="O188" s="8" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="P188" s="8"/>
       <c r="Q188" s="8" t="s">
@@ -36913,7 +36948,7 @@
       </c>
       <c r="W188" s="8"/>
       <c r="X188" s="8" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="Y188" s="8"/>
       <c r="Z188" s="8" t="s">
@@ -36922,7 +36957,7 @@
       <c r="AA188" s="8"/>
       <c r="AB188" s="8"/>
       <c r="AC188" s="8" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="AD188" s="8" t="s">
         <v>657</v>
@@ -36933,7 +36968,7 @@
       <c r="AH188" s="8"/>
       <c r="AI188" s="8"/>
       <c r="AJ188" s="8" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="AK188" s="8" t="s">
         <v>60</v>
@@ -36948,7 +36983,7 @@
     </row>
     <row r="189" spans="1:40" ht="28.5">
       <c r="A189" s="7" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="B189" s="5">
         <v>46076</v>
@@ -37004,7 +37039,7 @@
       </c>
       <c r="W189" s="8"/>
       <c r="X189" s="8" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="Y189" s="8"/>
       <c r="Z189" s="8" t="s">
@@ -37013,7 +37048,7 @@
       <c r="AA189" s="8"/>
       <c r="AB189" s="8"/>
       <c r="AC189" s="8" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="AD189" s="8" t="s">
         <v>154</v>
@@ -37039,7 +37074,7 @@
     </row>
     <row r="190" spans="1:40">
       <c r="A190" s="7" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="B190" s="5">
         <v>46076</v>
@@ -37097,7 +37132,7 @@
       </c>
       <c r="W190" s="8"/>
       <c r="X190" s="8" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="Y190" s="8"/>
       <c r="Z190" s="8" t="s">
@@ -37120,7 +37155,7 @@
     </row>
     <row r="191" spans="1:40">
       <c r="A191" s="7" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B191" s="5">
         <v>46078</v>
@@ -37176,10 +37211,10 @@
       </c>
       <c r="W191" s="8"/>
       <c r="X191" s="8" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="Y191" s="8" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="Z191" s="8" t="s">
         <v>55</v>
@@ -37202,12 +37237,12 @@
       <c r="AL191" s="8"/>
       <c r="AM191" s="8"/>
       <c r="AN191" s="8" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="192" spans="1:40" ht="28.5">
       <c r="A192" s="7" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="B192" s="5">
         <v>46079</v>
@@ -37232,7 +37267,7 @@
       </c>
       <c r="J192" s="8"/>
       <c r="K192" s="8" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="L192" s="8" t="s">
         <v>161</v>
@@ -37241,7 +37276,7 @@
         <v>107</v>
       </c>
       <c r="N192" s="8" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="O192" s="8" t="s">
         <v>715</v>
@@ -37253,7 +37288,7 @@
         <v>136</v>
       </c>
       <c r="R192" s="8" t="s">
-        <v>1047</v>
+        <v>929</v>
       </c>
       <c r="S192" s="8"/>
       <c r="T192" s="8" t="s">
@@ -37285,12 +37320,12 @@
       <c r="AL192" s="8"/>
       <c r="AM192" s="8"/>
       <c r="AN192" s="8" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="193" spans="1:40">
       <c r="A193" s="7" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B193" s="5">
         <v>46079</v>
@@ -37346,10 +37381,10 @@
       </c>
       <c r="W193" s="8"/>
       <c r="X193" s="8" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="Y193" s="8" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="Z193" s="8" t="s">
         <v>55</v>
@@ -37372,12 +37407,12 @@
       <c r="AL193" s="8"/>
       <c r="AM193" s="8"/>
       <c r="AN193" s="8" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="194" spans="1:40" ht="28.5">
       <c r="A194" s="7" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B194" s="5">
         <v>46079</v>
@@ -37414,7 +37449,7 @@
         <v>653</v>
       </c>
       <c r="O194" s="8" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="P194" s="8"/>
       <c r="Q194" s="8" t="s">
@@ -37435,7 +37470,7 @@
       </c>
       <c r="W194" s="8"/>
       <c r="X194" s="8" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="Y194" s="8"/>
       <c r="Z194" s="8" t="s">
@@ -37444,7 +37479,7 @@
       <c r="AA194" s="8"/>
       <c r="AB194" s="8"/>
       <c r="AC194" s="8" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="AD194" s="8" t="s">
         <v>657</v>
@@ -37455,7 +37490,7 @@
       <c r="AH194" s="8"/>
       <c r="AI194" s="8"/>
       <c r="AJ194" s="8" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="AK194" s="8" t="s">
         <v>60</v>
@@ -37470,14 +37505,14 @@
     </row>
     <row r="195" spans="1:40" ht="28.5">
       <c r="A195" s="7" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B195" s="5">
         <v>46080</v>
       </c>
-      <c r="C195" s="17">
+      <c r="C195" s="17" t="str">
         <f ca="1">IF(B195="","",IF(OR(TRIM(Q195)="En curso",TRIM(Q195)="En proceso de ingreso"),TODAY()-B195,"Cerrada"))</f>
-        <v>39</v>
+        <v>Cerrada</v>
       </c>
       <c r="D195" s="8" t="s">
         <v>144</v>
@@ -37511,10 +37546,10 @@
       </c>
       <c r="P195" s="8"/>
       <c r="Q195" s="8" t="s">
-        <v>472</v>
+        <v>51</v>
       </c>
       <c r="R195" s="8" t="s">
-        <v>733</v>
+        <v>52</v>
       </c>
       <c r="S195" s="8"/>
       <c r="T195" s="8" t="s">
@@ -37526,10 +37561,10 @@
       </c>
       <c r="W195" s="8"/>
       <c r="X195" s="8" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="Y195" s="8" t="s">
-        <v>1056</v>
+        <v>982</v>
       </c>
       <c r="Z195" s="8" t="s">
         <v>55</v>
@@ -37603,10 +37638,10 @@
         <v>213</v>
       </c>
       <c r="N196" s="8" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="O196" s="8" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="P196" s="8"/>
       <c r="Q196" s="8" t="s">
@@ -37766,9 +37801,9 @@
       <c r="B198" s="5">
         <v>46083</v>
       </c>
-      <c r="C198" s="17">
+      <c r="C198" s="17" t="str">
         <f ca="1">IF(B198="","",IF(OR(TRIM(Q198)="En curso",TRIM(Q198)="En proceso de ingreso"),TODAY()-B198,"Cerrada"))</f>
-        <v>36</v>
+        <v>Cerrada</v>
       </c>
       <c r="D198" s="8" t="s">
         <v>144</v>
@@ -37802,10 +37837,10 @@
       </c>
       <c r="P198" s="8"/>
       <c r="Q198" s="8" t="s">
-        <v>472</v>
+        <v>51</v>
       </c>
       <c r="R198" s="8" t="s">
-        <v>733</v>
+        <v>52</v>
       </c>
       <c r="S198" s="8"/>
       <c r="T198" s="8" t="s">
@@ -37822,7 +37857,7 @@
         <v>1071</v>
       </c>
       <c r="Y198" s="8" t="s">
-        <v>1056</v>
+        <v>982</v>
       </c>
       <c r="Z198" s="8" t="s">
         <v>55</v>
@@ -37830,7 +37865,7 @@
       <c r="AA198" s="8"/>
       <c r="AB198" s="8"/>
       <c r="AC198" s="8" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="AD198" s="8" t="s">
         <v>154</v>
@@ -37904,7 +37939,7 @@
         <v>136</v>
       </c>
       <c r="R199" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S199" s="8"/>
       <c r="T199" s="8" t="s">
@@ -37916,11 +37951,15 @@
       <c r="V199" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="W199" s="8"/>
+      <c r="W199" s="8">
+        <v>168093</v>
+      </c>
       <c r="X199" s="8" t="s">
         <v>1075</v>
       </c>
-      <c r="Y199" s="8"/>
+      <c r="Y199" s="8" t="s">
+        <v>982</v>
+      </c>
       <c r="Z199" s="8" t="s">
         <v>55</v>
       </c>
@@ -37983,7 +38022,7 @@
         <v>136</v>
       </c>
       <c r="R200" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S200" s="8"/>
       <c r="T200" s="8" t="s">
@@ -38001,7 +38040,9 @@
       <c r="X200" s="8" t="s">
         <v>1077</v>
       </c>
-      <c r="Y200" s="8"/>
+      <c r="Y200" s="8" t="s">
+        <v>982</v>
+      </c>
       <c r="Z200" s="8" t="s">
         <v>55</v>
       </c>
@@ -38064,7 +38105,7 @@
         <v>136</v>
       </c>
       <c r="R201" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S201" s="8"/>
       <c r="T201" s="8" t="s">
@@ -38082,7 +38123,9 @@
       <c r="X201" s="8" t="s">
         <v>1079</v>
       </c>
-      <c r="Y201" s="8"/>
+      <c r="Y201" s="8" t="s">
+        <v>982</v>
+      </c>
       <c r="Z201" s="8" t="s">
         <v>55</v>
       </c>
@@ -38145,7 +38188,7 @@
         <v>136</v>
       </c>
       <c r="R202" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S202" s="8"/>
       <c r="T202" s="8" t="s">
@@ -38163,7 +38206,9 @@
       <c r="X202" s="8" t="s">
         <v>1081</v>
       </c>
-      <c r="Y202" s="8"/>
+      <c r="Y202" s="8" t="s">
+        <v>982</v>
+      </c>
       <c r="Z202" s="8" t="s">
         <v>55</v>
       </c>
@@ -38226,7 +38271,7 @@
         <v>136</v>
       </c>
       <c r="R203" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S203" s="8"/>
       <c r="T203" s="8" t="s">
@@ -38244,7 +38289,9 @@
       <c r="X203" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="Y203" s="8"/>
+      <c r="Y203" s="8" t="s">
+        <v>275</v>
+      </c>
       <c r="Z203" s="8" t="s">
         <v>55</v>
       </c>
@@ -38307,7 +38354,7 @@
         <v>136</v>
       </c>
       <c r="R204" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S204" s="8"/>
       <c r="T204" s="8" t="s">
@@ -38325,7 +38372,9 @@
       <c r="X204" s="8" t="s">
         <v>1085</v>
       </c>
-      <c r="Y204" s="8"/>
+      <c r="Y204" s="8" t="s">
+        <v>982</v>
+      </c>
       <c r="Z204" s="8" t="s">
         <v>55</v>
       </c>
@@ -38380,7 +38429,7 @@
         <v>170</v>
       </c>
       <c r="N205" s="8" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="O205" s="8" t="s">
         <v>796</v>
@@ -38407,7 +38456,7 @@
         <v>1088</v>
       </c>
       <c r="Y205" s="8" t="s">
-        <v>1056</v>
+        <v>982</v>
       </c>
       <c r="Z205" s="8" t="s">
         <v>55</v>
@@ -38448,7 +38497,7 @@
         <v>103</v>
       </c>
       <c r="E206" s="8" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="F206" s="8" t="s">
         <v>43</v>
@@ -38462,7 +38511,7 @@
       </c>
       <c r="J206" s="8"/>
       <c r="K206" s="8" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="L206" s="8" t="s">
         <v>1092</v>
@@ -38581,7 +38630,7 @@
         <v>1101</v>
       </c>
       <c r="Y207" s="8" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="Z207" s="8" t="s">
         <v>173</v>
@@ -38653,7 +38702,7 @@
         <v>136</v>
       </c>
       <c r="R208" s="8" t="s">
-        <v>1047</v>
+        <v>929</v>
       </c>
       <c r="S208" s="8"/>
       <c r="T208" s="8" t="s">
@@ -38745,7 +38794,7 @@
         <v>474</v>
       </c>
       <c r="U209" s="8" t="s">
-        <v>139</v>
+        <v>69</v>
       </c>
       <c r="V209" s="8" t="s">
         <v>53</v>
@@ -38873,7 +38922,7 @@
         <v>467</v>
       </c>
       <c r="E211" s="8" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="F211" s="8" t="s">
         <v>43</v>
@@ -38892,7 +38941,7 @@
         <v>107</v>
       </c>
       <c r="N211" s="8" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="O211" s="8" t="s">
         <v>1118</v>
@@ -38919,7 +38968,7 @@
         <v>1120</v>
       </c>
       <c r="Y211" s="8" t="s">
-        <v>1056</v>
+        <v>982</v>
       </c>
       <c r="Z211" s="11" t="s">
         <v>55</v>
@@ -39176,7 +39225,7 @@
         <v>1130</v>
       </c>
       <c r="Y214" s="8" t="s">
-        <v>1056</v>
+        <v>982</v>
       </c>
       <c r="Z214" s="11" t="s">
         <v>55</v>
@@ -39265,7 +39314,7 @@
         <v>1132</v>
       </c>
       <c r="Y215" s="8" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="Z215" s="11" t="s">
         <v>173</v>
@@ -39330,7 +39379,7 @@
         <v>653</v>
       </c>
       <c r="O216" s="8" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="P216" s="8"/>
       <c r="Q216" s="8" t="s">
@@ -39354,7 +39403,7 @@
         <v>1135</v>
       </c>
       <c r="Y216" s="8" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="Z216" s="11" t="s">
         <v>173</v>
@@ -39504,7 +39553,7 @@
         <v>653</v>
       </c>
       <c r="O218" s="8" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="P218" s="8"/>
       <c r="Q218" s="8" t="s">
@@ -39528,7 +39577,7 @@
         <v>1140</v>
       </c>
       <c r="Y218" s="8" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="Z218" s="11" t="s">
         <v>173</v>
@@ -39547,7 +39596,7 @@
       <c r="AH218" s="8"/>
       <c r="AI218" s="8"/>
       <c r="AJ218" s="8" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="AK218" s="8" t="s">
         <v>60</v>
@@ -39601,7 +39650,7 @@
         <v>653</v>
       </c>
       <c r="O219" s="8" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="P219" s="8"/>
       <c r="Q219" s="8" t="s">
@@ -39652,7 +39701,7 @@
         <v>1147</v>
       </c>
       <c r="AJ219" s="8" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="AK219" s="8" t="s">
         <v>60</v>
@@ -39704,7 +39753,7 @@
         <v>653</v>
       </c>
       <c r="O220" s="8" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="P220" s="8"/>
       <c r="Q220" s="8" t="s">
@@ -39807,7 +39856,7 @@
         <v>653</v>
       </c>
       <c r="O221" s="8" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="P221" s="8"/>
       <c r="Q221" s="8" t="s">
@@ -39829,7 +39878,7 @@
         <v>1154</v>
       </c>
       <c r="Y221" s="8" t="s">
-        <v>1056</v>
+        <v>982</v>
       </c>
       <c r="Z221" s="11" t="s">
         <v>55</v>
@@ -40351,7 +40400,7 @@
         <v>1177</v>
       </c>
       <c r="Y227" s="8" t="s">
-        <v>1056</v>
+        <v>982</v>
       </c>
       <c r="Z227" s="11" t="s">
         <v>55</v>
@@ -40445,22 +40494,26 @@
       <c r="AD228" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="AE228" s="8"/>
+      <c r="AE228" s="5"/>
       <c r="AF228" s="8"/>
       <c r="AG228" s="5"/>
       <c r="AH228" s="8"/>
-      <c r="AI228" s="8" t="s">
+      <c r="AI228" s="8"/>
+      <c r="AJ228" s="8"/>
+      <c r="AK228" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="AL228" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM228" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN228" s="8"/>
+    </row>
+    <row r="229" spans="1:40" ht="28.5">
+      <c r="A229" s="7" t="s">
         <v>1185</v>
-      </c>
-      <c r="AJ228" s="8"/>
-      <c r="AK228" s="8"/>
-      <c r="AL228" s="8"/>
-      <c r="AM228" s="8"/>
-      <c r="AN228" s="8"/>
-    </row>
-    <row r="229" spans="1:40">
-      <c r="A229" s="7" t="s">
-        <v>1186</v>
       </c>
       <c r="B229" s="5">
         <v>46098</v>
@@ -40502,7 +40555,7 @@
         <v>136</v>
       </c>
       <c r="R229" s="8" t="s">
-        <v>1047</v>
+        <v>929</v>
       </c>
       <c r="S229" s="8"/>
       <c r="T229" s="8"/>
@@ -40514,7 +40567,7 @@
       </c>
       <c r="W229" s="8"/>
       <c r="X229" s="8" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="Y229" s="8" t="s">
         <v>275</v>
@@ -40525,22 +40578,32 @@
       <c r="AA229" s="8"/>
       <c r="AB229" s="8"/>
       <c r="AC229" s="8" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="AD229" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="AE229" s="8"/>
+      <c r="AE229" s="5">
+        <v>46119</v>
+      </c>
       <c r="AF229" s="8"/>
       <c r="AG229" s="5"/>
       <c r="AH229" s="8"/>
       <c r="AI229" s="8" t="s">
+        <v>1188</v>
+      </c>
+      <c r="AJ229" s="8" t="s">
         <v>1189</v>
       </c>
-      <c r="AJ229" s="8"/>
-      <c r="AK229" s="8"/>
-      <c r="AL229" s="8"/>
-      <c r="AM229" s="8"/>
+      <c r="AK229" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="AL229" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM229" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="AN229" s="8"/>
     </row>
     <row r="230" spans="1:40" ht="28.5">
@@ -40839,7 +40902,7 @@
         <v>1203</v>
       </c>
       <c r="Y233" s="8" t="s">
-        <v>1056</v>
+        <v>982</v>
       </c>
       <c r="Z233" s="11"/>
       <c r="AA233" s="8"/>
@@ -41228,7 +41291,7 @@
         <v>136</v>
       </c>
       <c r="R238" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S238" s="8"/>
       <c r="T238" s="8"/>
@@ -41264,9 +41327,9 @@
       <c r="B239" s="5">
         <v>46104</v>
       </c>
-      <c r="C239" s="17">
+      <c r="C239" s="17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>Cerrada</v>
       </c>
       <c r="D239" s="8" t="s">
         <v>144</v>
@@ -41298,10 +41361,10 @@
       </c>
       <c r="P239" s="8"/>
       <c r="Q239" s="8" t="s">
-        <v>472</v>
+        <v>51</v>
       </c>
       <c r="R239" s="8" t="s">
-        <v>733</v>
+        <v>52</v>
       </c>
       <c r="S239" s="8"/>
       <c r="T239" s="8"/>
@@ -41314,7 +41377,7 @@
         <v>1223</v>
       </c>
       <c r="Y239" s="8" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="Z239" s="11" t="s">
         <v>152</v>
@@ -41396,7 +41459,7 @@
         <v>136</v>
       </c>
       <c r="R240" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S240" s="8"/>
       <c r="T240" s="8" t="s">
@@ -41423,7 +41486,7 @@
       <c r="AA240" s="8"/>
       <c r="AB240" s="8"/>
       <c r="AC240" s="8" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="AD240" s="8" t="s">
         <v>154</v>
@@ -41439,7 +41502,7 @@
       <c r="AM240" s="8"/>
       <c r="AN240" s="8"/>
     </row>
-    <row r="241" spans="1:40">
+    <row r="241" spans="1:40" ht="28.5">
       <c r="A241" s="7" t="s">
         <v>1229</v>
       </c>
@@ -41486,7 +41549,9 @@
         <v>473</v>
       </c>
       <c r="S241" s="8"/>
-      <c r="T241" s="8"/>
+      <c r="T241" s="8" t="s">
+        <v>750</v>
+      </c>
       <c r="U241" s="8" t="s">
         <v>474</v>
       </c>
@@ -41498,33 +41563,45 @@
         <v>1230</v>
       </c>
       <c r="Y241" s="8" t="s">
-        <v>1056</v>
+        <v>982</v>
       </c>
       <c r="Z241" s="8" t="s">
         <v>55</v>
       </c>
       <c r="AA241" s="8"/>
       <c r="AB241" s="8"/>
-      <c r="AC241" s="8"/>
+      <c r="AC241" s="8" t="s">
+        <v>1231</v>
+      </c>
       <c r="AD241" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="AE241" s="8"/>
+      <c r="AE241" s="5">
+        <v>46119</v>
+      </c>
       <c r="AF241" s="8"/>
       <c r="AG241" s="5"/>
       <c r="AH241" s="8"/>
       <c r="AI241" s="8" t="s">
-        <v>1231</v>
-      </c>
-      <c r="AJ241" s="8"/>
-      <c r="AK241" s="8"/>
-      <c r="AL241" s="8"/>
-      <c r="AM241" s="8"/>
+        <v>1232</v>
+      </c>
+      <c r="AJ241" s="8" t="s">
+        <v>1233</v>
+      </c>
+      <c r="AK241" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="AL241" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM241" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="AN241" s="8"/>
     </row>
     <row r="242" spans="1:40" ht="28.5">
       <c r="A242" s="7" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="B242" s="5">
         <v>46107</v>
@@ -41556,7 +41633,7 @@
         <v>213</v>
       </c>
       <c r="N242" s="8" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="O242" s="8" t="s">
         <v>796</v>
@@ -41580,7 +41657,7 @@
       </c>
       <c r="W242" s="8"/>
       <c r="X242" s="8" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="Y242" s="8"/>
       <c r="Z242" s="11" t="s">
@@ -41589,7 +41666,7 @@
       <c r="AA242" s="8"/>
       <c r="AB242" s="8"/>
       <c r="AC242" s="8" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="AD242" s="8" t="s">
         <v>190</v>
@@ -41607,7 +41684,7 @@
     </row>
     <row r="243" spans="1:40" ht="28.5">
       <c r="A243" s="7" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="B243" s="5">
         <v>46107</v>
@@ -41641,7 +41718,7 @@
         <v>107</v>
       </c>
       <c r="N243" s="8" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="O243" s="8" t="s">
         <v>796</v>
@@ -41668,7 +41745,7 @@
       <c r="AA243" s="8"/>
       <c r="AB243" s="8"/>
       <c r="AC243" s="8" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="AD243" s="8" t="s">
         <v>190</v>
@@ -41688,7 +41765,7 @@
     </row>
     <row r="244" spans="1:40">
       <c r="A244" s="7" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="B244" s="5">
         <v>46108</v>
@@ -41730,7 +41807,7 @@
         <v>136</v>
       </c>
       <c r="R244" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S244" s="8"/>
       <c r="T244" s="8" t="s">
@@ -41751,7 +41828,7 @@
       <c r="AA244" s="8"/>
       <c r="AB244" s="8"/>
       <c r="AC244" s="8" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="AD244" s="8" t="s">
         <v>154</v>
@@ -41769,7 +41846,7 @@
     </row>
     <row r="245" spans="1:40">
       <c r="A245" s="7" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="B245" s="5">
         <v>46108</v>
@@ -41811,7 +41888,7 @@
         <v>136</v>
       </c>
       <c r="R245" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S245" s="8"/>
       <c r="T245" s="8" t="s">
@@ -41825,10 +41902,10 @@
       </c>
       <c r="W245" s="8"/>
       <c r="X245" s="8" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="Y245" s="8" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="Z245" s="11" t="s">
         <v>55</v>
@@ -41836,7 +41913,7 @@
       <c r="AA245" s="8"/>
       <c r="AB245" s="8"/>
       <c r="AC245" s="8" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="AD245" s="8" t="s">
         <v>154</v>
@@ -41854,7 +41931,7 @@
     </row>
     <row r="246" spans="1:40">
       <c r="A246" s="7" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="B246" s="5">
         <v>46108</v>
@@ -41896,7 +41973,7 @@
         <v>136</v>
       </c>
       <c r="R246" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S246" s="8"/>
       <c r="T246" s="8" t="s">
@@ -41910,10 +41987,10 @@
       </c>
       <c r="W246" s="8"/>
       <c r="X246" s="8" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="Y246" s="8" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="Z246" s="11" t="s">
         <v>55</v>
@@ -41921,7 +41998,7 @@
       <c r="AA246" s="8"/>
       <c r="AB246" s="8"/>
       <c r="AC246" s="8" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="AD246" s="8" t="s">
         <v>154</v>
@@ -41939,7 +42016,7 @@
     </row>
     <row r="247" spans="1:40">
       <c r="A247" s="7" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="B247" s="5">
         <v>46108</v>
@@ -41981,7 +42058,7 @@
         <v>136</v>
       </c>
       <c r="R247" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S247" s="8"/>
       <c r="T247" s="8" t="s">
@@ -41995,10 +42072,10 @@
       </c>
       <c r="W247" s="8"/>
       <c r="X247" s="8" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="Y247" s="8" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="Z247" s="11" t="s">
         <v>55</v>
@@ -42006,7 +42083,7 @@
       <c r="AA247" s="8"/>
       <c r="AB247" s="8"/>
       <c r="AC247" s="8" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="AD247" s="8" t="s">
         <v>154</v>
@@ -42024,7 +42101,7 @@
     </row>
     <row r="248" spans="1:40">
       <c r="A248" s="7" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B248" s="5">
         <v>46108</v>
@@ -42066,7 +42143,7 @@
         <v>136</v>
       </c>
       <c r="R248" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S248" s="8"/>
       <c r="T248" s="8" t="s">
@@ -42080,10 +42157,10 @@
       </c>
       <c r="W248" s="8"/>
       <c r="X248" s="8" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="Y248" s="8" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="Z248" s="11" t="s">
         <v>55</v>
@@ -42109,7 +42186,7 @@
     </row>
     <row r="249" spans="1:40">
       <c r="A249" s="7" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="B249" s="5">
         <v>46108</v>
@@ -42151,7 +42228,7 @@
         <v>136</v>
       </c>
       <c r="R249" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S249" s="8"/>
       <c r="T249" s="8" t="s">
@@ -42165,10 +42242,10 @@
       </c>
       <c r="W249" s="8"/>
       <c r="X249" s="8" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="Y249" s="8" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="Z249" s="11" t="s">
         <v>55</v>
@@ -42194,7 +42271,7 @@
     </row>
     <row r="250" spans="1:40" ht="28.5">
       <c r="A250" s="7" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="B250" s="5">
         <v>46111</v>
@@ -42230,7 +42307,7 @@
         <v>223</v>
       </c>
       <c r="N250" s="8" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="O250" s="8" t="s">
         <v>796</v>
@@ -42240,7 +42317,7 @@
         <v>136</v>
       </c>
       <c r="R250" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S250" s="8"/>
       <c r="T250" s="8"/>
@@ -42250,7 +42327,7 @@
       </c>
       <c r="W250" s="8"/>
       <c r="X250" s="8" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="Y250" s="8" t="s">
         <v>275</v>
@@ -42261,7 +42338,7 @@
       <c r="AA250" s="8"/>
       <c r="AB250" s="8"/>
       <c r="AC250" s="8" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="AD250" s="8" t="s">
         <v>190</v>
@@ -42278,12 +42355,12 @@
       <c r="AL250" s="8"/>
       <c r="AM250" s="8"/>
       <c r="AN250" s="8" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="251" spans="1:40" ht="28.5">
       <c r="A251" s="7" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="B251" s="5">
         <v>46111</v>
@@ -42319,7 +42396,7 @@
         <v>223</v>
       </c>
       <c r="N251" s="8" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="O251" s="8" t="s">
         <v>796</v>
@@ -42329,7 +42406,7 @@
         <v>136</v>
       </c>
       <c r="R251" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S251" s="8"/>
       <c r="T251" s="8"/>
@@ -42339,7 +42416,7 @@
       </c>
       <c r="W251" s="8"/>
       <c r="X251" s="8" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="Y251" s="8" t="s">
         <v>275</v>
@@ -42350,7 +42427,7 @@
       <c r="AA251" s="8"/>
       <c r="AB251" s="8"/>
       <c r="AC251" s="8" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="AD251" s="8" t="s">
         <v>190</v>
@@ -42367,12 +42444,12 @@
       <c r="AL251" s="8"/>
       <c r="AM251" s="8"/>
       <c r="AN251" s="8" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="252" spans="1:40" ht="28.5">
       <c r="A252" s="7" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="B252" s="5">
         <v>46111</v>
@@ -42430,10 +42507,10 @@
       </c>
       <c r="W252" s="8"/>
       <c r="X252" s="8" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="Y252" s="8" t="s">
-        <v>1056</v>
+        <v>982</v>
       </c>
       <c r="Z252" s="11" t="s">
         <v>55</v>
@@ -42441,7 +42518,7 @@
       <c r="AA252" s="8"/>
       <c r="AB252" s="8"/>
       <c r="AC252" s="8" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="AD252" s="8" t="s">
         <v>190</v>
@@ -42461,7 +42538,7 @@
     </row>
     <row r="253" spans="1:40" ht="28.5">
       <c r="A253" s="7" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="B253" s="5">
         <v>46112</v>
@@ -42544,10 +42621,10 @@
       </c>
       <c r="AH253" s="8"/>
       <c r="AI253" s="8" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="AJ253" s="8" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="AK253" s="8" t="s">
         <v>207</v>
@@ -42562,7 +42639,7 @@
     </row>
     <row r="254" spans="1:40">
       <c r="A254" s="7" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="B254" s="5">
         <v>46113</v>
@@ -42606,7 +42683,7 @@
         <v>136</v>
       </c>
       <c r="R254" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S254" s="8"/>
       <c r="T254" s="8" t="s">
@@ -42643,7 +42720,7 @@
     </row>
     <row r="255" spans="1:40">
       <c r="A255" s="7" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="B255" s="5">
         <v>46113</v>
@@ -42685,7 +42762,7 @@
         <v>136</v>
       </c>
       <c r="R255" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S255" s="8"/>
       <c r="T255" s="8"/>
@@ -42695,13 +42772,13 @@
       </c>
       <c r="W255" s="8"/>
       <c r="X255" s="8" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="Y255" s="8" t="s">
-        <v>1056</v>
+        <v>982</v>
       </c>
       <c r="Z255" s="11" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="AA255" s="8"/>
       <c r="AB255" s="8"/>
@@ -42720,7 +42797,7 @@
     </row>
     <row r="256" spans="1:40">
       <c r="A256" s="7" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="B256" s="5">
         <v>46113</v>
@@ -42762,7 +42839,7 @@
         <v>136</v>
       </c>
       <c r="R256" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S256" s="8"/>
       <c r="T256" s="8"/>
@@ -42772,13 +42849,13 @@
       </c>
       <c r="W256" s="8"/>
       <c r="X256" s="8" t="s">
+        <v>1266</v>
+      </c>
+      <c r="Y256" s="8" t="s">
+        <v>982</v>
+      </c>
+      <c r="Z256" s="11" t="s">
         <v>1264</v>
-      </c>
-      <c r="Y256" s="8" t="s">
-        <v>1056</v>
-      </c>
-      <c r="Z256" s="11" t="s">
-        <v>1262</v>
       </c>
       <c r="AA256" s="8"/>
       <c r="AB256" s="8"/>
@@ -42797,7 +42874,7 @@
     </row>
     <row r="257" spans="1:40">
       <c r="A257" s="7" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="B257" s="5">
         <v>46111</v>
@@ -42843,7 +42920,7 @@
         <v>136</v>
       </c>
       <c r="R257" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S257" s="8"/>
       <c r="T257" s="8"/>
@@ -42853,7 +42930,7 @@
       </c>
       <c r="W257" s="8"/>
       <c r="X257" s="8" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="Y257" s="8" t="s">
         <v>1228</v>
@@ -42864,7 +42941,7 @@
       <c r="AA257" s="8"/>
       <c r="AB257" s="8"/>
       <c r="AC257" s="8" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="AD257" s="8" t="s">
         <v>175</v>
@@ -42881,12 +42958,12 @@
       <c r="AL257" s="8"/>
       <c r="AM257" s="8"/>
       <c r="AN257" s="8" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="258" spans="1:40">
       <c r="A258" s="7" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="B258" s="5">
         <v>46111</v>
@@ -42932,7 +43009,7 @@
         <v>136</v>
       </c>
       <c r="R258" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S258" s="8"/>
       <c r="T258" s="8"/>
@@ -42942,7 +43019,7 @@
       </c>
       <c r="W258" s="8"/>
       <c r="X258" s="8" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="Y258" s="8" t="s">
         <v>1228</v>
@@ -42953,7 +43030,7 @@
       <c r="AA258" s="8"/>
       <c r="AB258" s="8"/>
       <c r="AC258" s="8" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="AD258" s="8" t="s">
         <v>175</v>
@@ -42970,12 +43047,12 @@
       <c r="AL258" s="8"/>
       <c r="AM258" s="8"/>
       <c r="AN258" s="8" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="259" spans="1:40">
       <c r="A259" s="7" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="B259" s="5">
         <v>46111</v>
@@ -43021,7 +43098,7 @@
         <v>136</v>
       </c>
       <c r="R259" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S259" s="8"/>
       <c r="T259" s="8"/>
@@ -43031,10 +43108,10 @@
       </c>
       <c r="W259" s="8"/>
       <c r="X259" s="8" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="Y259" s="8" t="s">
-        <v>1056</v>
+        <v>982</v>
       </c>
       <c r="Z259" s="11" t="s">
         <v>55</v>
@@ -43042,7 +43119,7 @@
       <c r="AA259" s="8"/>
       <c r="AB259" s="8"/>
       <c r="AC259" s="8" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="AD259" s="8" t="s">
         <v>175</v>
@@ -43059,12 +43136,12 @@
       <c r="AL259" s="8"/>
       <c r="AM259" s="8"/>
       <c r="AN259" s="8" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="260" spans="1:40">
       <c r="A260" s="7" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="B260" s="5">
         <v>46111</v>
@@ -43120,10 +43197,10 @@
       </c>
       <c r="W260" s="8"/>
       <c r="X260" s="8" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="Y260" s="8" t="s">
-        <v>1056</v>
+        <v>982</v>
       </c>
       <c r="Z260" s="11" t="s">
         <v>173</v>
@@ -43131,7 +43208,7 @@
       <c r="AA260" s="8"/>
       <c r="AB260" s="8"/>
       <c r="AC260" s="8" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="AD260" s="8" t="s">
         <v>175</v>
@@ -43148,12 +43225,12 @@
       <c r="AL260" s="8"/>
       <c r="AM260" s="8"/>
       <c r="AN260" s="8" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="261" spans="1:40">
       <c r="A261" s="7" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="B261" s="5">
         <v>46111</v>
@@ -43180,7 +43257,7 @@
       </c>
       <c r="J261" s="8"/>
       <c r="K261" s="8" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="L261" s="8" t="s">
         <v>1181</v>
@@ -43192,14 +43269,14 @@
         <v>214</v>
       </c>
       <c r="O261" s="8" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="P261" s="8"/>
       <c r="Q261" s="8" t="s">
         <v>136</v>
       </c>
       <c r="R261" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="S261" s="8"/>
       <c r="T261" s="8"/>
@@ -43209,10 +43286,10 @@
       </c>
       <c r="W261" s="8"/>
       <c r="X261" s="8" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="Y261" s="8" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="Z261" s="11" t="s">
         <v>173</v>
@@ -43220,7 +43297,7 @@
       <c r="AA261" s="8"/>
       <c r="AB261" s="8"/>
       <c r="AC261" s="8" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="AD261" s="8" t="s">
         <v>175</v>
@@ -43240,7 +43317,7 @@
     </row>
     <row r="262" spans="1:40">
       <c r="A262" s="7" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="B262" s="5">
         <v>46113</v>
@@ -43267,7 +43344,7 @@
       </c>
       <c r="J262" s="8"/>
       <c r="K262" s="8" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="L262" s="8" t="s">
         <v>756</v>
@@ -43276,7 +43353,7 @@
         <v>107</v>
       </c>
       <c r="N262" s="8" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="O262" s="8" t="s">
         <v>743</v>
@@ -43286,7 +43363,7 @@
         <v>136</v>
       </c>
       <c r="R262" s="8" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="S262" s="8"/>
       <c r="T262" s="8"/>
@@ -43297,7 +43374,7 @@
       <c r="W262" s="8"/>
       <c r="X262" s="8"/>
       <c r="Y262" s="8" t="s">
-        <v>1056</v>
+        <v>982</v>
       </c>
       <c r="Z262" s="11" t="s">
         <v>55</v>
@@ -43319,7 +43396,7 @@
     </row>
     <row r="263" spans="1:40">
       <c r="A263" s="7" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="B263" s="5">
         <v>46113</v>
@@ -43346,7 +43423,7 @@
       </c>
       <c r="J263" s="8"/>
       <c r="K263" s="8" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="L263" s="8" t="s">
         <v>756</v>
@@ -43355,17 +43432,17 @@
         <v>213</v>
       </c>
       <c r="N263" s="8" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="O263" s="8" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="P263" s="8"/>
       <c r="Q263" s="8" t="s">
         <v>136</v>
       </c>
       <c r="R263" s="8" t="s">
-        <v>1047</v>
+        <v>929</v>
       </c>
       <c r="S263" s="8"/>
       <c r="T263" s="8"/>
@@ -43375,10 +43452,10 @@
       </c>
       <c r="W263" s="8"/>
       <c r="X263" s="8" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="Y263" s="8" t="s">
-        <v>1056</v>
+        <v>982</v>
       </c>
       <c r="Z263" s="11" t="s">
         <v>55</v>
@@ -43386,7 +43463,7 @@
       <c r="AA263" s="8"/>
       <c r="AB263" s="8"/>
       <c r="AC263" s="8" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="AD263" s="8" t="s">
         <v>175</v>
@@ -43406,7 +43483,7 @@
     </row>
     <row r="264" spans="1:40">
       <c r="A264" s="7" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="B264" s="5">
         <v>46113</v>
@@ -43442,7 +43519,7 @@
         <v>223</v>
       </c>
       <c r="N264" s="8" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="O264" s="8" t="s">
         <v>225</v>
@@ -43462,10 +43539,10 @@
       </c>
       <c r="W264" s="8"/>
       <c r="X264" s="8" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="Y264" s="8" t="s">
-        <v>1056</v>
+        <v>982</v>
       </c>
       <c r="Z264" s="11" t="s">
         <v>55</v>
@@ -43473,7 +43550,7 @@
       <c r="AA264" s="8"/>
       <c r="AB264" s="8"/>
       <c r="AC264" s="8" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="AD264" s="8" t="s">
         <v>175</v>
@@ -43493,7 +43570,7 @@
     </row>
     <row r="265" spans="1:40" ht="28.5">
       <c r="A265" s="7" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="B265" s="5">
         <v>46118</v>
@@ -43517,8 +43594,12 @@
         <v>190</v>
       </c>
       <c r="J265" s="8"/>
-      <c r="K265" s="8"/>
-      <c r="L265" s="8"/>
+      <c r="K265" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="L265" s="8" t="s">
+        <v>249</v>
+      </c>
       <c r="M265" s="8" t="s">
         <v>170</v>
       </c>
@@ -43526,14 +43607,14 @@
         <v>171</v>
       </c>
       <c r="O265" s="8" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="P265" s="8"/>
       <c r="Q265" s="8" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="R265" s="8" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="S265" s="8"/>
       <c r="T265" s="8"/>
@@ -43541,12 +43622,14 @@
       <c r="V265" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="W265" s="8"/>
+      <c r="W265" s="8">
+        <v>11</v>
+      </c>
       <c r="X265" s="8" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="Y265" s="8" t="s">
-        <v>1056</v>
+        <v>982</v>
       </c>
       <c r="Z265" s="11" t="s">
         <v>55</v>
@@ -43554,10 +43637,10 @@
       <c r="AA265" s="8"/>
       <c r="AB265" s="8"/>
       <c r="AC265" s="8" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="AD265" s="8" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="AE265" s="8"/>
       <c r="AF265" s="8"/>
@@ -43574,7 +43657,7 @@
     </row>
     <row r="266" spans="1:40" ht="28.5">
       <c r="A266" s="7" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="B266" s="5">
         <v>46112</v>
@@ -43601,7 +43684,7 @@
         <v>45</v>
       </c>
       <c r="K266" s="8" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="L266" s="8" t="s">
         <v>1123</v>
@@ -43610,10 +43693,10 @@
         <v>170</v>
       </c>
       <c r="N266" s="8" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="O266" s="8" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="P266" s="8"/>
       <c r="Q266" s="8" t="s">
@@ -43630,10 +43713,10 @@
       </c>
       <c r="W266" s="8"/>
       <c r="X266" s="8" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="Y266" s="8" t="s">
-        <v>1056</v>
+        <v>982</v>
       </c>
       <c r="Z266" s="11" t="s">
         <v>55</v>
@@ -43641,7 +43724,7 @@
       <c r="AA266" s="8"/>
       <c r="AB266" s="8"/>
       <c r="AC266" s="8" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="AD266" s="8" t="s">
         <v>112</v>
@@ -43656,10 +43739,10 @@
         <v>889</v>
       </c>
       <c r="AH266" s="8" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="AI266" s="8" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="AJ266" s="8"/>
       <c r="AK266" s="8"/>
@@ -43669,36 +43752,74 @@
     </row>
     <row r="267" spans="1:40">
       <c r="A267" s="7" t="s">
-        <v>1307</v>
-      </c>
-      <c r="B267" s="8"/>
-      <c r="C267" s="17" t="str">
+        <v>1309</v>
+      </c>
+      <c r="B267" s="5">
+        <v>46108</v>
+      </c>
+      <c r="C267" s="17">
         <f ca="1">IF(B267="","",IF(OR(TRIM(Q267)="En curso",TRIM(Q267)="En proceso de ingreso"),TODAY()-B267,"Cerrada"))</f>
-        <v/>
-      </c>
-      <c r="D267" s="8"/>
-      <c r="E267" s="8"/>
-      <c r="F267" s="8"/>
+        <v>11</v>
+      </c>
+      <c r="D267" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E267" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F267" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="G267" s="8"/>
       <c r="H267" s="8"/>
-      <c r="I267" s="8"/>
+      <c r="I267" s="8" t="s">
+        <v>44</v>
+      </c>
       <c r="J267" s="8"/>
-      <c r="K267" s="8"/>
-      <c r="L267" s="8"/>
-      <c r="M267" s="8"/>
-      <c r="N267" s="8"/>
-      <c r="O267" s="8"/>
+      <c r="K267" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L267" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M267" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N267" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="O267" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="P267" s="8"/>
-      <c r="Q267" s="8"/>
-      <c r="R267" s="8"/>
+      <c r="Q267" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="R267" s="8" t="s">
+        <v>981</v>
+      </c>
       <c r="S267" s="8"/>
-      <c r="T267" s="8"/>
-      <c r="U267" s="8"/>
-      <c r="V267" s="8"/>
-      <c r="W267" s="8"/>
-      <c r="X267" s="8"/>
-      <c r="Y267" s="8"/>
-      <c r="Z267" s="11"/>
+      <c r="T267" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="U267" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="V267" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="W267" s="8">
+        <v>170632</v>
+      </c>
+      <c r="X267" s="8" t="s">
+        <v>1310</v>
+      </c>
+      <c r="Y267" s="8" t="s">
+        <v>982</v>
+      </c>
+      <c r="Z267" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="AA267" s="8"/>
       <c r="AB267" s="8"/>
       <c r="AC267" s="8"/>
@@ -43716,36 +43837,74 @@
     </row>
     <row r="268" spans="1:40">
       <c r="A268" s="7" t="s">
-        <v>1308</v>
-      </c>
-      <c r="B268" s="8"/>
-      <c r="C268" s="17" t="str">
+        <v>1311</v>
+      </c>
+      <c r="B268" s="5">
+        <v>46112</v>
+      </c>
+      <c r="C268" s="17">
         <f ca="1">IF(B268="","",IF(OR(TRIM(Q268)="En curso",TRIM(Q268)="En proceso de ingreso"),TODAY()-B268,"Cerrada"))</f>
-        <v/>
-      </c>
-      <c r="D268" s="8"/>
-      <c r="E268" s="8"/>
-      <c r="F268" s="8"/>
+        <v>7</v>
+      </c>
+      <c r="D268" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E268" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F268" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="G268" s="8"/>
       <c r="H268" s="8"/>
-      <c r="I268" s="8"/>
+      <c r="I268" s="8" t="s">
+        <v>44</v>
+      </c>
       <c r="J268" s="8"/>
-      <c r="K268" s="8"/>
-      <c r="L268" s="8"/>
-      <c r="M268" s="8"/>
-      <c r="N268" s="8"/>
-      <c r="O268" s="8"/>
+      <c r="K268" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L268" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M268" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N268" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="O268" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="P268" s="8"/>
-      <c r="Q268" s="8"/>
-      <c r="R268" s="8"/>
+      <c r="Q268" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="R268" s="8" t="s">
+        <v>981</v>
+      </c>
       <c r="S268" s="8"/>
-      <c r="T268" s="8"/>
-      <c r="U268" s="8"/>
-      <c r="V268" s="8"/>
-      <c r="W268" s="8"/>
-      <c r="X268" s="8"/>
-      <c r="Y268" s="8"/>
-      <c r="Z268" s="11"/>
+      <c r="T268" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="U268" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="V268" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="W268" s="8">
+        <v>1094</v>
+      </c>
+      <c r="X268" s="8" t="s">
+        <v>1312</v>
+      </c>
+      <c r="Y268" s="8" t="s">
+        <v>982</v>
+      </c>
+      <c r="Z268" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="AA268" s="8"/>
       <c r="AB268" s="8"/>
       <c r="AC268" s="8"/>
@@ -43763,36 +43922,74 @@
     </row>
     <row r="269" spans="1:40">
       <c r="A269" s="7" t="s">
-        <v>1309</v>
-      </c>
-      <c r="B269" s="8"/>
-      <c r="C269" s="17" t="str">
+        <v>1313</v>
+      </c>
+      <c r="B269" s="5">
+        <v>46097</v>
+      </c>
+      <c r="C269" s="17">
         <f ca="1">IF(B269="","",IF(OR(TRIM(Q269)="En curso",TRIM(Q269)="En proceso de ingreso"),TODAY()-B269,"Cerrada"))</f>
-        <v/>
-      </c>
-      <c r="D269" s="8"/>
-      <c r="E269" s="8"/>
-      <c r="F269" s="8"/>
+        <v>22</v>
+      </c>
+      <c r="D269" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E269" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F269" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="G269" s="8"/>
       <c r="H269" s="8"/>
-      <c r="I269" s="8"/>
+      <c r="I269" s="8" t="s">
+        <v>44</v>
+      </c>
       <c r="J269" s="8"/>
-      <c r="K269" s="8"/>
-      <c r="L269" s="8"/>
-      <c r="M269" s="8"/>
-      <c r="N269" s="8"/>
-      <c r="O269" s="8"/>
+      <c r="K269" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L269" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M269" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N269" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="O269" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="P269" s="8"/>
-      <c r="Q269" s="8"/>
-      <c r="R269" s="8"/>
+      <c r="Q269" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="R269" s="8" t="s">
+        <v>981</v>
+      </c>
       <c r="S269" s="8"/>
-      <c r="T269" s="8"/>
-      <c r="U269" s="8"/>
-      <c r="V269" s="8"/>
-      <c r="W269" s="8"/>
-      <c r="X269" s="8"/>
-      <c r="Y269" s="8"/>
-      <c r="Z269" s="11"/>
+      <c r="T269" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="U269" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="V269" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="W269" s="8">
+        <v>1093</v>
+      </c>
+      <c r="X269" s="8" t="s">
+        <v>1314</v>
+      </c>
+      <c r="Y269" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="Z269" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="AA269" s="8"/>
       <c r="AB269" s="8"/>
       <c r="AC269" s="8"/>
@@ -43810,36 +44007,74 @@
     </row>
     <row r="270" spans="1:40">
       <c r="A270" s="7" t="s">
-        <v>1310</v>
-      </c>
-      <c r="B270" s="8"/>
-      <c r="C270" s="17" t="str">
+        <v>1315</v>
+      </c>
+      <c r="B270" s="5">
+        <v>46097</v>
+      </c>
+      <c r="C270" s="17">
         <f ca="1">IF(B270="","",IF(OR(TRIM(Q270)="En curso",TRIM(Q270)="En proceso de ingreso"),TODAY()-B270,"Cerrada"))</f>
-        <v/>
-      </c>
-      <c r="D270" s="8"/>
-      <c r="E270" s="8"/>
-      <c r="F270" s="8"/>
+        <v>22</v>
+      </c>
+      <c r="D270" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E270" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F270" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="G270" s="8"/>
       <c r="H270" s="8"/>
-      <c r="I270" s="8"/>
+      <c r="I270" s="8" t="s">
+        <v>44</v>
+      </c>
       <c r="J270" s="8"/>
-      <c r="K270" s="8"/>
-      <c r="L270" s="8"/>
-      <c r="M270" s="8"/>
-      <c r="N270" s="8"/>
-      <c r="O270" s="8"/>
+      <c r="K270" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L270" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M270" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N270" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="O270" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="P270" s="8"/>
-      <c r="Q270" s="8"/>
-      <c r="R270" s="8"/>
+      <c r="Q270" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="R270" s="8" t="s">
+        <v>981</v>
+      </c>
       <c r="S270" s="8"/>
-      <c r="T270" s="8"/>
-      <c r="U270" s="8"/>
-      <c r="V270" s="8"/>
-      <c r="W270" s="8"/>
-      <c r="X270" s="8"/>
-      <c r="Y270" s="8"/>
-      <c r="Z270" s="11"/>
+      <c r="T270" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="U270" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="V270" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="W270" s="8">
+        <v>168680</v>
+      </c>
+      <c r="X270" s="8" t="s">
+        <v>1316</v>
+      </c>
+      <c r="Y270" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="Z270" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="AA270" s="8"/>
       <c r="AB270" s="8"/>
       <c r="AC270" s="8"/>
@@ -43857,36 +44092,74 @@
     </row>
     <row r="271" spans="1:40">
       <c r="A271" s="7" t="s">
-        <v>1311</v>
-      </c>
-      <c r="B271" s="8"/>
-      <c r="C271" s="17" t="str">
+        <v>1317</v>
+      </c>
+      <c r="B271" s="5">
+        <v>46097</v>
+      </c>
+      <c r="C271" s="17">
         <f ca="1">IF(B271="","",IF(OR(TRIM(Q271)="En curso",TRIM(Q271)="En proceso de ingreso"),TODAY()-B271,"Cerrada"))</f>
-        <v/>
-      </c>
-      <c r="D271" s="8"/>
-      <c r="E271" s="8"/>
-      <c r="F271" s="8"/>
+        <v>22</v>
+      </c>
+      <c r="D271" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E271" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F271" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="G271" s="8"/>
       <c r="H271" s="8"/>
-      <c r="I271" s="8"/>
+      <c r="I271" s="8" t="s">
+        <v>44</v>
+      </c>
       <c r="J271" s="8"/>
-      <c r="K271" s="8"/>
-      <c r="L271" s="8"/>
-      <c r="M271" s="8"/>
-      <c r="N271" s="8"/>
-      <c r="O271" s="8"/>
+      <c r="K271" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L271" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M271" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N271" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="O271" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="P271" s="8"/>
-      <c r="Q271" s="8"/>
-      <c r="R271" s="8"/>
+      <c r="Q271" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="R271" s="8" t="s">
+        <v>981</v>
+      </c>
       <c r="S271" s="8"/>
-      <c r="T271" s="8"/>
-      <c r="U271" s="8"/>
-      <c r="V271" s="8"/>
-      <c r="W271" s="8"/>
-      <c r="X271" s="8"/>
-      <c r="Y271" s="8"/>
-      <c r="Z271" s="11"/>
+      <c r="T271" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="U271" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="V271" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="W271" s="8">
+        <v>168697</v>
+      </c>
+      <c r="X271" s="8" t="s">
+        <v>1318</v>
+      </c>
+      <c r="Y271" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="Z271" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="AA271" s="8"/>
       <c r="AB271" s="8"/>
       <c r="AC271" s="8"/>
@@ -43904,7 +44177,7 @@
     </row>
     <row r="272" spans="1:40">
       <c r="A272" s="7" t="s">
-        <v>1312</v>
+        <v>1319</v>
       </c>
       <c r="B272" s="8"/>
       <c r="C272" s="17" t="str">
@@ -43951,7 +44224,7 @@
     </row>
     <row r="273" spans="1:40">
       <c r="A273" s="7" t="s">
-        <v>1313</v>
+        <v>1320</v>
       </c>
       <c r="B273" s="8"/>
       <c r="C273" s="17" t="str">
@@ -43998,7 +44271,7 @@
     </row>
     <row r="274" spans="1:40">
       <c r="A274" s="7" t="s">
-        <v>1314</v>
+        <v>1321</v>
       </c>
       <c r="B274" s="8"/>
       <c r="C274" s="17" t="str">
@@ -44045,7 +44318,7 @@
     </row>
     <row r="275" spans="1:40">
       <c r="A275" s="7" t="s">
-        <v>1315</v>
+        <v>1322</v>
       </c>
       <c r="B275" s="8"/>
       <c r="C275" s="17" t="str">
@@ -44092,7 +44365,7 @@
     </row>
     <row r="276" spans="1:40">
       <c r="A276" s="7" t="s">
-        <v>1316</v>
+        <v>1323</v>
       </c>
       <c r="B276" s="8"/>
       <c r="C276" s="17" t="str">
@@ -44139,7 +44412,7 @@
     </row>
     <row r="277" spans="1:40">
       <c r="A277" s="7" t="s">
-        <v>1317</v>
+        <v>1324</v>
       </c>
       <c r="B277" s="8"/>
       <c r="C277" s="17" t="str">
@@ -44186,7 +44459,7 @@
     </row>
     <row r="278" spans="1:40">
       <c r="A278" s="7" t="s">
-        <v>1318</v>
+        <v>1325</v>
       </c>
       <c r="B278" s="8"/>
       <c r="C278" s="17" t="str">
@@ -44233,7 +44506,7 @@
     </row>
     <row r="279" spans="1:40">
       <c r="A279" s="7" t="s">
-        <v>1319</v>
+        <v>1326</v>
       </c>
       <c r="B279" s="8"/>
       <c r="C279" s="17" t="str">
@@ -44280,7 +44553,7 @@
     </row>
     <row r="280" spans="1:40">
       <c r="A280" s="7" t="s">
-        <v>1320</v>
+        <v>1327</v>
       </c>
       <c r="B280" s="8"/>
       <c r="C280" s="17" t="str">
@@ -44327,7 +44600,7 @@
     </row>
     <row r="281" spans="1:40">
       <c r="A281" s="7" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="B281" s="8"/>
       <c r="C281" s="17" t="str">
@@ -44374,7 +44647,7 @@
     </row>
     <row r="282" spans="1:40">
       <c r="A282" s="7" t="s">
-        <v>1322</v>
+        <v>1329</v>
       </c>
       <c r="B282" s="8"/>
       <c r="C282" s="17" t="str">
@@ -44421,7 +44694,7 @@
     </row>
     <row r="283" spans="1:40">
       <c r="A283" s="7" t="s">
-        <v>1323</v>
+        <v>1330</v>
       </c>
       <c r="B283" s="8"/>
       <c r="C283" s="17" t="str">
@@ -44468,7 +44741,7 @@
     </row>
     <row r="284" spans="1:40">
       <c r="A284" s="7" t="s">
-        <v>1324</v>
+        <v>1331</v>
       </c>
       <c r="B284" s="8"/>
       <c r="C284" s="17" t="str">
@@ -44515,7 +44788,7 @@
     </row>
     <row r="285" spans="1:40">
       <c r="A285" s="7" t="s">
-        <v>1325</v>
+        <v>1332</v>
       </c>
       <c r="B285" s="8"/>
       <c r="C285" s="17" t="str">
@@ -44562,7 +44835,7 @@
     </row>
     <row r="286" spans="1:40">
       <c r="A286" s="7" t="s">
-        <v>1326</v>
+        <v>1333</v>
       </c>
       <c r="B286" s="8"/>
       <c r="C286" s="17" t="str">
@@ -44609,7 +44882,7 @@
     </row>
     <row r="287" spans="1:40">
       <c r="A287" s="7" t="s">
-        <v>1327</v>
+        <v>1334</v>
       </c>
       <c r="B287" s="8"/>
       <c r="C287" s="17" t="str">
@@ -44656,7 +44929,7 @@
     </row>
     <row r="288" spans="1:40">
       <c r="A288" s="7" t="s">
-        <v>1328</v>
+        <v>1335</v>
       </c>
       <c r="B288" s="8"/>
       <c r="C288" s="17" t="str">
@@ -44703,7 +44976,7 @@
     </row>
     <row r="289" spans="1:40">
       <c r="A289" s="7" t="s">
-        <v>1329</v>
+        <v>1336</v>
       </c>
       <c r="B289" s="8"/>
       <c r="C289" s="17" t="str">
@@ -44750,7 +45023,7 @@
     </row>
     <row r="290" spans="1:40">
       <c r="A290" s="7" t="s">
-        <v>1330</v>
+        <v>1337</v>
       </c>
       <c r="B290" s="8"/>
       <c r="C290" s="17" t="str">
@@ -44797,7 +45070,7 @@
     </row>
     <row r="291" spans="1:40">
       <c r="A291" s="7" t="s">
-        <v>1331</v>
+        <v>1338</v>
       </c>
       <c r="B291" s="8"/>
       <c r="C291" s="17" t="str">
@@ -44844,7 +45117,7 @@
     </row>
     <row r="292" spans="1:40">
       <c r="A292" s="7" t="s">
-        <v>1332</v>
+        <v>1339</v>
       </c>
       <c r="B292" s="8"/>
       <c r="C292" s="17" t="str">
@@ -44891,7 +45164,7 @@
     </row>
     <row r="293" spans="1:40">
       <c r="A293" s="7" t="s">
-        <v>1333</v>
+        <v>1340</v>
       </c>
       <c r="B293" s="8"/>
       <c r="C293" s="17" t="str">
@@ -44938,7 +45211,7 @@
     </row>
     <row r="294" spans="1:40">
       <c r="A294" s="7" t="s">
-        <v>1334</v>
+        <v>1341</v>
       </c>
       <c r="B294" s="8"/>
       <c r="C294" s="17" t="str">
@@ -44985,7 +45258,7 @@
     </row>
     <row r="295" spans="1:40">
       <c r="A295" s="7" t="s">
-        <v>1335</v>
+        <v>1342</v>
       </c>
       <c r="B295" s="8"/>
       <c r="C295" s="17" t="str">
@@ -45032,7 +45305,7 @@
     </row>
     <row r="296" spans="1:40">
       <c r="A296" s="7" t="s">
-        <v>1336</v>
+        <v>1343</v>
       </c>
       <c r="B296" s="8"/>
       <c r="C296" s="17" t="str">
@@ -45079,7 +45352,7 @@
     </row>
     <row r="297" spans="1:40">
       <c r="A297" s="7" t="s">
-        <v>1337</v>
+        <v>1344</v>
       </c>
       <c r="B297" s="8"/>
       <c r="C297" s="17" t="str">
@@ -45126,7 +45399,7 @@
     </row>
     <row r="298" spans="1:40">
       <c r="A298" s="7" t="s">
-        <v>1338</v>
+        <v>1345</v>
       </c>
       <c r="B298" s="8"/>
       <c r="C298" s="17" t="str">
@@ -45173,7 +45446,7 @@
     </row>
     <row r="299" spans="1:40">
       <c r="A299" s="7" t="s">
-        <v>1339</v>
+        <v>1346</v>
       </c>
       <c r="B299" s="8"/>
       <c r="C299" s="17" t="str">
@@ -45220,7 +45493,7 @@
     </row>
     <row r="300" spans="1:40">
       <c r="A300" s="7" t="s">
-        <v>1340</v>
+        <v>1347</v>
       </c>
       <c r="B300" s="8"/>
       <c r="C300" s="17" t="str">
@@ -45267,7 +45540,7 @@
     </row>
     <row r="301" spans="1:40">
       <c r="A301" s="7" t="s">
-        <v>1341</v>
+        <v>1348</v>
       </c>
       <c r="B301" s="8"/>
       <c r="C301" s="17" t="str">
@@ -45314,7 +45587,7 @@
     </row>
     <row r="302" spans="1:40">
       <c r="A302" s="7" t="s">
-        <v>1342</v>
+        <v>1349</v>
       </c>
       <c r="B302" s="8"/>
       <c r="C302" s="17" t="str">
@@ -45361,7 +45634,7 @@
     </row>
     <row r="303" spans="1:40">
       <c r="A303" s="7" t="s">
-        <v>1343</v>
+        <v>1350</v>
       </c>
       <c r="B303" s="8"/>
       <c r="C303" s="17" t="str">
@@ -45408,7 +45681,7 @@
     </row>
     <row r="304" spans="1:40">
       <c r="A304" s="7" t="s">
-        <v>1344</v>
+        <v>1351</v>
       </c>
       <c r="B304" s="8"/>
       <c r="C304" s="17" t="str">
@@ -45455,7 +45728,7 @@
     </row>
     <row r="305" spans="1:40">
       <c r="A305" s="7" t="s">
-        <v>1345</v>
+        <v>1352</v>
       </c>
       <c r="B305" s="8"/>
       <c r="C305" s="17" t="str">
@@ -45502,7 +45775,7 @@
     </row>
     <row r="306" spans="1:40">
       <c r="A306" s="7" t="s">
-        <v>1346</v>
+        <v>1353</v>
       </c>
       <c r="B306" s="8"/>
       <c r="C306" s="17" t="str">
@@ -45549,7 +45822,7 @@
     </row>
     <row r="307" spans="1:40">
       <c r="A307" s="7" t="s">
-        <v>1347</v>
+        <v>1354</v>
       </c>
       <c r="B307" s="8"/>
       <c r="C307" s="17" t="str">
@@ -45596,7 +45869,7 @@
     </row>
     <row r="308" spans="1:40">
       <c r="A308" s="7" t="s">
-        <v>1348</v>
+        <v>1355</v>
       </c>
       <c r="B308" s="8"/>
       <c r="C308" s="17" t="str">
@@ -45643,7 +45916,7 @@
     </row>
     <row r="309" spans="1:40">
       <c r="A309" s="7" t="s">
-        <v>1349</v>
+        <v>1356</v>
       </c>
       <c r="B309" s="8"/>
       <c r="C309" s="17" t="str">
@@ -45688,8 +45961,10 @@
       <c r="AM309" s="8"/>
       <c r="AN309" s="8"/>
     </row>
+    <row r="310" spans="1:40">
+      <c r="A310" s="7"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN1" xr:uid="{325F248B-5B5A-4EA2-90C8-48DA023AA97A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:AN221">
     <sortCondition ref="B2:B221"/>
   </sortState>
@@ -45718,14 +45993,14 @@
       <formula>LEN(TRIM(G171))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A309">
+  <conditionalFormatting sqref="A2:A310">
     <cfRule type="duplicateValues" dxfId="0" priority="42"/>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL2:AM2 AL207:AM304 F2:G309" xr:uid="{BE1C9EA3-F87F-46EF-B894-6F18EE76B437}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL2:AM2 AL207:AM266 AL269:AM304 F2:G309" xr:uid="{BE1C9EA3-F87F-46EF-B894-6F18EE76B437}">
       <formula1>"Si,No"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W205:W309 W2:W200 H2:H309 AA2:AB309" xr:uid="{419406C0-34B6-447D-A00F-064CE22CD2A6}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W200 AA2:AB309 H2:H309 W205:W309" xr:uid="{419406C0-34B6-447D-A00F-064CE22CD2A6}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG309" xr:uid="{4AB4C081-870E-4D3B-986A-4F3EAA9A398C}">
       <formula1>"Externa,Interna,Mixta"</formula1>
     </dataValidation>
@@ -45734,7 +46009,7 @@
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="24">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="25">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0FD40EAE-D994-4062-A195-B5499C87236C}">
           <x14:formula1>
             <xm:f>Referencias!$A$2:$A$12</xm:f>
@@ -45745,25 +46020,25 @@
           <x14:formula1>
             <xm:f>Referencias!$C$2:$C$27</xm:f>
           </x14:formula1>
-          <xm:sqref>J205:J212 J155 J103:J104 J146 J2:J19 J44 J60 J77 J100:J101 J197:J198 J216:J252 J254:J304</xm:sqref>
+          <xm:sqref>J205:J212 J155 J103:J104 J146 J2:J19 J44 J60 J77 J100:J101 J197:J198 J216:J252 J254:J266 J272:J304</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{07E7D30B-712F-4E59-A9D3-3FD1EF13F438}">
           <x14:formula1>
             <xm:f>Referencias!$D$2:$D$161</xm:f>
           </x14:formula1>
-          <xm:sqref>K2 K197 K174 L205:L206 K193 K198:L198 K24:K25 K37 K46:K47 K50 K53 K55:K57 K61:K62 K66 K68 K70:K71 K74 K82:K86 K100 K104:K105 K107 K109 K118:K119 K122 K133 K140 K149 K151 K153 K161 K163:K167 K191 K205:K240 K242:K251 K255:K304</xm:sqref>
+          <xm:sqref>K2 K197 K174 L205:L206 K193 K198:L198 K24:K25 K37 K46:K47 K50 K53 K55:K57 K61:K62 K66 K68 K70:K71 K74 K82:K86 K100 K104:K105 K107 K109 K118:K119 K122 K133 K140 K149 K151 K153 K161 K163:K167 K191 K205:K240 K242:K251 K272:K304 K255:K264 K266</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1A21BAF7-C587-437A-A923-3F33D1B63032}">
           <x14:formula1>
             <xm:f>Referencias!$G$2:$G$125</xm:f>
           </x14:formula1>
-          <xm:sqref>N50:N51 N163 N124:N130 N2:N13 N104:N105 N116:N117 N114 N45:N47 N244:N247 N53:N54 N191:N193 N37 N63:N67 N222:N224 N71 N74:N75 N24:N25 N82:N83 N110 N161 N108 N112 N121:N122 N148:N149 N151 N60 N22 N135:N139 N198:N207 N170:N171 N153 N155:N158 N17 N145:N146 N308:N309 N213 N175:N188 N32:N33 N88:N101 N42:N43 N77 N28:N29 N196 N215 N232:N240 N253 N255:N256</xm:sqref>
+          <xm:sqref>N50:N51 N163 N124:N130 N2:N13 N104:N105 N116:N117 N114 N45:N47 N244:N247 N53:N54 N191:N193 N37 N63:N67 N222:N224 N71 N74:N75 N24:N25 N82:N83 N110 N161 N108 N112 N121:N122 N148:N149 N151 N60 N22 N135:N139 N198:N207 N170:N171 N153 N155:N158 N17 N145:N146 N308:N309 N213 N175:N188 N32:N33 N88:N101 N42:N43 N77 N28:N29 N196 N215 N232:N240 N253 N255:N256 N267:N271</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1852AFEE-2141-4306-91C9-0D73D82A216C}">
           <x14:formula1>
             <xm:f>Referencias!$I$2:$I$7</xm:f>
           </x14:formula1>
-          <xm:sqref>T196 T134:T137 T160 T163 T168 T186 T208:T214 T183 T250:T304 T2:T131 T241:T243 T216:T239</xm:sqref>
+          <xm:sqref>T196 T134:T137 T160 T163 T168 T186 T208:T214 T183 T216:T239 T2:T131 T241:T243 T250:T266 T272:T304</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5B7ADC06-48EC-4C24-9D01-DE66B6D7E3E0}">
           <x14:formula1>
@@ -45781,13 +46056,13 @@
           <x14:formula1>
             <xm:f>Referencias!$G$2:$G$300</xm:f>
           </x14:formula1>
-          <xm:sqref>N118:N120 N61:N62 N115 N23 N68:N70 N147 N38:N41 N72:N73 N76 N102:N103 N123 N113 N111 N26:N27 N48:N49 N225:N231 N35:N36 N150 N109 N152 N162 N189:N190 N52 N164:N169 N78:N81 N55:N59 N172:N174 N194:N195 N154 N208:N212 N214 N131:N134 N183 N216:N221 N107 N14:N16 N30:N31 N18:N20 N44 N159:N160 N84:N87 N140:N144 N241:N243 N248:N252 N257:N307 N254</xm:sqref>
+          <xm:sqref>N118:N120 N61:N62 N115 N23 N68:N70 N147 N38:N41 N72:N73 N76 N102:N103 N123 N113 N111 N26:N27 N48:N49 N225:N231 N35:N36 N150 N109 N152 N162 N189:N190 N52 N164:N169 N78:N81 N55:N59 N172:N174 N194:N195 N154 N208:N212 N214 N131:N134 N183 N216:N221 N107 N14:N16 N30:N31 N18:N20 N44 N159:N160 N84:N87 N140:N144 N241:N243 N248:N252 N254 N257:N266 N272:N307</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7173E375-7CAA-4B4B-91E4-145119A810C6}">
           <x14:formula1>
             <xm:f>Referencias!$E$2:$E$74</xm:f>
           </x14:formula1>
-          <xm:sqref>L2:L14 L197 L207:L208 L174 L193 K252 L118:L119 L133 L161 L191 L86 L210:L240 L242:L252 L255:L304</xm:sqref>
+          <xm:sqref>L2:L14 L197 L207:L208 L174 L193 K252 L118:L119 L133 L161 L191 L86 L210:L240 L242:L252 L255:L266 L272:L304</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3B81C6F5-57D2-43AF-BBD6-705F972889FA}">
           <x14:formula1>
@@ -45799,7 +46074,7 @@
           <x14:formula1>
             <xm:f>Referencias!$L$2:$L$9</xm:f>
           </x14:formula1>
-          <xm:sqref>Y308 Y194:Y244 Y2:Y190 Y192 Y250:Y305</xm:sqref>
+          <xm:sqref>Y308 Y2:Y190 Y250:Y305 Y192 Y194:Y244</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7EA61090-6BBB-49D3-9636-5A45BF271470}">
           <x14:formula1>
@@ -45811,7 +46086,7 @@
           <x14:formula1>
             <xm:f>Referencias!$F$2:$F$17</xm:f>
           </x14:formula1>
-          <xm:sqref>M68:M72 M195:M196 M55 M133:M134 M207:M209 M124 M41 M152 M187 M25:M29 M111 M52 M212:M215 M223:M231 M198 M76:M91 M150 M17 M140:M144 M43:M49 M37:M38 M57 M217 M100 M159:M168 M32:M34 M115:M119 M170:M172 M97 M147:M148 M66 M19:M23 M60:M64 M113 M189:M191 M155:M157 M185 M103:M109 M128 M121 M239:M252 M257:M308</xm:sqref>
+          <xm:sqref>M68:M72 M195:M196 M55 M133:M134 M207:M209 M124 M41 M152 M187 M25:M29 M111 M52 M212:M215 M223:M231 M198 M76:M91 M150 M17 M140:M144 M43:M49 M37:M38 M57 M217 M100 M159:M168 M32:M34 M115:M119 M170:M172 M97 M147:M148 M66 M19:M23 M60:M64 M113 M189:M191 M155:M157 M185 M103:M109 M128 M121 M239:M252 M257:M266 M272:M308</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BF24E846-9817-4F77-8393-F6F5B6D6915B}">
           <x14:formula1>
@@ -45823,7 +46098,7 @@
           <x14:formula1>
             <xm:f>Referencias!$F$2:$F$50</xm:f>
           </x14:formula1>
-          <xm:sqref>M58 M40 M42 M73 M75 M98:M99 M123 M145 M169 M173:M180 M101:M102 M154 M2:M13 M199:M204</xm:sqref>
+          <xm:sqref>M58 M40 M42 M73 M75 M98:M99 M123 M145 M169 M173:M180 M101:M102 M154 M2:M13 M199:M204 M267:M271</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C7AD649B-3E4C-44AA-9B13-BBE72F115F3B}">
           <x14:formula1>
@@ -45879,6 +46154,12 @@
           </x14:formula1>
           <xm:sqref>Y245:Y249</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{46237520-9963-40E3-9A98-D963FC2B04FA}">
+          <x14:formula1>
+            <xm:f>Referencias!$D$2:$D$300</xm:f>
+          </x14:formula1>
+          <xm:sqref>K265</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -45891,7 +46172,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.28515625" bestFit="1" customWidth="1"/>
@@ -45909,7 +46190,7 @@
         <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>1350</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -45917,7 +46198,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>1351</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -45925,17 +46206,17 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>1350</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>1352</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="20">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -45943,12 +46224,12 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>1350</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="15" t="s">
-        <v>1352</v>
+        <v>1359</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>17</v>
@@ -45965,7 +46246,7 @@
         <v>512</v>
       </c>
       <c r="D13" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="E13" t="s">
         <v>602</v>
@@ -45974,16 +46255,16 @@
         <v>473</v>
       </c>
       <c r="G13" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H13" t="s">
         <v>733</v>
       </c>
       <c r="I13" t="s">
-        <v>1047</v>
+        <v>929</v>
       </c>
       <c r="J13" t="s">
-        <v>1353</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -46032,12 +46313,12 @@
         <v>1</v>
       </c>
       <c r="G15" s="16">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H15" s="16"/>
       <c r="I15" s="16"/>
       <c r="J15" s="16">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -46059,13 +46340,13 @@
       </c>
       <c r="G16" s="16"/>
       <c r="H16" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="16">
         <v>1</v>
       </c>
       <c r="J16" s="16">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -46110,7 +46391,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>1353</v>
+        <v>1360</v>
       </c>
       <c r="B19" s="16">
         <v>7</v>
@@ -46128,16 +46409,16 @@
         <v>7</v>
       </c>
       <c r="G19" s="16">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H19" s="16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I19" s="16">
         <v>4</v>
       </c>
       <c r="J19" s="16">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -46145,7 +46426,7 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>1350</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -46153,7 +46434,7 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>1350</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -46161,7 +46442,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>1352</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -46177,7 +46458,7 @@
         <v>44</v>
       </c>
       <c r="B28" s="16">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -46185,7 +46466,7 @@
         <v>180</v>
       </c>
       <c r="B29" s="16">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -46206,10 +46487,10 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>1353</v>
+        <v>1360</v>
       </c>
       <c r="B32" s="16">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -46217,12 +46498,12 @@
         <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>1351</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="15" t="s">
-        <v>1352</v>
+        <v>1359</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>16</v>
@@ -46239,7 +46520,7 @@
         <v>472</v>
       </c>
       <c r="D40" t="s">
-        <v>1353</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -46261,13 +46542,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="16">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C42" s="16">
         <v>8</v>
       </c>
       <c r="D42" s="16">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -46292,24 +46573,24 @@
         <v>6</v>
       </c>
       <c r="C44" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" s="16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>1353</v>
+        <v>1360</v>
       </c>
       <c r="B45" s="16">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C45" s="16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D45" s="16">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -46317,7 +46598,7 @@
         <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>1351</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -46330,7 +46611,7 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="15" t="s">
-        <v>1352</v>
+        <v>1359</v>
       </c>
       <c r="B51" s="15" t="s">
         <v>16</v>
@@ -46347,7 +46628,7 @@
         <v>472</v>
       </c>
       <c r="D52" t="s">
-        <v>1353</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -46456,7 +46737,7 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>1353</v>
+        <v>1360</v>
       </c>
       <c r="B61" s="16">
         <v>28</v>
@@ -46497,7 +46778,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1354</v>
+        <v>1361</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>9</v>
@@ -46506,16 +46787,16 @@
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1355</v>
+        <v>1362</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1356</v>
+        <v>1363</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1357</v>
+        <v>1364</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>1358</v>
+        <v>1365</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>19</v>
@@ -46524,13 +46805,13 @@
         <v>20</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>1359</v>
+        <v>1366</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1360</v>
+        <v>1367</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1361</v>
+        <v>1368</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>29</v>
@@ -46539,10 +46820,10 @@
         <v>33</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>1362</v>
+        <v>1369</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>1363</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -46565,10 +46846,10 @@
         <v>223</v>
       </c>
       <c r="G2" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="H2" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="I2" t="s">
         <v>474</v>
@@ -46583,10 +46864,10 @@
         <v>275</v>
       </c>
       <c r="M2" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="O2" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="P2" t="s">
         <v>136</v>
@@ -46603,22 +46884,22 @@
         <v>720</v>
       </c>
       <c r="C3" t="s">
-        <v>1364</v>
+        <v>1371</v>
       </c>
       <c r="D3" t="s">
         <v>1169</v>
       </c>
       <c r="E3" t="s">
-        <v>1365</v>
+        <v>1372</v>
       </c>
       <c r="F3" t="s">
         <v>149</v>
       </c>
       <c r="G3" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="H3" t="s">
-        <v>1366</v>
+        <v>1373</v>
       </c>
       <c r="I3" t="s">
         <v>750</v>
@@ -46630,7 +46911,7 @@
         <v>53</v>
       </c>
       <c r="L3" t="s">
-        <v>1056</v>
+        <v>982</v>
       </c>
       <c r="M3" t="s">
         <v>152</v>
@@ -46653,7 +46934,7 @@
         <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>1367</v>
+        <v>1374</v>
       </c>
       <c r="D4" t="s">
         <v>1158</v>
@@ -46665,10 +46946,10 @@
         <v>213</v>
       </c>
       <c r="G4" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="H4" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="I4" t="s">
         <v>68</v>
@@ -46677,13 +46958,13 @@
         <v>69</v>
       </c>
       <c r="L4" t="s">
-        <v>1368</v>
+        <v>1375</v>
       </c>
       <c r="M4" t="s">
         <v>173</v>
       </c>
       <c r="O4" t="s">
-        <v>1369</v>
+        <v>1376</v>
       </c>
       <c r="P4" t="s">
         <v>51</v>
@@ -46703,7 +46984,7 @@
         <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="E5" t="s">
         <v>898</v>
@@ -46715,7 +46996,7 @@
         <v>150</v>
       </c>
       <c r="H5" t="s">
-        <v>1370</v>
+        <v>1377</v>
       </c>
       <c r="I5" t="s">
         <v>1119</v>
@@ -46724,16 +47005,16 @@
         <v>1119</v>
       </c>
       <c r="L5" t="s">
-        <v>1371</v>
+        <v>1378</v>
       </c>
       <c r="O5" t="s">
-        <v>1372</v>
+        <v>1379</v>
       </c>
       <c r="P5" t="s">
         <v>744</v>
       </c>
       <c r="Q5" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -46762,10 +47043,10 @@
         <v>602</v>
       </c>
       <c r="L6" t="s">
-        <v>1373</v>
+        <v>1380</v>
       </c>
       <c r="O6" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="P6" t="s">
         <v>766</v>
@@ -46773,13 +47054,13 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>1374</v>
+        <v>1381</v>
       </c>
       <c r="B7" t="s">
         <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>1375</v>
+        <v>1382</v>
       </c>
       <c r="D7" t="s">
         <v>1110</v>
@@ -46794,7 +47075,7 @@
         <v>49</v>
       </c>
       <c r="H7" t="s">
-        <v>1047</v>
+        <v>929</v>
       </c>
       <c r="L7" t="s">
         <v>1114</v>
@@ -46803,12 +47084,12 @@
         <v>890</v>
       </c>
       <c r="P7" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" t="s">
-        <v>1376</v>
+        <v>1383</v>
       </c>
       <c r="C8" t="s">
         <v>90</v>
@@ -46823,7 +47104,7 @@
         <v>200</v>
       </c>
       <c r="G8" t="s">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="H8" t="s">
         <v>473</v>
@@ -46840,25 +47121,25 @@
         <v>320</v>
       </c>
       <c r="C9" t="s">
-        <v>1378</v>
+        <v>1385</v>
       </c>
       <c r="D9" t="s">
-        <v>1379</v>
+        <v>1386</v>
       </c>
       <c r="E9" t="s">
-        <v>1380</v>
+        <v>1387</v>
       </c>
       <c r="F9" t="s">
         <v>409</v>
       </c>
       <c r="G9" t="s">
-        <v>1381</v>
+        <v>1388</v>
       </c>
       <c r="H9" t="s">
-        <v>1382</v>
+        <v>1389</v>
       </c>
       <c r="L9" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -46866,56 +47147,56 @@
         <v>246</v>
       </c>
       <c r="C10" t="s">
-        <v>1383</v>
+        <v>1390</v>
       </c>
       <c r="D10" t="s">
         <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>1384</v>
+        <v>1391</v>
       </c>
       <c r="F10" t="s">
         <v>48</v>
       </c>
       <c r="G10" t="s">
-        <v>1385</v>
+        <v>1392</v>
       </c>
       <c r="H10" t="s">
-        <v>1386</v>
+        <v>1393</v>
       </c>
       <c r="L10" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="C11" t="s">
-        <v>1387</v>
+        <v>1394</v>
       </c>
       <c r="D11" t="s">
-        <v>1388</v>
+        <v>1395</v>
       </c>
       <c r="E11" t="s">
-        <v>1389</v>
+        <v>1396</v>
       </c>
       <c r="F11" t="s">
         <v>469</v>
       </c>
       <c r="G11" t="s">
-        <v>1390</v>
+        <v>1397</v>
       </c>
       <c r="H11" t="s">
-        <v>1391</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="C12" t="s">
-        <v>1392</v>
+        <v>1399</v>
       </c>
       <c r="D12" t="s">
         <v>1180</v>
       </c>
       <c r="E12" t="s">
-        <v>1393</v>
+        <v>1400</v>
       </c>
       <c r="F12" t="s">
         <v>283</v>
@@ -46929,19 +47210,19 @@
     </row>
     <row r="13" spans="1:17">
       <c r="C13" t="s">
-        <v>1394</v>
+        <v>1401</v>
       </c>
       <c r="D13" t="s">
-        <v>1395</v>
+        <v>1402</v>
       </c>
       <c r="E13" t="s">
-        <v>1396</v>
+        <v>1403</v>
       </c>
       <c r="F13" t="s">
         <v>107</v>
       </c>
       <c r="G13" t="s">
-        <v>1397</v>
+        <v>1404</v>
       </c>
       <c r="H13" t="s">
         <v>52</v>
@@ -46949,7 +47230,7 @@
     </row>
     <row r="14" spans="1:17">
       <c r="C14" t="s">
-        <v>1398</v>
+        <v>1405</v>
       </c>
       <c r="D14" t="s">
         <v>47</v>
@@ -46958,7 +47239,7 @@
         <v>1159</v>
       </c>
       <c r="G14" t="s">
-        <v>1399</v>
+        <v>1406</v>
       </c>
       <c r="H14" t="s">
         <v>744</v>
@@ -46966,16 +47247,16 @@
     </row>
     <row r="15" spans="1:17">
       <c r="C15" t="s">
-        <v>1400</v>
+        <v>1407</v>
       </c>
       <c r="D15" t="s">
-        <v>1401</v>
+        <v>1408</v>
       </c>
       <c r="E15" t="s">
-        <v>1401</v>
+        <v>1408</v>
       </c>
       <c r="G15" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="H15" t="s">
         <v>766</v>
@@ -46983,24 +47264,24 @@
     </row>
     <row r="16" spans="1:17">
       <c r="C16" t="s">
-        <v>1402</v>
+        <v>1409</v>
       </c>
       <c r="D16" t="s">
-        <v>1403</v>
+        <v>1410</v>
       </c>
       <c r="E16" t="s">
-        <v>1404</v>
+        <v>1411</v>
       </c>
       <c r="G16" t="s">
         <v>559</v>
       </c>
       <c r="H16" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>1405</v>
+        <v>1412</v>
       </c>
       <c r="D17" t="s">
         <v>132</v>
@@ -47009,7 +47290,7 @@
         <v>259</v>
       </c>
       <c r="G17" t="s">
-        <v>1406</v>
+        <v>1413</v>
       </c>
       <c r="H17" t="s">
         <v>775</v>
@@ -47017,55 +47298,55 @@
     </row>
     <row r="18" spans="3:8">
       <c r="C18" t="s">
-        <v>1407</v>
+        <v>1414</v>
       </c>
       <c r="D18" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="E18" t="s">
-        <v>1408</v>
+        <v>1415</v>
       </c>
       <c r="G18" t="s">
-        <v>1409</v>
+        <v>1416</v>
       </c>
       <c r="H18" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="19" spans="3:8">
       <c r="C19" t="s">
-        <v>1410</v>
+        <v>1417</v>
       </c>
       <c r="D19" t="s">
-        <v>1411</v>
+        <v>1418</v>
       </c>
       <c r="E19" t="s">
-        <v>1412</v>
+        <v>1419</v>
       </c>
       <c r="G19" t="s">
-        <v>1413</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="20" spans="3:8">
       <c r="C20" t="s">
-        <v>1414</v>
+        <v>1421</v>
       </c>
       <c r="D20" t="s">
         <v>1122</v>
       </c>
       <c r="E20" t="s">
-        <v>1415</v>
+        <v>1422</v>
       </c>
       <c r="G20" t="s">
-        <v>1416</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="21" spans="3:8">
       <c r="C21" t="s">
-        <v>1417</v>
+        <v>1424</v>
       </c>
       <c r="D21" t="s">
-        <v>1418</v>
+        <v>1425</v>
       </c>
       <c r="E21" t="s">
         <v>161</v>
@@ -47079,18 +47360,18 @@
         <v>282</v>
       </c>
       <c r="E22" t="s">
-        <v>1419</v>
+        <v>1426</v>
       </c>
       <c r="G22" t="s">
-        <v>1420</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="23" spans="3:8">
       <c r="D23" t="s">
-        <v>1421</v>
+        <v>1428</v>
       </c>
       <c r="E23" t="s">
-        <v>1422</v>
+        <v>1429</v>
       </c>
       <c r="G23" t="s">
         <v>171</v>
@@ -47098,10 +47379,10 @@
     </row>
     <row r="24" spans="3:8">
       <c r="D24" t="s">
-        <v>1423</v>
+        <v>1430</v>
       </c>
       <c r="E24" t="s">
-        <v>1376</v>
+        <v>1383</v>
       </c>
       <c r="G24" t="s">
         <v>364</v>
@@ -47109,7 +47390,7 @@
     </row>
     <row r="25" spans="3:8">
       <c r="D25" t="s">
-        <v>1424</v>
+        <v>1431</v>
       </c>
       <c r="E25" t="s">
         <v>122</v>
@@ -47123,7 +47404,7 @@
         <v>1123</v>
       </c>
       <c r="E26" t="s">
-        <v>1425</v>
+        <v>1432</v>
       </c>
       <c r="G26" t="s">
         <v>482</v>
@@ -47131,84 +47412,84 @@
     </row>
     <row r="27" spans="3:8">
       <c r="D27" t="s">
-        <v>1426</v>
+        <v>1433</v>
       </c>
       <c r="E27" t="s">
-        <v>1427</v>
+        <v>1434</v>
       </c>
       <c r="G27" t="s">
-        <v>1428</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="28" spans="3:8">
       <c r="D28" t="s">
-        <v>1429</v>
+        <v>1436</v>
       </c>
       <c r="E28" t="s">
-        <v>1430</v>
+        <v>1437</v>
       </c>
       <c r="G28" t="s">
-        <v>1431</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="29" spans="3:8">
       <c r="D29" t="s">
-        <v>1432</v>
+        <v>1439</v>
       </c>
       <c r="E29" t="s">
-        <v>1433</v>
+        <v>1440</v>
       </c>
       <c r="G29" t="s">
-        <v>1434</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="30" spans="3:8">
       <c r="D30" t="s">
-        <v>1435</v>
+        <v>1442</v>
       </c>
       <c r="E30" t="s">
         <v>332</v>
       </c>
       <c r="G30" t="s">
-        <v>1436</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="31" spans="3:8">
       <c r="D31" t="s">
-        <v>1437</v>
+        <v>1444</v>
       </c>
       <c r="E31" t="s">
-        <v>1438</v>
+        <v>1445</v>
       </c>
       <c r="G31" t="s">
-        <v>1439</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="32" spans="3:8">
       <c r="D32" t="s">
-        <v>1440</v>
+        <v>1447</v>
       </c>
       <c r="E32" t="s">
-        <v>1441</v>
+        <v>1448</v>
       </c>
       <c r="G32" t="s">
-        <v>1442</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="33" spans="4:7">
       <c r="D33" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="E33" t="s">
-        <v>1443</v>
+        <v>1450</v>
       </c>
       <c r="G33" t="s">
-        <v>1444</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="34" spans="4:7">
       <c r="D34" t="s">
-        <v>1445</v>
+        <v>1452</v>
       </c>
       <c r="E34" t="s">
         <v>1092</v>
@@ -47219,7 +47500,7 @@
     </row>
     <row r="35" spans="4:7">
       <c r="D35" t="s">
-        <v>1446</v>
+        <v>1453</v>
       </c>
       <c r="E35" t="s">
         <v>190</v>
@@ -47230,54 +47511,54 @@
     </row>
     <row r="36" spans="4:7">
       <c r="D36" t="s">
-        <v>1447</v>
+        <v>1454</v>
       </c>
       <c r="E36" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
       <c r="G36" t="s">
-        <v>1449</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="37" spans="4:7">
       <c r="D37" t="s">
-        <v>1450</v>
+        <v>1457</v>
       </c>
       <c r="E37" t="s">
-        <v>1451</v>
+        <v>1458</v>
       </c>
       <c r="G37" t="s">
-        <v>1452</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="38" spans="4:7">
       <c r="D38" t="s">
-        <v>1453</v>
+        <v>1460</v>
       </c>
       <c r="E38" t="s">
-        <v>1454</v>
+        <v>1461</v>
       </c>
       <c r="G38" t="s">
-        <v>1455</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="39" spans="4:7">
       <c r="D39" t="s">
-        <v>1456</v>
+        <v>1463</v>
       </c>
       <c r="E39" t="s">
-        <v>1457</v>
+        <v>1464</v>
       </c>
       <c r="G39" t="s">
-        <v>1458</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="40" spans="4:7">
       <c r="D40" t="s">
-        <v>1459</v>
+        <v>1466</v>
       </c>
       <c r="E40" t="s">
-        <v>1460</v>
+        <v>1467</v>
       </c>
       <c r="G40" t="s">
         <v>272</v>
@@ -47288,54 +47569,54 @@
         <v>1087</v>
       </c>
       <c r="E41" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="G41" t="s">
-        <v>1461</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="42" spans="4:7">
       <c r="D42" t="s">
-        <v>1462</v>
+        <v>1469</v>
       </c>
       <c r="E42" t="s">
         <v>1098</v>
       </c>
       <c r="G42" t="s">
-        <v>1463</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="43" spans="4:7">
       <c r="D43" t="s">
-        <v>1376</v>
+        <v>1383</v>
       </c>
       <c r="E43" t="s">
         <v>1105</v>
       </c>
       <c r="G43" t="s">
-        <v>1464</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="44" spans="4:7">
       <c r="D44" t="s">
-        <v>1404</v>
+        <v>1411</v>
       </c>
       <c r="E44" t="s">
-        <v>1465</v>
+        <v>1472</v>
       </c>
       <c r="G44" t="s">
-        <v>1466</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="45" spans="4:7">
       <c r="D45" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="E45" t="s">
         <v>557</v>
       </c>
       <c r="G45" t="s">
-        <v>1467</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="46" spans="4:7">
@@ -47343,15 +47624,15 @@
         <v>320</v>
       </c>
       <c r="E46" t="s">
-        <v>1392</v>
+        <v>1399</v>
       </c>
       <c r="G46" t="s">
-        <v>1468</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="47" spans="4:7">
       <c r="D47" t="s">
-        <v>1469</v>
+        <v>1476</v>
       </c>
       <c r="E47" t="s">
         <v>599</v>
@@ -47365,12 +47646,12 @@
         <v>747</v>
       </c>
       <c r="G48" t="s">
-        <v>1470</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="49" spans="4:7">
       <c r="D49" t="s">
-        <v>1471</v>
+        <v>1478</v>
       </c>
       <c r="G49" t="s">
         <v>295</v>
@@ -47378,47 +47659,47 @@
     </row>
     <row r="50" spans="4:7">
       <c r="D50" t="s">
-        <v>1472</v>
+        <v>1479</v>
       </c>
       <c r="G50" t="s">
-        <v>1473</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="51" spans="4:7">
       <c r="D51" t="s">
-        <v>1474</v>
+        <v>1481</v>
       </c>
       <c r="G51" t="s">
-        <v>1475</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="52" spans="4:7">
       <c r="D52" t="s">
-        <v>1476</v>
+        <v>1483</v>
       </c>
       <c r="G52" t="s">
-        <v>1477</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="53" spans="4:7">
       <c r="D53" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="G53" t="s">
-        <v>1478</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="54" spans="4:7">
       <c r="D54" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="G54" t="s">
-        <v>1480</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="55" spans="4:7">
       <c r="D55" t="s">
-        <v>1481</v>
+        <v>1488</v>
       </c>
       <c r="G55" t="s">
         <v>640</v>
@@ -47426,15 +47707,15 @@
     </row>
     <row r="56" spans="4:7">
       <c r="D56" t="s">
-        <v>1482</v>
+        <v>1489</v>
       </c>
       <c r="G56" t="s">
-        <v>1483</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="57" spans="4:7">
       <c r="D57" t="s">
-        <v>1484</v>
+        <v>1491</v>
       </c>
       <c r="G57" t="s">
         <v>393</v>
@@ -47442,74 +47723,74 @@
     </row>
     <row r="58" spans="4:7">
       <c r="D58" t="s">
-        <v>1485</v>
+        <v>1492</v>
       </c>
       <c r="G58" t="s">
-        <v>1486</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="59" spans="4:7">
       <c r="D59" t="s">
-        <v>1487</v>
+        <v>1494</v>
       </c>
       <c r="G59" t="s">
-        <v>1488</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="60" spans="4:7">
       <c r="D60" t="s">
-        <v>1489</v>
+        <v>1496</v>
       </c>
       <c r="G60" t="s">
-        <v>1490</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="61" spans="4:7">
       <c r="D61" t="s">
-        <v>1491</v>
+        <v>1498</v>
       </c>
       <c r="G61" t="s">
-        <v>1492</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="62" spans="4:7">
       <c r="D62" t="s">
-        <v>1493</v>
+        <v>1500</v>
       </c>
       <c r="G62" t="s">
-        <v>1494</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="63" spans="4:7">
       <c r="D63" t="s">
-        <v>1495</v>
+        <v>1502</v>
       </c>
       <c r="G63" t="s">
-        <v>1496</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="64" spans="4:7">
       <c r="D64" t="s">
-        <v>1497</v>
+        <v>1504</v>
       </c>
       <c r="G64" t="s">
-        <v>1498</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="65" spans="4:7">
       <c r="D65" t="s">
-        <v>1499</v>
+        <v>1506</v>
       </c>
       <c r="G65" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="66" spans="4:7">
       <c r="D66" t="s">
-        <v>1500</v>
+        <v>1507</v>
       </c>
       <c r="G66" t="s">
-        <v>1501</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="67" spans="4:7">
@@ -47522,82 +47803,82 @@
     </row>
     <row r="68" spans="4:7">
       <c r="D68" t="s">
-        <v>1502</v>
+        <v>1509</v>
       </c>
       <c r="G68" t="s">
-        <v>1503</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="69" spans="4:7">
       <c r="D69" t="s">
-        <v>1504</v>
+        <v>1511</v>
       </c>
       <c r="G69" t="s">
-        <v>1505</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="70" spans="4:7">
       <c r="D70" t="s">
-        <v>1506</v>
+        <v>1513</v>
       </c>
       <c r="G70" t="s">
-        <v>1507</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="71" spans="4:7">
       <c r="D71" t="s">
-        <v>1508</v>
+        <v>1515</v>
       </c>
       <c r="G71" t="s">
-        <v>1509</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="72" spans="4:7">
       <c r="D72" t="s">
-        <v>1438</v>
+        <v>1445</v>
       </c>
       <c r="G72" t="s">
-        <v>1510</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="73" spans="4:7">
       <c r="D73" t="s">
-        <v>1511</v>
+        <v>1518</v>
       </c>
       <c r="G73" t="s">
-        <v>1512</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="74" spans="4:7">
       <c r="D74" t="s">
-        <v>1513</v>
+        <v>1520</v>
       </c>
       <c r="G74" t="s">
-        <v>1514</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="75" spans="4:7">
       <c r="D75" t="s">
-        <v>1515</v>
+        <v>1522</v>
       </c>
       <c r="G75" t="s">
-        <v>1516</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="76" spans="4:7">
       <c r="D76" t="s">
-        <v>1517</v>
+        <v>1524</v>
       </c>
       <c r="G76" t="s">
-        <v>1518</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="77" spans="4:7">
       <c r="D77" t="s">
-        <v>1519</v>
+        <v>1526</v>
       </c>
       <c r="G77" t="s">
-        <v>1520</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="78" spans="4:7">
@@ -47605,12 +47886,12 @@
         <v>1192</v>
       </c>
       <c r="G78" t="s">
-        <v>1521</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="79" spans="4:7">
       <c r="D79" t="s">
-        <v>1522</v>
+        <v>1529</v>
       </c>
       <c r="G79" t="s">
         <v>132</v>
@@ -47618,10 +47899,10 @@
     </row>
     <row r="80" spans="4:7">
       <c r="D80" t="s">
-        <v>1523</v>
+        <v>1530</v>
       </c>
       <c r="G80" t="s">
-        <v>1524</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="81" spans="4:7">
@@ -47629,108 +47910,108 @@
         <v>848</v>
       </c>
       <c r="G81" t="s">
-        <v>1525</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="82" spans="4:7">
       <c r="D82" t="s">
-        <v>1526</v>
+        <v>1533</v>
       </c>
       <c r="G82" t="s">
-        <v>1527</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="83" spans="4:7">
       <c r="D83" t="s">
-        <v>1528</v>
+        <v>1535</v>
       </c>
       <c r="G83" t="s">
-        <v>1529</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="84" spans="4:7">
       <c r="D84" t="s">
-        <v>1530</v>
+        <v>1537</v>
       </c>
       <c r="G84" t="s">
-        <v>1531</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="85" spans="4:7">
       <c r="D85" t="s">
-        <v>1532</v>
+        <v>1539</v>
       </c>
       <c r="G85" t="s">
-        <v>1533</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="86" spans="4:7">
       <c r="D86" t="s">
-        <v>1534</v>
+        <v>1541</v>
       </c>
       <c r="G86" t="s">
-        <v>1535</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="87" spans="4:7">
       <c r="D87" t="s">
-        <v>1536</v>
+        <v>1543</v>
       </c>
       <c r="G87" t="s">
-        <v>1537</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="88" spans="4:7">
       <c r="D88" t="s">
-        <v>1538</v>
+        <v>1545</v>
       </c>
       <c r="G88" t="s">
-        <v>1539</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="89" spans="4:7">
       <c r="D89" t="s">
-        <v>1540</v>
+        <v>1547</v>
       </c>
       <c r="G89" t="s">
-        <v>1541</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="90" spans="4:7">
       <c r="D90" t="s">
-        <v>1542</v>
+        <v>1549</v>
       </c>
       <c r="G90" t="s">
-        <v>1543</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="91" spans="4:7">
       <c r="D91" t="s">
-        <v>1544</v>
+        <v>1551</v>
       </c>
       <c r="G91" t="s">
-        <v>1545</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="92" spans="4:7">
       <c r="D92" t="s">
-        <v>1546</v>
+        <v>1553</v>
       </c>
       <c r="G92" t="s">
-        <v>1547</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="93" spans="4:7">
       <c r="D93" t="s">
-        <v>1548</v>
+        <v>1555</v>
       </c>
       <c r="G93" t="s">
-        <v>1549</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="94" spans="4:7">
       <c r="D94" t="s">
-        <v>1550</v>
+        <v>1557</v>
       </c>
       <c r="G94" t="s">
         <v>260</v>
@@ -47741,20 +48022,20 @@
         <v>1104</v>
       </c>
       <c r="G95" t="s">
-        <v>1551</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="96" spans="4:7">
       <c r="D96" t="s">
-        <v>1552</v>
+        <v>1559</v>
       </c>
       <c r="G96" t="s">
-        <v>1553</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="97" spans="4:7">
       <c r="D97" t="s">
-        <v>1554</v>
+        <v>1561</v>
       </c>
       <c r="G97" t="s">
         <v>653</v>
@@ -47765,12 +48046,12 @@
         <v>190</v>
       </c>
       <c r="G98" t="s">
-        <v>1555</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="99" spans="4:7">
       <c r="D99" t="s">
-        <v>1556</v>
+        <v>1563</v>
       </c>
       <c r="G99" t="s">
         <v>765</v>
@@ -47778,7 +48059,7 @@
     </row>
     <row r="100" spans="4:7">
       <c r="D100" t="s">
-        <v>1557</v>
+        <v>1564</v>
       </c>
       <c r="G100" t="s">
         <v>899</v>
@@ -47786,111 +48067,111 @@
     </row>
     <row r="101" spans="4:7">
       <c r="D101" t="s">
-        <v>1558</v>
+        <v>1565</v>
       </c>
       <c r="G101" t="s">
-        <v>1559</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="102" spans="4:7">
       <c r="D102" t="s">
-        <v>1560</v>
+        <v>1567</v>
       </c>
       <c r="G102" t="s">
-        <v>1561</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="103" spans="4:7">
       <c r="D103" t="s">
-        <v>1562</v>
+        <v>1569</v>
       </c>
       <c r="G103" t="s">
-        <v>1563</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="104" spans="4:7">
       <c r="D104" t="s">
-        <v>1564</v>
+        <v>1571</v>
       </c>
       <c r="G104" t="s">
-        <v>1565</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="105" spans="4:7">
       <c r="D105" t="s">
-        <v>1566</v>
+        <v>1573</v>
       </c>
       <c r="G105" t="s">
-        <v>1567</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="106" spans="4:7">
       <c r="D106" t="s">
-        <v>1568</v>
+        <v>1575</v>
       </c>
       <c r="G106" t="s">
-        <v>1569</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="107" spans="4:7">
       <c r="D107" t="s">
-        <v>1570</v>
+        <v>1577</v>
       </c>
       <c r="G107" t="s">
-        <v>1571</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="108" spans="4:7">
       <c r="D108" t="s">
-        <v>1572</v>
+        <v>1579</v>
       </c>
       <c r="G108" t="s">
-        <v>1573</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="109" spans="4:7">
       <c r="D109" t="s">
-        <v>1574</v>
+        <v>1581</v>
       </c>
       <c r="G109" t="s">
-        <v>1575</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="110" spans="4:7">
       <c r="D110" t="s">
-        <v>1576</v>
+        <v>1583</v>
       </c>
       <c r="G110" t="s">
-        <v>1577</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="111" spans="4:7">
       <c r="D111" t="s">
-        <v>1578</v>
+        <v>1585</v>
       </c>
       <c r="G111" t="s">
-        <v>1579</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="112" spans="4:7">
       <c r="D112" t="s">
-        <v>1580</v>
+        <v>1587</v>
       </c>
       <c r="G112" t="s">
-        <v>1581</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="113" spans="4:7">
       <c r="D113" t="s">
-        <v>1582</v>
+        <v>1589</v>
       </c>
       <c r="G113" t="s">
-        <v>1583</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="114" spans="4:7">
       <c r="D114" t="s">
-        <v>1584</v>
+        <v>1591</v>
       </c>
       <c r="G114" t="s">
         <v>271</v>
@@ -47898,71 +48179,71 @@
     </row>
     <row r="115" spans="4:7">
       <c r="D115" t="s">
-        <v>1585</v>
+        <v>1592</v>
       </c>
       <c r="G115" t="s">
-        <v>1586</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="116" spans="4:7">
       <c r="D116" t="s">
-        <v>1587</v>
+        <v>1594</v>
       </c>
       <c r="G116" t="s">
-        <v>1588</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="117" spans="4:7">
       <c r="D117" t="s">
-        <v>1589</v>
+        <v>1596</v>
       </c>
       <c r="G117" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="118" spans="4:7">
       <c r="D118" t="s">
-        <v>1590</v>
+        <v>1597</v>
       </c>
       <c r="G118" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="119" spans="4:7">
       <c r="D119" t="s">
-        <v>1591</v>
+        <v>1598</v>
       </c>
       <c r="G119" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="120" spans="4:7">
       <c r="D120" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="G120" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="121" spans="4:7">
       <c r="D121" t="s">
-        <v>1593</v>
+        <v>1600</v>
       </c>
       <c r="G121" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="122" spans="4:7">
       <c r="D122" t="s">
-        <v>1594</v>
+        <v>1601</v>
       </c>
       <c r="G122" t="s">
-        <v>1595</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="123" spans="4:7">
       <c r="D123" t="s">
-        <v>1596</v>
+        <v>1603</v>
       </c>
       <c r="G123" t="s">
         <v>1093</v>
@@ -47970,7 +48251,7 @@
     </row>
     <row r="124" spans="4:7">
       <c r="D124" t="s">
-        <v>1597</v>
+        <v>1604</v>
       </c>
       <c r="G124" t="s">
         <v>867</v>
@@ -47978,15 +48259,15 @@
     </row>
     <row r="125" spans="4:7">
       <c r="D125" t="s">
-        <v>1598</v>
+        <v>1605</v>
       </c>
       <c r="G125" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="126" spans="4:7">
       <c r="D126" t="s">
-        <v>1599</v>
+        <v>1606</v>
       </c>
       <c r="G126" t="s">
         <v>748</v>
@@ -47994,7 +48275,7 @@
     </row>
     <row r="127" spans="4:7">
       <c r="D127" t="s">
-        <v>1600</v>
+        <v>1607</v>
       </c>
       <c r="G127" t="s">
         <v>728</v>
@@ -48002,7 +48283,7 @@
     </row>
     <row r="128" spans="4:7">
       <c r="D128" t="s">
-        <v>1601</v>
+        <v>1608</v>
       </c>
       <c r="G128" t="s">
         <v>134</v>
@@ -48010,15 +48291,15 @@
     </row>
     <row r="129" spans="4:7">
       <c r="D129" t="s">
-        <v>1602</v>
+        <v>1609</v>
       </c>
       <c r="G129" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="130" spans="4:7">
       <c r="D130" t="s">
-        <v>1603</v>
+        <v>1610</v>
       </c>
       <c r="G130" t="s">
         <v>714</v>
@@ -48026,7 +48307,7 @@
     </row>
     <row r="131" spans="4:7">
       <c r="D131" t="s">
-        <v>1604</v>
+        <v>1611</v>
       </c>
       <c r="G131" t="s">
         <v>510</v>
@@ -48034,7 +48315,7 @@
     </row>
     <row r="132" spans="4:7">
       <c r="D132" t="s">
-        <v>1605</v>
+        <v>1612</v>
       </c>
       <c r="G132" t="s">
         <v>864</v>
@@ -48042,7 +48323,7 @@
     </row>
     <row r="133" spans="4:7">
       <c r="D133" t="s">
-        <v>1606</v>
+        <v>1613</v>
       </c>
       <c r="G133" t="s">
         <v>224</v>
@@ -48050,7 +48331,7 @@
     </row>
     <row r="134" spans="4:7">
       <c r="D134" t="s">
-        <v>1607</v>
+        <v>1614</v>
       </c>
       <c r="G134" t="s">
         <v>433</v>
@@ -48058,7 +48339,7 @@
     </row>
     <row r="135" spans="4:7">
       <c r="D135" t="s">
-        <v>1608</v>
+        <v>1615</v>
       </c>
       <c r="G135" t="s">
         <v>708</v>
@@ -48066,7 +48347,7 @@
     </row>
     <row r="136" spans="4:7">
       <c r="D136" t="s">
-        <v>1609</v>
+        <v>1616</v>
       </c>
       <c r="G136" t="s">
         <v>458</v>
@@ -48074,15 +48355,15 @@
     </row>
     <row r="137" spans="4:7">
       <c r="D137" t="s">
-        <v>1610</v>
+        <v>1617</v>
       </c>
       <c r="G137" t="s">
-        <v>1611</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="138" spans="4:7">
       <c r="D138" t="s">
-        <v>1612</v>
+        <v>1619</v>
       </c>
       <c r="G138" t="s">
         <v>342</v>
@@ -48090,7 +48371,7 @@
     </row>
     <row r="139" spans="4:7">
       <c r="D139" t="s">
-        <v>1613</v>
+        <v>1620</v>
       </c>
       <c r="G139" t="s">
         <v>441</v>
@@ -48098,15 +48379,15 @@
     </row>
     <row r="140" spans="4:7">
       <c r="D140" t="s">
-        <v>1614</v>
+        <v>1621</v>
       </c>
       <c r="G140" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="141" spans="4:7">
       <c r="D141" t="s">
-        <v>1615</v>
+        <v>1622</v>
       </c>
       <c r="G141" t="s">
         <v>810</v>
@@ -48114,7 +48395,7 @@
     </row>
     <row r="142" spans="4:7">
       <c r="D142" t="s">
-        <v>1616</v>
+        <v>1623</v>
       </c>
       <c r="G142" t="s">
         <v>887</v>
@@ -48122,7 +48403,7 @@
     </row>
     <row r="143" spans="4:7">
       <c r="D143" t="s">
-        <v>1617</v>
+        <v>1624</v>
       </c>
       <c r="G143" t="s">
         <v>1099</v>
@@ -48130,7 +48411,7 @@
     </row>
     <row r="144" spans="4:7">
       <c r="D144" t="s">
-        <v>1618</v>
+        <v>1625</v>
       </c>
       <c r="G144" t="s">
         <v>470</v>
@@ -48138,7 +48419,7 @@
     </row>
     <row r="145" spans="4:7">
       <c r="D145" t="s">
-        <v>1619</v>
+        <v>1626</v>
       </c>
       <c r="G145" t="s">
         <v>1106</v>
@@ -48146,7 +48427,7 @@
     </row>
     <row r="146" spans="4:7">
       <c r="D146" t="s">
-        <v>1620</v>
+        <v>1627</v>
       </c>
       <c r="G146" t="s">
         <v>1113</v>
@@ -48154,7 +48435,7 @@
     </row>
     <row r="147" spans="4:7">
       <c r="D147" t="s">
-        <v>1621</v>
+        <v>1628</v>
       </c>
       <c r="G147" t="s">
         <v>1124</v>
@@ -48162,15 +48443,15 @@
     </row>
     <row r="148" spans="4:7">
       <c r="D148" t="s">
-        <v>1622</v>
+        <v>1629</v>
       </c>
       <c r="G148" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="149" spans="4:7">
       <c r="D149" t="s">
-        <v>1623</v>
+        <v>1630</v>
       </c>
       <c r="G149" t="s">
         <v>607</v>
@@ -48178,7 +48459,7 @@
     </row>
     <row r="150" spans="4:7">
       <c r="D150" t="s">
-        <v>1624</v>
+        <v>1631</v>
       </c>
       <c r="G150" t="s">
         <v>1175</v>
@@ -48194,7 +48475,7 @@
     </row>
     <row r="152" spans="4:7">
       <c r="D152" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="G152" t="s">
         <v>853</v>
@@ -48217,6 +48498,9 @@
       </c>
     </row>
     <row r="155" spans="4:7">
+      <c r="D155" t="s">
+        <v>558</v>
+      </c>
       <c r="G155" t="s">
         <v>690</v>
       </c>
@@ -48273,12 +48557,12 @@
     </row>
     <row r="166" spans="7:7">
       <c r="G166" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="167" spans="7:7">
       <c r="G167" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="168" spans="7:7">
@@ -48311,34 +48595,34 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15">
       <c r="A1" s="19" t="s">
-        <v>1625</v>
+        <v>1632</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>1626</v>
+        <v>1633</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>1627</v>
+        <v>1634</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>1628</v>
+        <v>1635</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>1629</v>
+        <v>1636</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>1630</v>
+        <v>1637</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>1632</v>
+        <v>1639</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>1633</v>
+        <v>1640</v>
       </c>
       <c r="J1" s="19" t="s">
-        <v>1634</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -48381,22 +48665,22 @@
         <v>5</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>1635</v>
+        <v>1642</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>1357</v>
+        <v>1364</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>1636</v>
+        <v>1643</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>1637</v>
+        <v>1644</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>1638</v>
+        <v>1645</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>1639</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -48419,10 +48703,10 @@
         <v>24</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>1640</v>
+        <v>1647</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>1641</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -48445,7 +48729,7 @@
         <v>36</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>1642</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -48477,19 +48761,19 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="45.85546875" style="22" customWidth="1"/>
+    <col min="2" max="2" width="72.42578125" style="22" customWidth="1"/>
     <col min="3" max="3" width="52.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="24" t="s">
-        <v>1643</v>
+        <v>1650</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>645</v>
+        <v>1147</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>1644</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="23.25" customHeight="1">
@@ -48498,19 +48782,19 @@
       </c>
       <c r="B2" s="25">
         <f>_xlfn.XLOOKUP($B$1,BASE!$AI:$AI,BASE!$AF:$AF,"No encontrado",0)</f>
-        <v>46090</v>
+        <v>46120</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>1645</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="24" t="s">
-        <v>1357</v>
+        <v>1364</v>
       </c>
       <c r="B3" s="26" t="str">
         <f>_xlfn.XLOOKUP($B$1,BASE!$AI:$AI,BASE!$N:$N,"No encontrado",0)</f>
-        <v>Soporte Tecnico</v>
+        <v>Operador call center</v>
       </c>
       <c r="C3" s="30"/>
     </row>
@@ -48520,7 +48804,7 @@
       </c>
       <c r="B4" s="26" t="str">
         <f>_xlfn.XLOOKUP($B$1,BASE!$AI:$AI,BASE!$K:$K,"No encontrado",0)</f>
-        <v>Sistemas</v>
+        <v>CONTACT CENTER</v>
       </c>
       <c r="C4" s="30"/>
     </row>
@@ -48530,7 +48814,7 @@
       </c>
       <c r="B5" s="26" t="str">
         <f>_xlfn.XLOOKUP($B$1,BASE!$AI:$AI,BASE!$L:$L,"No encontrado",0)</f>
-        <v>Sistemas</v>
+        <v>Operaciones</v>
       </c>
       <c r="C5" s="23"/>
     </row>
@@ -48540,17 +48824,17 @@
       </c>
       <c r="B6" s="26" t="str">
         <f>_xlfn.XLOOKUP($B$1,BASE!$AI:$AI,BASE!$AJ:$AJ,"No encontrado",0)</f>
-        <v>$1.504.151,39 bruto /  1.229.258,00 neto</v>
+        <v xml:space="preserve"> $1.264.501,58 bruto /	 $1.032.990,00 neto</v>
       </c>
       <c r="C6" s="23"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="24" t="s">
-        <v>1638</v>
+        <v>1645</v>
       </c>
       <c r="B7" s="26" t="str">
         <f>_xlfn.XLOOKUP($B$1,BASE!$AI:$AI,BASE!$AC:$AC,"No encontrado",0)</f>
-        <v>Lunes a Viernes de 13 a 21hs y Sábado por medio de 8 a 13hs (45hs semanales)</v>
+        <v xml:space="preserve"> lunes a jueves de 11:00 a 20:00 viernes de 12:00 a 20:00 y sábados de 8:00 a 12:00</v>
       </c>
       <c r="C7" s="23"/>
     </row>
@@ -48576,11 +48860,11 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="24" t="s">
-        <v>1640</v>
+        <v>1647</v>
       </c>
       <c r="B10" s="26" t="str">
         <f>_xlfn.XLOOKUP($B$1,BASE!$AI:$AI,BASE!$AD:$AD,"No encontrado",0)</f>
-        <v>Vilella</v>
+        <v>CONTACT CENTER</v>
       </c>
       <c r="C10" s="23"/>
     </row>
@@ -48590,13 +48874,13 @@
       </c>
       <c r="B11" s="26" t="str">
         <f>_xlfn.XLOOKUP($B$1,BASE!$AI:$AI,BASE!$O:$O,"No encontrado",0)</f>
-        <v>Marcelo Engel</v>
+        <v>Zukoski</v>
       </c>
       <c r="C11" s="23"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="24" t="s">
-        <v>1646</v>
+        <v>1653</v>
       </c>
       <c r="B12" s="26">
         <f>_xlfn.XLOOKUP($B$1,BASE!$AI:$AI,BASE!$W:$W,"No encontrado",0)</f>
@@ -48606,11 +48890,11 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="24" t="s">
-        <v>1647</v>
+        <v>1654</v>
       </c>
       <c r="B13" s="26" t="str">
         <f>_xlfn.XLOOKUP($B$1,BASE!$AI:$AI,BASE!$X:$X,"No encontrado",0)</f>
-        <v>Pablo Cammi</v>
+        <v>MARCOS ORTIZ OSCAR</v>
       </c>
       <c r="C13" s="23"/>
     </row>
@@ -48640,17 +48924,17 @@
       </c>
       <c r="B16" s="26" t="str">
         <f>_xlfn.XLOOKUP($B$1,BASE!$AI:$AI,BASE!$K:$K,"No encontrado",0)</f>
-        <v>Sistemas</v>
+        <v>CONTACT CENTER</v>
       </c>
       <c r="C16" s="23"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="24" t="s">
-        <v>1648</v>
+        <v>1655</v>
       </c>
       <c r="B17" s="26" t="str">
         <f>_xlfn.XLOOKUP($B$1,BASE!$AI:$AI,BASE!$L:$L,"No encontrado",0)</f>
-        <v>Sistemas</v>
+        <v>Operaciones</v>
       </c>
       <c r="C17" s="23"/>
     </row>

--- a/Seguimiento de Vacantes.xlsx
+++ b/Seguimiento de Vacantes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan Pablo Sanchez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C77ACAA-0EA0-42C2-8219-4BDAF2E0B96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E144CAC-792A-4C95-B7A1-4D5A2FB559BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{3B13A29B-20F1-4D27-890C-391D6AD58285}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6443" uniqueCount="1672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6487" uniqueCount="1677">
   <si>
     <t>N° Vacante</t>
   </si>
@@ -3979,6 +3979,9 @@
     <t>NEGRI, ELENA GLADYS</t>
   </si>
   <si>
+    <t>Jubilación</t>
+  </si>
+  <si>
     <t>9 a 18 hs lunes a Viernes</t>
   </si>
   <si>
@@ -4081,9 +4084,27 @@
     <t>00277</t>
   </si>
   <si>
+    <t>VENTAS CORPORATIVAS</t>
+  </si>
+  <si>
+    <t>Juan Francisco Mandingorra</t>
+  </si>
+  <si>
+    <t>MARIA LUJAN BARRIENTOS</t>
+  </si>
+  <si>
+    <t>10 a 18 hs</t>
+  </si>
+  <si>
+    <t>Perón 1479 CABA</t>
+  </si>
+  <si>
     <t>00278</t>
   </si>
   <si>
+    <t>KARINA SAYAL</t>
+  </si>
+  <si>
     <t>00279</t>
   </si>
   <si>
@@ -4231,9 +4252,6 @@
     <t>Referidos</t>
   </si>
   <si>
-    <t>Jubilación</t>
-  </si>
-  <si>
     <t>Base general</t>
   </si>
   <si>
@@ -4571,9 +4589,6 @@
   </si>
   <si>
     <t>PROGRAMADOR/A</t>
-  </si>
-  <si>
-    <t>VENTAS CORPORATIVAS</t>
   </si>
   <si>
     <t>OBRAS</t>
@@ -43773,7 +43788,7 @@
         <v>1308</v>
       </c>
       <c r="Y265" s="8" t="s">
-        <v>987</v>
+        <v>1309</v>
       </c>
       <c r="Z265" s="11" t="s">
         <v>55</v>
@@ -43781,10 +43796,10 @@
       <c r="AA265" s="8"/>
       <c r="AB265" s="8"/>
       <c r="AC265" s="8" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="AD265" s="8" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="AE265" s="8"/>
       <c r="AF265" s="8"/>
@@ -43801,7 +43816,7 @@
     </row>
     <row r="266" spans="1:40" ht="28.5">
       <c r="A266" s="7" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B266" s="5">
         <v>46112</v>
@@ -43828,7 +43843,7 @@
         <v>45</v>
       </c>
       <c r="K266" s="8" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="L266" s="8" t="s">
         <v>1131</v>
@@ -43837,10 +43852,10 @@
         <v>170</v>
       </c>
       <c r="N266" s="8" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="O266" s="8" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="P266" s="8"/>
       <c r="Q266" s="8" t="s">
@@ -43857,7 +43872,7 @@
       </c>
       <c r="W266" s="8"/>
       <c r="X266" s="8" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="Y266" s="8" t="s">
         <v>987</v>
@@ -43868,7 +43883,7 @@
       <c r="AA266" s="8"/>
       <c r="AB266" s="8"/>
       <c r="AC266" s="8" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="AD266" s="8" t="s">
         <v>112</v>
@@ -43883,10 +43898,10 @@
         <v>611</v>
       </c>
       <c r="AH266" s="8" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="AI266" s="8" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="AJ266" s="8"/>
       <c r="AK266" s="8"/>
@@ -43896,7 +43911,7 @@
     </row>
     <row r="267" spans="1:40">
       <c r="A267" s="7" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B267" s="5">
         <v>46108</v>
@@ -43956,7 +43971,7 @@
         <v>170632</v>
       </c>
       <c r="X267" s="8" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="Y267" s="8" t="s">
         <v>987</v>
@@ -43981,7 +43996,7 @@
     </row>
     <row r="268" spans="1:40">
       <c r="A268" s="7" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B268" s="5">
         <v>46112</v>
@@ -44041,7 +44056,7 @@
         <v>1094</v>
       </c>
       <c r="X268" s="8" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="Y268" s="8" t="s">
         <v>987</v>
@@ -44066,7 +44081,7 @@
     </row>
     <row r="269" spans="1:40">
       <c r="A269" s="7" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B269" s="5">
         <v>46097</v>
@@ -44126,7 +44141,7 @@
         <v>1093</v>
       </c>
       <c r="X269" s="8" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="Y269" s="8" t="s">
         <v>275</v>
@@ -44151,7 +44166,7 @@
     </row>
     <row r="270" spans="1:40">
       <c r="A270" s="7" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B270" s="5">
         <v>46097</v>
@@ -44211,7 +44226,7 @@
         <v>168680</v>
       </c>
       <c r="X270" s="8" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="Y270" s="8" t="s">
         <v>275</v>
@@ -44236,7 +44251,7 @@
     </row>
     <row r="271" spans="1:40">
       <c r="A271" s="7" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B271" s="5">
         <v>46097</v>
@@ -44296,7 +44311,7 @@
         <v>168697</v>
       </c>
       <c r="X271" s="8" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="Y271" s="8" t="s">
         <v>275</v>
@@ -44321,7 +44336,7 @@
     </row>
     <row r="272" spans="1:40">
       <c r="A272" s="7" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B272" s="5">
         <v>46113</v>
@@ -44381,7 +44396,7 @@
       </c>
       <c r="W272" s="8"/>
       <c r="X272" s="8" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="Y272" s="8" t="s">
         <v>987</v>
@@ -44392,7 +44407,7 @@
       <c r="AA272" s="8"/>
       <c r="AB272" s="8"/>
       <c r="AC272" s="8" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="AD272" s="8"/>
       <c r="AE272" s="8"/>
@@ -44410,7 +44425,7 @@
     </row>
     <row r="273" spans="1:40">
       <c r="A273" s="7" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B273" s="5">
         <v>46098</v>
@@ -44470,7 +44485,7 @@
       </c>
       <c r="W273" s="8"/>
       <c r="X273" s="8" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="Y273" s="8" t="s">
         <v>987</v>
@@ -44499,7 +44514,7 @@
     </row>
     <row r="274" spans="1:40">
       <c r="A274" s="7" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B274" s="5">
         <v>46119</v>
@@ -44559,7 +44574,7 @@
       </c>
       <c r="W274" s="8"/>
       <c r="X274" s="8" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="Y274" s="8" t="s">
         <v>987</v>
@@ -44586,7 +44601,7 @@
     </row>
     <row r="275" spans="1:40">
       <c r="A275" s="7" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B275" s="5">
         <v>46119</v>
@@ -44646,7 +44661,7 @@
       </c>
       <c r="W275" s="8"/>
       <c r="X275" s="8" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="Y275" s="8" t="s">
         <v>987</v>
@@ -44673,7 +44688,7 @@
     </row>
     <row r="276" spans="1:40">
       <c r="A276" s="7" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B276" s="5">
         <v>46125</v>
@@ -44735,7 +44750,7 @@
         <v>160471</v>
       </c>
       <c r="X276" s="8" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="Y276" s="8" t="s">
         <v>1238</v>
@@ -44764,7 +44779,7 @@
     </row>
     <row r="277" spans="1:40">
       <c r="A277" s="7" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B277" s="5">
         <v>46122</v>
@@ -44808,17 +44823,21 @@
         <v>136</v>
       </c>
       <c r="R277" s="8" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="S277" s="8"/>
-      <c r="T277" s="8"/>
-      <c r="U277" s="8"/>
+      <c r="T277" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="U277" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="V277" s="8" t="s">
         <v>53</v>
       </c>
       <c r="W277" s="8"/>
       <c r="X277" s="8" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="Y277" s="8" t="s">
         <v>987</v>
@@ -44845,42 +44864,88 @@
       <c r="AM277" s="8"/>
       <c r="AN277" s="8"/>
     </row>
-    <row r="278" spans="1:40">
+    <row r="278" spans="1:40" ht="28.5">
       <c r="A278" s="7" t="s">
-        <v>1342</v>
-      </c>
-      <c r="B278" s="8"/>
-      <c r="C278" s="17" t="str">
+        <v>1343</v>
+      </c>
+      <c r="B278" s="5">
+        <v>46125</v>
+      </c>
+      <c r="C278" s="17">
         <f ca="1">IF(B278="","",IF(OR(TRIM(Q278)="En curso",TRIM(Q278)="En proceso de ingreso"),TODAY()-B278,"Cerrada"))</f>
-        <v/>
-      </c>
-      <c r="D278" s="8"/>
-      <c r="E278" s="8"/>
-      <c r="F278" s="8"/>
-      <c r="G278" s="8"/>
+        <v>0</v>
+      </c>
+      <c r="D278" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E278" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F278" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="G278" s="8" t="s">
+        <v>187</v>
+      </c>
       <c r="H278" s="8"/>
-      <c r="I278" s="8"/>
-      <c r="J278" s="8"/>
-      <c r="K278" s="8"/>
-      <c r="L278" s="8"/>
-      <c r="M278" s="8"/>
-      <c r="N278" s="8"/>
-      <c r="O278" s="8"/>
+      <c r="I278" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J278" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="K278" s="8" t="s">
+        <v>1344</v>
+      </c>
+      <c r="L278" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M278" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N278" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="O278" s="8" t="s">
+        <v>1345</v>
+      </c>
       <c r="P278" s="8"/>
-      <c r="Q278" s="8"/>
-      <c r="R278" s="8"/>
+      <c r="Q278" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="R278" s="8" t="s">
+        <v>1297</v>
+      </c>
       <c r="S278" s="8"/>
-      <c r="T278" s="8"/>
-      <c r="U278" s="8"/>
-      <c r="V278" s="8"/>
-      <c r="W278" s="8"/>
-      <c r="X278" s="8"/>
-      <c r="Y278" s="8"/>
-      <c r="Z278" s="11"/>
+      <c r="T278" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="U278" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="V278" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="W278" s="8">
+        <v>164312</v>
+      </c>
+      <c r="X278" s="8" t="s">
+        <v>1346</v>
+      </c>
+      <c r="Y278" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="Z278" s="11" t="s">
+        <v>55</v>
+      </c>
       <c r="AA278" s="8"/>
       <c r="AB278" s="8"/>
-      <c r="AC278" s="8"/>
-      <c r="AD278" s="8"/>
+      <c r="AC278" s="8" t="s">
+        <v>1347</v>
+      </c>
+      <c r="AD278" s="8" t="s">
+        <v>1348</v>
+      </c>
       <c r="AE278" s="8"/>
       <c r="AF278" s="8"/>
       <c r="AG278" s="5"/>
@@ -44892,42 +44957,88 @@
       <c r="AM278" s="8"/>
       <c r="AN278" s="8"/>
     </row>
-    <row r="279" spans="1:40">
+    <row r="279" spans="1:40" ht="28.5">
       <c r="A279" s="7" t="s">
-        <v>1343</v>
-      </c>
-      <c r="B279" s="8"/>
-      <c r="C279" s="17" t="str">
+        <v>1349</v>
+      </c>
+      <c r="B279" s="5">
+        <v>46125</v>
+      </c>
+      <c r="C279" s="17">
         <f ca="1">IF(B279="","",IF(OR(TRIM(Q279)="En curso",TRIM(Q279)="En proceso de ingreso"),TODAY()-B279,"Cerrada"))</f>
-        <v/>
-      </c>
-      <c r="D279" s="8"/>
-      <c r="E279" s="8"/>
-      <c r="F279" s="8"/>
-      <c r="G279" s="8"/>
+        <v>0</v>
+      </c>
+      <c r="D279" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E279" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F279" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="G279" s="8" t="s">
+        <v>187</v>
+      </c>
       <c r="H279" s="8"/>
-      <c r="I279" s="8"/>
-      <c r="J279" s="8"/>
-      <c r="K279" s="8"/>
-      <c r="L279" s="8"/>
-      <c r="M279" s="8"/>
-      <c r="N279" s="8"/>
-      <c r="O279" s="8"/>
+      <c r="I279" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J279" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="K279" s="8" t="s">
+        <v>1344</v>
+      </c>
+      <c r="L279" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M279" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N279" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="O279" s="8" t="s">
+        <v>1345</v>
+      </c>
       <c r="P279" s="8"/>
-      <c r="Q279" s="8"/>
-      <c r="R279" s="8"/>
+      <c r="Q279" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="R279" s="8" t="s">
+        <v>1297</v>
+      </c>
       <c r="S279" s="8"/>
-      <c r="T279" s="8"/>
-      <c r="U279" s="8"/>
-      <c r="V279" s="8"/>
-      <c r="W279" s="8"/>
-      <c r="X279" s="8"/>
-      <c r="Y279" s="8"/>
-      <c r="Z279" s="11"/>
+      <c r="T279" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="U279" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="V279" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="W279" s="8">
+        <v>163654</v>
+      </c>
+      <c r="X279" s="8" t="s">
+        <v>1350</v>
+      </c>
+      <c r="Y279" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="Z279" s="11" t="s">
+        <v>55</v>
+      </c>
       <c r="AA279" s="8"/>
       <c r="AB279" s="8"/>
-      <c r="AC279" s="8"/>
-      <c r="AD279" s="8"/>
+      <c r="AC279" s="8" t="s">
+        <v>1347</v>
+      </c>
+      <c r="AD279" s="8" t="s">
+        <v>1348</v>
+      </c>
       <c r="AE279" s="8"/>
       <c r="AF279" s="8"/>
       <c r="AG279" s="5"/>
@@ -44941,7 +45052,7 @@
     </row>
     <row r="280" spans="1:40">
       <c r="A280" s="7" t="s">
-        <v>1344</v>
+        <v>1351</v>
       </c>
       <c r="B280" s="8"/>
       <c r="C280" s="17" t="str">
@@ -44988,7 +45099,7 @@
     </row>
     <row r="281" spans="1:40">
       <c r="A281" s="7" t="s">
-        <v>1345</v>
+        <v>1352</v>
       </c>
       <c r="B281" s="8"/>
       <c r="C281" s="17" t="str">
@@ -45035,7 +45146,7 @@
     </row>
     <row r="282" spans="1:40">
       <c r="A282" s="7" t="s">
-        <v>1346</v>
+        <v>1353</v>
       </c>
       <c r="B282" s="8"/>
       <c r="C282" s="17" t="str">
@@ -45082,7 +45193,7 @@
     </row>
     <row r="283" spans="1:40">
       <c r="A283" s="7" t="s">
-        <v>1347</v>
+        <v>1354</v>
       </c>
       <c r="B283" s="8"/>
       <c r="C283" s="17" t="str">
@@ -45129,7 +45240,7 @@
     </row>
     <row r="284" spans="1:40">
       <c r="A284" s="7" t="s">
-        <v>1348</v>
+        <v>1355</v>
       </c>
       <c r="B284" s="8"/>
       <c r="C284" s="17" t="str">
@@ -45176,7 +45287,7 @@
     </row>
     <row r="285" spans="1:40">
       <c r="A285" s="7" t="s">
-        <v>1349</v>
+        <v>1356</v>
       </c>
       <c r="B285" s="8"/>
       <c r="C285" s="17" t="str">
@@ -45223,7 +45334,7 @@
     </row>
     <row r="286" spans="1:40">
       <c r="A286" s="7" t="s">
-        <v>1350</v>
+        <v>1357</v>
       </c>
       <c r="B286" s="8"/>
       <c r="C286" s="17" t="str">
@@ -45270,7 +45381,7 @@
     </row>
     <row r="287" spans="1:40">
       <c r="A287" s="7" t="s">
-        <v>1351</v>
+        <v>1358</v>
       </c>
       <c r="B287" s="8"/>
       <c r="C287" s="17" t="str">
@@ -45317,7 +45428,7 @@
     </row>
     <row r="288" spans="1:40">
       <c r="A288" s="7" t="s">
-        <v>1352</v>
+        <v>1359</v>
       </c>
       <c r="B288" s="8"/>
       <c r="C288" s="17" t="str">
@@ -45364,7 +45475,7 @@
     </row>
     <row r="289" spans="1:40">
       <c r="A289" s="7" t="s">
-        <v>1353</v>
+        <v>1360</v>
       </c>
       <c r="B289" s="8"/>
       <c r="C289" s="17" t="str">
@@ -45411,7 +45522,7 @@
     </row>
     <row r="290" spans="1:40">
       <c r="A290" s="7" t="s">
-        <v>1354</v>
+        <v>1361</v>
       </c>
       <c r="B290" s="8"/>
       <c r="C290" s="17" t="str">
@@ -45458,7 +45569,7 @@
     </row>
     <row r="291" spans="1:40">
       <c r="A291" s="7" t="s">
-        <v>1355</v>
+        <v>1362</v>
       </c>
       <c r="B291" s="8"/>
       <c r="C291" s="17" t="str">
@@ -45505,7 +45616,7 @@
     </row>
     <row r="292" spans="1:40">
       <c r="A292" s="7" t="s">
-        <v>1356</v>
+        <v>1363</v>
       </c>
       <c r="B292" s="8"/>
       <c r="C292" s="17" t="str">
@@ -45552,7 +45663,7 @@
     </row>
     <row r="293" spans="1:40">
       <c r="A293" s="7" t="s">
-        <v>1357</v>
+        <v>1364</v>
       </c>
       <c r="B293" s="8"/>
       <c r="C293" s="17" t="str">
@@ -45599,7 +45710,7 @@
     </row>
     <row r="294" spans="1:40">
       <c r="A294" s="7" t="s">
-        <v>1358</v>
+        <v>1365</v>
       </c>
       <c r="B294" s="8"/>
       <c r="C294" s="17" t="str">
@@ -45646,7 +45757,7 @@
     </row>
     <row r="295" spans="1:40">
       <c r="A295" s="7" t="s">
-        <v>1359</v>
+        <v>1366</v>
       </c>
       <c r="B295" s="8"/>
       <c r="C295" s="17" t="str">
@@ -45693,7 +45804,7 @@
     </row>
     <row r="296" spans="1:40">
       <c r="A296" s="7" t="s">
-        <v>1360</v>
+        <v>1367</v>
       </c>
       <c r="B296" s="8"/>
       <c r="C296" s="17" t="str">
@@ -45740,7 +45851,7 @@
     </row>
     <row r="297" spans="1:40">
       <c r="A297" s="7" t="s">
-        <v>1361</v>
+        <v>1368</v>
       </c>
       <c r="B297" s="8"/>
       <c r="C297" s="17" t="str">
@@ -45787,7 +45898,7 @@
     </row>
     <row r="298" spans="1:40">
       <c r="A298" s="7" t="s">
-        <v>1362</v>
+        <v>1369</v>
       </c>
       <c r="B298" s="8"/>
       <c r="C298" s="17" t="str">
@@ -45834,7 +45945,7 @@
     </row>
     <row r="299" spans="1:40">
       <c r="A299" s="7" t="s">
-        <v>1363</v>
+        <v>1370</v>
       </c>
       <c r="B299" s="8"/>
       <c r="C299" s="17" t="str">
@@ -45881,7 +45992,7 @@
     </row>
     <row r="300" spans="1:40">
       <c r="A300" s="7" t="s">
-        <v>1364</v>
+        <v>1371</v>
       </c>
       <c r="B300" s="8"/>
       <c r="C300" s="17" t="str">
@@ -45928,7 +46039,7 @@
     </row>
     <row r="301" spans="1:40">
       <c r="A301" s="7" t="s">
-        <v>1365</v>
+        <v>1372</v>
       </c>
       <c r="B301" s="8"/>
       <c r="C301" s="17" t="str">
@@ -45975,7 +46086,7 @@
     </row>
     <row r="302" spans="1:40">
       <c r="A302" s="7" t="s">
-        <v>1366</v>
+        <v>1373</v>
       </c>
       <c r="B302" s="8"/>
       <c r="C302" s="17" t="str">
@@ -46022,7 +46133,7 @@
     </row>
     <row r="303" spans="1:40">
       <c r="A303" s="7" t="s">
-        <v>1367</v>
+        <v>1374</v>
       </c>
       <c r="B303" s="8"/>
       <c r="C303" s="17" t="str">
@@ -46069,7 +46180,7 @@
     </row>
     <row r="304" spans="1:40">
       <c r="A304" s="7" t="s">
-        <v>1368</v>
+        <v>1375</v>
       </c>
       <c r="B304" s="8"/>
       <c r="C304" s="17" t="str">
@@ -46116,7 +46227,7 @@
     </row>
     <row r="305" spans="1:40">
       <c r="A305" s="7" t="s">
-        <v>1369</v>
+        <v>1376</v>
       </c>
       <c r="B305" s="8"/>
       <c r="C305" s="17" t="str">
@@ -46163,7 +46274,7 @@
     </row>
     <row r="306" spans="1:40">
       <c r="A306" s="7" t="s">
-        <v>1370</v>
+        <v>1377</v>
       </c>
       <c r="B306" s="8"/>
       <c r="C306" s="17" t="str">
@@ -46210,7 +46321,7 @@
     </row>
     <row r="307" spans="1:40">
       <c r="A307" s="7" t="s">
-        <v>1371</v>
+        <v>1378</v>
       </c>
       <c r="B307" s="8"/>
       <c r="C307" s="17" t="str">
@@ -46257,7 +46368,7 @@
     </row>
     <row r="308" spans="1:40">
       <c r="A308" s="7" t="s">
-        <v>1372</v>
+        <v>1379</v>
       </c>
       <c r="B308" s="8"/>
       <c r="C308" s="17" t="str">
@@ -46304,7 +46415,7 @@
     </row>
     <row r="309" spans="1:40">
       <c r="A309" s="7" t="s">
-        <v>1373</v>
+        <v>1380</v>
       </c>
       <c r="B309" s="8"/>
       <c r="C309" s="17" t="str">
@@ -46385,10 +46496,10 @@
     <cfRule type="duplicateValues" dxfId="0" priority="42"/>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL2:AM2 F2:G309 AL269:AM304 AL207:AM215 AL217:AM266" xr:uid="{BE1C9EA3-F87F-46EF-B894-6F18EE76B437}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL2:AM2 AL217:AM266 AL269:AM304 AL207:AM215 F2:G309" xr:uid="{BE1C9EA3-F87F-46EF-B894-6F18EE76B437}">
       <formula1>"Si,No"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W200 AA2:AB309 H2:H309 W205:W309" xr:uid="{419406C0-34B6-447D-A00F-064CE22CD2A6}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W200 AA2:AB309 W205:W309 H2:H309" xr:uid="{419406C0-34B6-447D-A00F-064CE22CD2A6}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG309" xr:uid="{4AB4C081-870E-4D3B-986A-4F3EAA9A398C}">
       <formula1>"Externa,Interna,Mixta"</formula1>
     </dataValidation>
@@ -46578,7 +46689,7 @@
         <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>1374</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -46586,7 +46697,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>1375</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -46594,12 +46705,12 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>1374</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>1376</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -46612,12 +46723,12 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>1374</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="15" t="s">
-        <v>1376</v>
+        <v>1383</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>17</v>
@@ -46637,7 +46748,7 @@
         <v>1297</v>
       </c>
       <c r="E13" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="F13" t="s">
         <v>608</v>
@@ -46658,7 +46769,7 @@
         <v>935</v>
       </c>
       <c r="L13" t="s">
-        <v>1377</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -46789,7 +46900,7 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="B19" s="16">
         <v>1</v>
@@ -46830,7 +46941,7 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>1374</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -46838,7 +46949,7 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>1374</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -46846,7 +46957,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>1376</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -46891,7 +47002,7 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="B32" s="16">
         <v>65</v>
@@ -46902,12 +47013,12 @@
         <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>1375</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="15" t="s">
-        <v>1376</v>
+        <v>1383</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>16</v>
@@ -46924,7 +47035,7 @@
         <v>472</v>
       </c>
       <c r="D40" t="s">
-        <v>1377</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -46985,7 +47096,7 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="B45" s="16">
         <v>63</v>
@@ -47002,7 +47113,7 @@
         <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>1375</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -47015,7 +47126,7 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="15" t="s">
-        <v>1376</v>
+        <v>1383</v>
       </c>
       <c r="B51" s="15" t="s">
         <v>16</v>
@@ -47032,7 +47143,7 @@
         <v>472</v>
       </c>
       <c r="D52" t="s">
-        <v>1377</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -47139,7 +47250,7 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="B61" s="16">
         <v>28</v>
@@ -47180,7 +47291,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1378</v>
+        <v>1385</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>9</v>
@@ -47189,16 +47300,16 @@
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1379</v>
+        <v>1386</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1380</v>
+        <v>1387</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1381</v>
+        <v>1388</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>1382</v>
+        <v>1389</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>19</v>
@@ -47207,13 +47318,13 @@
         <v>20</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>1383</v>
+        <v>1390</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1384</v>
+        <v>1391</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1385</v>
+        <v>1392</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>29</v>
@@ -47222,10 +47333,10 @@
         <v>33</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>1386</v>
+        <v>1393</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>1387</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -47248,7 +47359,7 @@
         <v>223</v>
       </c>
       <c r="G2" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H2" t="s">
         <v>1297</v>
@@ -47286,13 +47397,13 @@
         <v>727</v>
       </c>
       <c r="C3" t="s">
-        <v>1388</v>
+        <v>1395</v>
       </c>
       <c r="D3" t="s">
         <v>1179</v>
       </c>
       <c r="E3" t="s">
-        <v>1389</v>
+        <v>1396</v>
       </c>
       <c r="F3" t="s">
         <v>149</v>
@@ -47301,7 +47412,7 @@
         <v>1258</v>
       </c>
       <c r="H3" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="I3" t="s">
         <v>757</v>
@@ -47336,7 +47447,7 @@
         <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>1390</v>
+        <v>1397</v>
       </c>
       <c r="D4" t="s">
         <v>1168</v>
@@ -47360,13 +47471,13 @@
         <v>69</v>
       </c>
       <c r="L4" t="s">
-        <v>1391</v>
+        <v>1398</v>
       </c>
       <c r="M4" t="s">
         <v>173</v>
       </c>
       <c r="O4" t="s">
-        <v>1392</v>
+        <v>1399</v>
       </c>
       <c r="P4" t="s">
         <v>51</v>
@@ -47407,10 +47518,10 @@
         <v>1127</v>
       </c>
       <c r="L5" t="s">
-        <v>1393</v>
+        <v>1309</v>
       </c>
       <c r="O5" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="P5" t="s">
         <v>751</v>
@@ -47445,10 +47556,10 @@
         <v>608</v>
       </c>
       <c r="L6" t="s">
-        <v>1395</v>
+        <v>1401</v>
       </c>
       <c r="O6" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="P6" t="s">
         <v>773</v>
@@ -47456,13 +47567,13 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>1396</v>
+        <v>1402</v>
       </c>
       <c r="B7" t="s">
         <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>1397</v>
+        <v>1403</v>
       </c>
       <c r="D7" t="s">
         <v>1118</v>
@@ -47486,12 +47597,12 @@
         <v>896</v>
       </c>
       <c r="P7" t="s">
-        <v>1398</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" t="s">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="C8" t="s">
         <v>90</v>
@@ -47506,7 +47617,7 @@
         <v>200</v>
       </c>
       <c r="G8" t="s">
-        <v>1400</v>
+        <v>1406</v>
       </c>
       <c r="H8" t="s">
         <v>1108</v>
@@ -47523,22 +47634,22 @@
         <v>320</v>
       </c>
       <c r="C9" t="s">
-        <v>1401</v>
+        <v>1407</v>
       </c>
       <c r="D9" t="s">
-        <v>1402</v>
+        <v>1408</v>
       </c>
       <c r="E9" t="s">
-        <v>1403</v>
+        <v>1409</v>
       </c>
       <c r="F9" t="s">
         <v>409</v>
       </c>
       <c r="G9" t="s">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="H9" t="s">
-        <v>1405</v>
+        <v>1411</v>
       </c>
       <c r="L9" t="s">
         <v>958</v>
@@ -47549,22 +47660,22 @@
         <v>246</v>
       </c>
       <c r="C10" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="D10" t="s">
         <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="F10" t="s">
         <v>48</v>
       </c>
       <c r="G10" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="H10" t="s">
-        <v>1409</v>
+        <v>1415</v>
       </c>
       <c r="L10" t="s">
         <v>1050</v>
@@ -47572,33 +47683,33 @@
     </row>
     <row r="11" spans="1:17">
       <c r="C11" t="s">
-        <v>1410</v>
+        <v>1416</v>
       </c>
       <c r="D11" t="s">
-        <v>1411</v>
+        <v>1417</v>
       </c>
       <c r="E11" t="s">
-        <v>1412</v>
+        <v>1418</v>
       </c>
       <c r="F11" t="s">
         <v>469</v>
       </c>
       <c r="G11" t="s">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="H11" t="s">
-        <v>1414</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="C12" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="D12" t="s">
         <v>1190</v>
       </c>
       <c r="E12" t="s">
-        <v>1416</v>
+        <v>1422</v>
       </c>
       <c r="F12" t="s">
         <v>283</v>
@@ -47612,19 +47723,19 @@
     </row>
     <row r="13" spans="1:17">
       <c r="C13" t="s">
-        <v>1417</v>
+        <v>1423</v>
       </c>
       <c r="D13" t="s">
-        <v>1418</v>
+        <v>1424</v>
       </c>
       <c r="E13" t="s">
-        <v>1419</v>
+        <v>1425</v>
       </c>
       <c r="F13" t="s">
         <v>107</v>
       </c>
       <c r="G13" t="s">
-        <v>1420</v>
+        <v>1426</v>
       </c>
       <c r="H13" t="s">
         <v>52</v>
@@ -47632,7 +47743,7 @@
     </row>
     <row r="14" spans="1:17">
       <c r="C14" t="s">
-        <v>1421</v>
+        <v>1427</v>
       </c>
       <c r="D14" t="s">
         <v>47</v>
@@ -47641,7 +47752,7 @@
         <v>1169</v>
       </c>
       <c r="G14" t="s">
-        <v>1422</v>
+        <v>1428</v>
       </c>
       <c r="H14" t="s">
         <v>751</v>
@@ -47649,13 +47760,13 @@
     </row>
     <row r="15" spans="1:17">
       <c r="C15" t="s">
-        <v>1423</v>
+        <v>1429</v>
       </c>
       <c r="D15" t="s">
-        <v>1424</v>
+        <v>1430</v>
       </c>
       <c r="E15" t="s">
-        <v>1424</v>
+        <v>1430</v>
       </c>
       <c r="G15" t="s">
         <v>1296</v>
@@ -47666,13 +47777,13 @@
     </row>
     <row r="16" spans="1:17">
       <c r="C16" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
       <c r="D16" t="s">
-        <v>1426</v>
+        <v>1432</v>
       </c>
       <c r="E16" t="s">
-        <v>1427</v>
+        <v>1433</v>
       </c>
       <c r="G16" t="s">
         <v>565</v>
@@ -47683,7 +47794,7 @@
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>1428</v>
+        <v>1434</v>
       </c>
       <c r="D17" t="s">
         <v>132</v>
@@ -47692,7 +47803,7 @@
         <v>259</v>
       </c>
       <c r="G17" t="s">
-        <v>1429</v>
+        <v>1435</v>
       </c>
       <c r="H17" t="s">
         <v>782</v>
@@ -47700,55 +47811,55 @@
     </row>
     <row r="18" spans="3:8">
       <c r="C18" t="s">
-        <v>1430</v>
+        <v>1436</v>
       </c>
       <c r="D18" t="s">
         <v>1299</v>
       </c>
       <c r="E18" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="G18" t="s">
-        <v>1432</v>
+        <v>1438</v>
       </c>
       <c r="H18" t="s">
-        <v>1398</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="19" spans="3:8">
       <c r="C19" t="s">
-        <v>1433</v>
+        <v>1439</v>
       </c>
       <c r="D19" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="E19" t="s">
-        <v>1435</v>
+        <v>1441</v>
       </c>
       <c r="G19" t="s">
-        <v>1436</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="20" spans="3:8">
       <c r="C20" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="D20" t="s">
         <v>1130</v>
       </c>
       <c r="E20" t="s">
-        <v>1438</v>
+        <v>1444</v>
       </c>
       <c r="G20" t="s">
-        <v>1439</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="21" spans="3:8">
       <c r="C21" t="s">
-        <v>1440</v>
+        <v>1446</v>
       </c>
       <c r="D21" t="s">
-        <v>1441</v>
+        <v>1447</v>
       </c>
       <c r="E21" t="s">
         <v>161</v>
@@ -47762,18 +47873,18 @@
         <v>282</v>
       </c>
       <c r="E22" t="s">
-        <v>1442</v>
+        <v>1448</v>
       </c>
       <c r="G22" t="s">
-        <v>1443</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="23" spans="3:8">
       <c r="D23" t="s">
-        <v>1444</v>
+        <v>1450</v>
       </c>
       <c r="E23" t="s">
-        <v>1445</v>
+        <v>1451</v>
       </c>
       <c r="G23" t="s">
         <v>171</v>
@@ -47781,10 +47892,10 @@
     </row>
     <row r="24" spans="3:8">
       <c r="D24" t="s">
-        <v>1446</v>
+        <v>1452</v>
       </c>
       <c r="E24" t="s">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="G24" t="s">
         <v>364</v>
@@ -47792,7 +47903,7 @@
     </row>
     <row r="25" spans="3:8">
       <c r="D25" t="s">
-        <v>1447</v>
+        <v>1453</v>
       </c>
       <c r="E25" t="s">
         <v>122</v>
@@ -47806,7 +47917,7 @@
         <v>1131</v>
       </c>
       <c r="E26" t="s">
-        <v>1448</v>
+        <v>1454</v>
       </c>
       <c r="G26" t="s">
         <v>484</v>
@@ -47814,68 +47925,68 @@
     </row>
     <row r="27" spans="3:8">
       <c r="D27" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="E27" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="G27" t="s">
-        <v>1451</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="28" spans="3:8">
       <c r="D28" t="s">
-        <v>1452</v>
+        <v>1458</v>
       </c>
       <c r="E28" t="s">
-        <v>1453</v>
+        <v>1459</v>
       </c>
       <c r="G28" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="29" spans="3:8">
       <c r="D29" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="E29" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="G29" t="s">
-        <v>1457</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="30" spans="3:8">
       <c r="D30" t="s">
-        <v>1458</v>
+        <v>1464</v>
       </c>
       <c r="E30" t="s">
         <v>332</v>
       </c>
       <c r="G30" t="s">
-        <v>1459</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="31" spans="3:8">
       <c r="D31" t="s">
-        <v>1460</v>
+        <v>1466</v>
       </c>
       <c r="E31" t="s">
-        <v>1461</v>
+        <v>1467</v>
       </c>
       <c r="G31" t="s">
-        <v>1462</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="32" spans="3:8">
       <c r="D32" t="s">
-        <v>1463</v>
+        <v>1469</v>
       </c>
       <c r="E32" t="s">
-        <v>1464</v>
+        <v>1470</v>
       </c>
       <c r="G32" t="s">
-        <v>1465</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="33" spans="4:7">
@@ -47883,15 +47994,15 @@
         <v>1053</v>
       </c>
       <c r="E33" t="s">
-        <v>1466</v>
+        <v>1472</v>
       </c>
       <c r="G33" t="s">
-        <v>1467</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="34" spans="4:7">
       <c r="D34" t="s">
-        <v>1468</v>
+        <v>1474</v>
       </c>
       <c r="E34" t="s">
         <v>1099</v>
@@ -47902,7 +48013,7 @@
     </row>
     <row r="35" spans="4:7">
       <c r="D35" t="s">
-        <v>1469</v>
+        <v>1475</v>
       </c>
       <c r="E35" t="s">
         <v>190</v>
@@ -47913,54 +48024,54 @@
     </row>
     <row r="36" spans="4:7">
       <c r="D36" t="s">
-        <v>1470</v>
+        <v>1476</v>
       </c>
       <c r="E36" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="G36" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="37" spans="4:7">
       <c r="D37" t="s">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="E37" t="s">
-        <v>1474</v>
+        <v>1480</v>
       </c>
       <c r="G37" t="s">
-        <v>1475</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="38" spans="4:7">
       <c r="D38" t="s">
-        <v>1476</v>
+        <v>1482</v>
       </c>
       <c r="E38" t="s">
-        <v>1477</v>
+        <v>1483</v>
       </c>
       <c r="G38" t="s">
-        <v>1478</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="39" spans="4:7">
       <c r="D39" t="s">
-        <v>1479</v>
+        <v>1485</v>
       </c>
       <c r="E39" t="s">
-        <v>1480</v>
+        <v>1486</v>
       </c>
       <c r="G39" t="s">
-        <v>1481</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="40" spans="4:7">
       <c r="D40" t="s">
-        <v>1482</v>
+        <v>1488</v>
       </c>
       <c r="E40" t="s">
-        <v>1483</v>
+        <v>1489</v>
       </c>
       <c r="G40" t="s">
         <v>272</v>
@@ -47974,40 +48085,40 @@
         <v>1028</v>
       </c>
       <c r="G41" t="s">
-        <v>1484</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="42" spans="4:7">
       <c r="D42" t="s">
-        <v>1485</v>
+        <v>1491</v>
       </c>
       <c r="E42" t="s">
         <v>1105</v>
       </c>
       <c r="G42" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="43" spans="4:7">
       <c r="D43" t="s">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="E43" t="s">
         <v>1113</v>
       </c>
       <c r="G43" t="s">
-        <v>1487</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="44" spans="4:7">
       <c r="D44" t="s">
-        <v>1427</v>
+        <v>1433</v>
       </c>
       <c r="E44" t="s">
-        <v>1488</v>
+        <v>1494</v>
       </c>
       <c r="G44" t="s">
-        <v>1489</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="45" spans="4:7">
@@ -48018,7 +48129,7 @@
         <v>563</v>
       </c>
       <c r="G45" t="s">
-        <v>1490</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="46" spans="4:7">
@@ -48026,15 +48137,15 @@
         <v>320</v>
       </c>
       <c r="E46" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="G46" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="47" spans="4:7">
       <c r="D47" t="s">
-        <v>1492</v>
+        <v>1498</v>
       </c>
       <c r="E47" t="s">
         <v>605</v>
@@ -48048,12 +48159,12 @@
         <v>754</v>
       </c>
       <c r="G48" t="s">
-        <v>1493</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="49" spans="4:7">
       <c r="D49" t="s">
-        <v>1494</v>
+        <v>1500</v>
       </c>
       <c r="G49" t="s">
         <v>295</v>
@@ -48061,47 +48172,47 @@
     </row>
     <row r="50" spans="4:7">
       <c r="D50" t="s">
-        <v>1495</v>
+        <v>1501</v>
       </c>
       <c r="G50" t="s">
-        <v>1496</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="51" spans="4:7">
       <c r="D51" t="s">
-        <v>1497</v>
+        <v>1503</v>
       </c>
       <c r="G51" t="s">
-        <v>1498</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="52" spans="4:7">
       <c r="D52" t="s">
-        <v>1499</v>
+        <v>1505</v>
       </c>
       <c r="G52" t="s">
-        <v>1500</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="53" spans="4:7">
       <c r="D53" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="G53" t="s">
-        <v>1501</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="54" spans="4:7">
       <c r="D54" t="s">
-        <v>1502</v>
+        <v>1508</v>
       </c>
       <c r="G54" t="s">
-        <v>1503</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="55" spans="4:7">
       <c r="D55" t="s">
-        <v>1504</v>
+        <v>1510</v>
       </c>
       <c r="G55" t="s">
         <v>647</v>
@@ -48109,15 +48220,15 @@
     </row>
     <row r="56" spans="4:7">
       <c r="D56" t="s">
-        <v>1505</v>
+        <v>1511</v>
       </c>
       <c r="G56" t="s">
-        <v>1506</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="57" spans="4:7">
       <c r="D57" t="s">
-        <v>1507</v>
+        <v>1344</v>
       </c>
       <c r="G57" t="s">
         <v>393</v>
@@ -48125,63 +48236,63 @@
     </row>
     <row r="58" spans="4:7">
       <c r="D58" t="s">
-        <v>1508</v>
+        <v>1513</v>
       </c>
       <c r="G58" t="s">
-        <v>1509</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="59" spans="4:7">
       <c r="D59" t="s">
-        <v>1510</v>
+        <v>1515</v>
       </c>
       <c r="G59" t="s">
-        <v>1511</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="60" spans="4:7">
       <c r="D60" t="s">
-        <v>1512</v>
+        <v>1517</v>
       </c>
       <c r="G60" t="s">
-        <v>1513</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="61" spans="4:7">
       <c r="D61" t="s">
-        <v>1514</v>
+        <v>1519</v>
       </c>
       <c r="G61" t="s">
-        <v>1515</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="62" spans="4:7">
       <c r="D62" t="s">
-        <v>1516</v>
+        <v>1521</v>
       </c>
       <c r="G62" t="s">
-        <v>1517</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="63" spans="4:7">
       <c r="D63" t="s">
-        <v>1518</v>
+        <v>1523</v>
       </c>
       <c r="G63" t="s">
-        <v>1519</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="64" spans="4:7">
       <c r="D64" t="s">
-        <v>1520</v>
+        <v>1525</v>
       </c>
       <c r="G64" t="s">
-        <v>1521</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="65" spans="4:7">
       <c r="D65" t="s">
-        <v>1522</v>
+        <v>1527</v>
       </c>
       <c r="G65" t="s">
         <v>970</v>
@@ -48189,10 +48300,10 @@
     </row>
     <row r="66" spans="4:7">
       <c r="D66" t="s">
-        <v>1523</v>
+        <v>1528</v>
       </c>
       <c r="G66" t="s">
-        <v>1524</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="67" spans="4:7">
@@ -48205,82 +48316,82 @@
     </row>
     <row r="68" spans="4:7">
       <c r="D68" t="s">
-        <v>1525</v>
+        <v>1530</v>
       </c>
       <c r="G68" t="s">
-        <v>1526</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="69" spans="4:7">
       <c r="D69" t="s">
-        <v>1527</v>
+        <v>1532</v>
       </c>
       <c r="G69" t="s">
-        <v>1528</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="70" spans="4:7">
       <c r="D70" t="s">
-        <v>1529</v>
+        <v>1534</v>
       </c>
       <c r="G70" t="s">
-        <v>1530</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="71" spans="4:7">
       <c r="D71" t="s">
-        <v>1531</v>
+        <v>1536</v>
       </c>
       <c r="G71" t="s">
-        <v>1532</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="72" spans="4:7">
       <c r="D72" t="s">
-        <v>1461</v>
+        <v>1467</v>
       </c>
       <c r="G72" t="s">
-        <v>1533</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="73" spans="4:7">
       <c r="D73" t="s">
-        <v>1534</v>
+        <v>1539</v>
       </c>
       <c r="G73" t="s">
-        <v>1535</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="74" spans="4:7">
       <c r="D74" t="s">
-        <v>1536</v>
+        <v>1541</v>
       </c>
       <c r="G74" t="s">
-        <v>1537</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="75" spans="4:7">
       <c r="D75" t="s">
-        <v>1538</v>
+        <v>1543</v>
       </c>
       <c r="G75" t="s">
-        <v>1539</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="76" spans="4:7">
       <c r="D76" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="G76" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="77" spans="4:7">
       <c r="D77" t="s">
-        <v>1542</v>
+        <v>1547</v>
       </c>
       <c r="G77" t="s">
-        <v>1543</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="78" spans="4:7">
@@ -48288,12 +48399,12 @@
         <v>1202</v>
       </c>
       <c r="G78" t="s">
-        <v>1544</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="79" spans="4:7">
       <c r="D79" t="s">
-        <v>1545</v>
+        <v>1550</v>
       </c>
       <c r="G79" t="s">
         <v>132</v>
@@ -48301,10 +48412,10 @@
     </row>
     <row r="80" spans="4:7">
       <c r="D80" t="s">
-        <v>1546</v>
+        <v>1551</v>
       </c>
       <c r="G80" t="s">
-        <v>1547</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="81" spans="4:7">
@@ -48312,108 +48423,108 @@
         <v>855</v>
       </c>
       <c r="G81" t="s">
-        <v>1548</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="82" spans="4:7">
       <c r="D82" t="s">
-        <v>1549</v>
+        <v>1554</v>
       </c>
       <c r="G82" t="s">
-        <v>1550</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="83" spans="4:7">
       <c r="D83" t="s">
-        <v>1551</v>
+        <v>1556</v>
       </c>
       <c r="G83" t="s">
-        <v>1552</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="84" spans="4:7">
       <c r="D84" t="s">
-        <v>1553</v>
+        <v>1558</v>
       </c>
       <c r="G84" t="s">
-        <v>1554</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="85" spans="4:7">
       <c r="D85" t="s">
-        <v>1555</v>
+        <v>1560</v>
       </c>
       <c r="G85" t="s">
-        <v>1556</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="86" spans="4:7">
       <c r="D86" t="s">
-        <v>1557</v>
+        <v>1562</v>
       </c>
       <c r="G86" t="s">
-        <v>1558</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="87" spans="4:7">
       <c r="D87" t="s">
-        <v>1559</v>
+        <v>1564</v>
       </c>
       <c r="G87" t="s">
-        <v>1560</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="88" spans="4:7">
       <c r="D88" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="G88" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="89" spans="4:7">
       <c r="D89" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="G89" t="s">
-        <v>1564</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="90" spans="4:7">
       <c r="D90" t="s">
-        <v>1565</v>
+        <v>1570</v>
       </c>
       <c r="G90" t="s">
-        <v>1566</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="91" spans="4:7">
       <c r="D91" t="s">
-        <v>1567</v>
+        <v>1572</v>
       </c>
       <c r="G91" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="92" spans="4:7">
       <c r="D92" t="s">
-        <v>1569</v>
+        <v>1574</v>
       </c>
       <c r="G92" t="s">
-        <v>1570</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="93" spans="4:7">
       <c r="D93" t="s">
-        <v>1571</v>
+        <v>1576</v>
       </c>
       <c r="G93" t="s">
-        <v>1572</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="94" spans="4:7">
       <c r="D94" t="s">
-        <v>1573</v>
+        <v>1578</v>
       </c>
       <c r="G94" t="s">
         <v>260</v>
@@ -48424,20 +48535,20 @@
         <v>1112</v>
       </c>
       <c r="G95" t="s">
-        <v>1574</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="96" spans="4:7">
       <c r="D96" t="s">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="G96" t="s">
-        <v>1576</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="97" spans="4:7">
       <c r="D97" t="s">
-        <v>1577</v>
+        <v>1582</v>
       </c>
       <c r="G97" t="s">
         <v>660</v>
@@ -48448,12 +48559,12 @@
         <v>190</v>
       </c>
       <c r="G98" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="99" spans="4:7">
       <c r="D99" t="s">
-        <v>1579</v>
+        <v>1584</v>
       </c>
       <c r="G99" t="s">
         <v>772</v>
@@ -48461,7 +48572,7 @@
     </row>
     <row r="100" spans="4:7">
       <c r="D100" t="s">
-        <v>1580</v>
+        <v>1585</v>
       </c>
       <c r="G100" t="s">
         <v>905</v>
@@ -48469,111 +48580,111 @@
     </row>
     <row r="101" spans="4:7">
       <c r="D101" t="s">
-        <v>1581</v>
+        <v>1586</v>
       </c>
       <c r="G101" t="s">
-        <v>1582</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="102" spans="4:7">
       <c r="D102" t="s">
-        <v>1583</v>
+        <v>1588</v>
       </c>
       <c r="G102" t="s">
-        <v>1584</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="103" spans="4:7">
       <c r="D103" t="s">
-        <v>1585</v>
+        <v>1590</v>
       </c>
       <c r="G103" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="104" spans="4:7">
       <c r="D104" t="s">
-        <v>1587</v>
+        <v>1592</v>
       </c>
       <c r="G104" t="s">
-        <v>1588</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="105" spans="4:7">
       <c r="D105" t="s">
-        <v>1589</v>
+        <v>1594</v>
       </c>
       <c r="G105" t="s">
-        <v>1590</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="106" spans="4:7">
       <c r="D106" t="s">
-        <v>1591</v>
+        <v>1596</v>
       </c>
       <c r="G106" t="s">
-        <v>1592</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="107" spans="4:7">
       <c r="D107" t="s">
-        <v>1593</v>
+        <v>1598</v>
       </c>
       <c r="G107" t="s">
-        <v>1594</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="108" spans="4:7">
       <c r="D108" t="s">
-        <v>1595</v>
+        <v>1600</v>
       </c>
       <c r="G108" t="s">
-        <v>1596</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="109" spans="4:7">
       <c r="D109" t="s">
-        <v>1597</v>
+        <v>1602</v>
       </c>
       <c r="G109" t="s">
-        <v>1598</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="110" spans="4:7">
       <c r="D110" t="s">
-        <v>1599</v>
+        <v>1604</v>
       </c>
       <c r="G110" t="s">
-        <v>1600</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="111" spans="4:7">
       <c r="D111" t="s">
-        <v>1601</v>
+        <v>1606</v>
       </c>
       <c r="G111" t="s">
-        <v>1602</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="112" spans="4:7">
       <c r="D112" t="s">
-        <v>1603</v>
+        <v>1608</v>
       </c>
       <c r="G112" t="s">
-        <v>1604</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="113" spans="4:7">
       <c r="D113" t="s">
-        <v>1605</v>
+        <v>1610</v>
       </c>
       <c r="G113" t="s">
-        <v>1606</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="114" spans="4:7">
       <c r="D114" t="s">
-        <v>1607</v>
+        <v>1612</v>
       </c>
       <c r="G114" t="s">
         <v>271</v>
@@ -48581,23 +48692,23 @@
     </row>
     <row r="115" spans="4:7">
       <c r="D115" t="s">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="G115" t="s">
-        <v>1609</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="116" spans="4:7">
       <c r="D116" t="s">
-        <v>1610</v>
+        <v>1615</v>
       </c>
       <c r="G116" t="s">
-        <v>1611</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="117" spans="4:7">
       <c r="D117" t="s">
-        <v>1612</v>
+        <v>1617</v>
       </c>
       <c r="G117" t="s">
         <v>1020</v>
@@ -48605,7 +48716,7 @@
     </row>
     <row r="118" spans="4:7">
       <c r="D118" t="s">
-        <v>1613</v>
+        <v>1618</v>
       </c>
       <c r="G118" t="s">
         <v>1007</v>
@@ -48613,7 +48724,7 @@
     </row>
     <row r="119" spans="4:7">
       <c r="D119" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="G119" t="s">
         <v>1029</v>
@@ -48621,7 +48732,7 @@
     </row>
     <row r="120" spans="4:7">
       <c r="D120" t="s">
-        <v>1615</v>
+        <v>1620</v>
       </c>
       <c r="G120" t="s">
         <v>1032</v>
@@ -48629,7 +48740,7 @@
     </row>
     <row r="121" spans="4:7">
       <c r="D121" t="s">
-        <v>1616</v>
+        <v>1621</v>
       </c>
       <c r="G121" t="s">
         <v>982</v>
@@ -48637,15 +48748,15 @@
     </row>
     <row r="122" spans="4:7">
       <c r="D122" t="s">
-        <v>1617</v>
+        <v>1622</v>
       </c>
       <c r="G122" t="s">
-        <v>1618</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="123" spans="4:7">
       <c r="D123" t="s">
-        <v>1619</v>
+        <v>1624</v>
       </c>
       <c r="G123" t="s">
         <v>1100</v>
@@ -48653,7 +48764,7 @@
     </row>
     <row r="124" spans="4:7">
       <c r="D124" t="s">
-        <v>1620</v>
+        <v>1625</v>
       </c>
       <c r="G124" t="s">
         <v>874</v>
@@ -48661,7 +48772,7 @@
     </row>
     <row r="125" spans="4:7">
       <c r="D125" t="s">
-        <v>1621</v>
+        <v>1626</v>
       </c>
       <c r="G125" t="s">
         <v>1001</v>
@@ -48669,7 +48780,7 @@
     </row>
     <row r="126" spans="4:7">
       <c r="D126" t="s">
-        <v>1622</v>
+        <v>1627</v>
       </c>
       <c r="G126" t="s">
         <v>755</v>
@@ -48677,7 +48788,7 @@
     </row>
     <row r="127" spans="4:7">
       <c r="D127" t="s">
-        <v>1623</v>
+        <v>1628</v>
       </c>
       <c r="G127" t="s">
         <v>735</v>
@@ -48685,7 +48796,7 @@
     </row>
     <row r="128" spans="4:7">
       <c r="D128" t="s">
-        <v>1624</v>
+        <v>1629</v>
       </c>
       <c r="G128" t="s">
         <v>134</v>
@@ -48693,7 +48804,7 @@
     </row>
     <row r="129" spans="4:7">
       <c r="D129" t="s">
-        <v>1625</v>
+        <v>1630</v>
       </c>
       <c r="G129" t="s">
         <v>1054</v>
@@ -48701,7 +48812,7 @@
     </row>
     <row r="130" spans="4:7">
       <c r="D130" t="s">
-        <v>1626</v>
+        <v>1631</v>
       </c>
       <c r="G130" t="s">
         <v>721</v>
@@ -48709,7 +48820,7 @@
     </row>
     <row r="131" spans="4:7">
       <c r="D131" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="G131" t="s">
         <v>512</v>
@@ -48717,7 +48828,7 @@
     </row>
     <row r="132" spans="4:7">
       <c r="D132" t="s">
-        <v>1628</v>
+        <v>1633</v>
       </c>
       <c r="G132" t="s">
         <v>871</v>
@@ -48725,7 +48836,7 @@
     </row>
     <row r="133" spans="4:7">
       <c r="D133" t="s">
-        <v>1629</v>
+        <v>1634</v>
       </c>
       <c r="G133" t="s">
         <v>224</v>
@@ -48733,7 +48844,7 @@
     </row>
     <row r="134" spans="4:7">
       <c r="D134" t="s">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="G134" t="s">
         <v>433</v>
@@ -48741,7 +48852,7 @@
     </row>
     <row r="135" spans="4:7">
       <c r="D135" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="G135" t="s">
         <v>715</v>
@@ -48749,7 +48860,7 @@
     </row>
     <row r="136" spans="4:7">
       <c r="D136" t="s">
-        <v>1632</v>
+        <v>1637</v>
       </c>
       <c r="G136" t="s">
         <v>458</v>
@@ -48757,15 +48868,15 @@
     </row>
     <row r="137" spans="4:7">
       <c r="D137" t="s">
-        <v>1633</v>
+        <v>1638</v>
       </c>
       <c r="G137" t="s">
-        <v>1634</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="138" spans="4:7">
       <c r="D138" t="s">
-        <v>1635</v>
+        <v>1640</v>
       </c>
       <c r="G138" t="s">
         <v>342</v>
@@ -48773,7 +48884,7 @@
     </row>
     <row r="139" spans="4:7">
       <c r="D139" t="s">
-        <v>1636</v>
+        <v>1641</v>
       </c>
       <c r="G139" t="s">
         <v>441</v>
@@ -48781,7 +48892,7 @@
     </row>
     <row r="140" spans="4:7">
       <c r="D140" t="s">
-        <v>1637</v>
+        <v>1642</v>
       </c>
       <c r="G140" t="s">
         <v>977</v>
@@ -48789,7 +48900,7 @@
     </row>
     <row r="141" spans="4:7">
       <c r="D141" t="s">
-        <v>1638</v>
+        <v>1643</v>
       </c>
       <c r="G141" t="s">
         <v>817</v>
@@ -48797,7 +48908,7 @@
     </row>
     <row r="142" spans="4:7">
       <c r="D142" t="s">
-        <v>1639</v>
+        <v>1644</v>
       </c>
       <c r="G142" t="s">
         <v>894</v>
@@ -48805,7 +48916,7 @@
     </row>
     <row r="143" spans="4:7">
       <c r="D143" t="s">
-        <v>1640</v>
+        <v>1645</v>
       </c>
       <c r="G143" t="s">
         <v>1106</v>
@@ -48813,7 +48924,7 @@
     </row>
     <row r="144" spans="4:7">
       <c r="D144" t="s">
-        <v>1641</v>
+        <v>1646</v>
       </c>
       <c r="G144" t="s">
         <v>470</v>
@@ -48821,7 +48932,7 @@
     </row>
     <row r="145" spans="4:7">
       <c r="D145" t="s">
-        <v>1642</v>
+        <v>1647</v>
       </c>
       <c r="G145" t="s">
         <v>1114</v>
@@ -48829,7 +48940,7 @@
     </row>
     <row r="146" spans="4:7">
       <c r="D146" t="s">
-        <v>1643</v>
+        <v>1648</v>
       </c>
       <c r="G146" t="s">
         <v>1121</v>
@@ -48837,7 +48948,7 @@
     </row>
     <row r="147" spans="4:7">
       <c r="D147" t="s">
-        <v>1644</v>
+        <v>1649</v>
       </c>
       <c r="G147" t="s">
         <v>1132</v>
@@ -48845,7 +48956,7 @@
     </row>
     <row r="148" spans="4:7">
       <c r="D148" t="s">
-        <v>1645</v>
+        <v>1650</v>
       </c>
       <c r="G148" t="s">
         <v>1014</v>
@@ -48853,7 +48964,7 @@
     </row>
     <row r="149" spans="4:7">
       <c r="D149" t="s">
-        <v>1646</v>
+        <v>1651</v>
       </c>
       <c r="G149" t="s">
         <v>614</v>
@@ -48861,7 +48972,7 @@
     </row>
     <row r="150" spans="4:7">
       <c r="D150" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="G150" t="s">
         <v>1185</v>
@@ -48997,34 +49108,34 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15">
       <c r="A1" s="19" t="s">
-        <v>1648</v>
+        <v>1653</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>1649</v>
+        <v>1654</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>1650</v>
+        <v>1655</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>1651</v>
+        <v>1656</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>1652</v>
+        <v>1657</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>1653</v>
+        <v>1658</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>1654</v>
+        <v>1659</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>1655</v>
+        <v>1660</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>1656</v>
+        <v>1661</v>
       </c>
       <c r="J1" s="19" t="s">
-        <v>1657</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -49067,22 +49178,22 @@
         <v>5</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>1658</v>
+        <v>1663</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>1381</v>
+        <v>1388</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>1659</v>
+        <v>1664</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>1660</v>
+        <v>1665</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>1661</v>
+        <v>1666</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>1662</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -49105,10 +49216,10 @@
         <v>24</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>1663</v>
+        <v>1668</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>1664</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -49131,7 +49242,7 @@
         <v>36</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>1665</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -49169,13 +49280,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="24" t="s">
-        <v>1666</v>
+        <v>1671</v>
       </c>
       <c r="B1" s="28" t="s">
         <v>744</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>1667</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="23.25" customHeight="1">
@@ -49187,12 +49298,12 @@
         <v>46113</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>1668</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="24" t="s">
-        <v>1381</v>
+        <v>1388</v>
       </c>
       <c r="B3" s="26" t="str">
         <f>_xlfn.XLOOKUP($B$1,BASE!$AI:$AI,BASE!$N:$N,"No encontrado",0)</f>
@@ -49232,7 +49343,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="24" t="s">
-        <v>1661</v>
+        <v>1666</v>
       </c>
       <c r="B7" s="26" t="str">
         <f>_xlfn.XLOOKUP($B$1,BASE!$AI:$AI,BASE!$AC:$AC,"No encontrado",0)</f>
@@ -49262,7 +49373,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="24" t="s">
-        <v>1663</v>
+        <v>1668</v>
       </c>
       <c r="B10" s="26" t="str">
         <f>_xlfn.XLOOKUP($B$1,BASE!$AI:$AI,BASE!$AD:$AD,"No encontrado",0)</f>
@@ -49282,7 +49393,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="24" t="s">
-        <v>1669</v>
+        <v>1674</v>
       </c>
       <c r="B12" s="26">
         <f>_xlfn.XLOOKUP($B$1,BASE!$AI:$AI,BASE!$W:$W,"No encontrado",0)</f>
@@ -49292,7 +49403,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="24" t="s">
-        <v>1670</v>
+        <v>1675</v>
       </c>
       <c r="B13" s="26" t="str">
         <f>_xlfn.XLOOKUP($B$1,BASE!$AI:$AI,BASE!$X:$X,"No encontrado",0)</f>
@@ -49332,7 +49443,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="24" t="s">
-        <v>1671</v>
+        <v>1676</v>
       </c>
       <c r="B17" s="26" t="str">
         <f>_xlfn.XLOOKUP($B$1,BASE!$AI:$AI,BASE!$L:$L,"No encontrado",0)</f>
